--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -1224,30 +1224,33 @@
     <t xml:space="preserve">Jodi Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">SASSY SIREN</t>
+    <t xml:space="preserve">FEDERAL SABLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashley Bock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLATER'S GATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUNA ROSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tammy Hancock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECRET ASSASSIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brett Hazelgrove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOOKED ON HER</t>
   </si>
   <si>
     <t xml:space="preserve">Jamie Hosking</t>
   </si>
   <si>
-    <t xml:space="preserve">SLATER'S GATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUNA ROSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tammy Hancock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SECRET ASSASSIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brett Hazelgrove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOOKED ON HER</t>
-  </si>
-  <si>
     <t xml:space="preserve">MITTS WHITAKER</t>
   </si>
   <si>
@@ -1350,174 +1353,174 @@
     <t xml:space="preserve">GARRARD'S HORSE AND HOUND 300m</t>
   </si>
   <si>
-    <t xml:space="preserve">DO RUN BANDI</t>
+    <t xml:space="preserve">BIG OPERATOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHE'S BUBBLES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVEN MORE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matthew Heilbronn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SISSY MAYBELLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anne Clelland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SALLY VISION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peter Young</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OH LENNY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARMOR DEFIANT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lina Langmaid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAABINGA TIGER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Geoff Draheim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE LIDS FLY ON LADBROKES LIVE CHANNELS 5th Grade  300m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAME OF LOVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANDO WHIRLWIND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keith Boan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUTA SUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPICY VIKING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barry Kitchener</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSUNAMI SEA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anita Watts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOVING JESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIZZARO BOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg Hazelgrove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANAMA KING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LADBROKES BIG BETS COPY NOW 5th Grade H 300m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDSTAR JOBLIN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAST LOVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOAKI RADAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ORLANDO BEACH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chloe Muller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT'S AN ACE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terry Priest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOM GUMP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZABDON JUSTICE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AFFLECK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T20:48:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GORSKI SEMI TIPPERS 5th Grade H 300m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLIGHTS BOOKED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gary Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASTON POSEIDON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mal Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRUSTFUL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANDO WATCH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRETTY STRAIGHT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXHIBIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INLAND MARK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GOLDSTAR HECTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14T21:08:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THE IPSWICH TRIBUNE 300m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT AIRLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAPPING ACES</t>
   </si>
   <si>
     <t xml:space="preserve">Christopher Supple</t>
   </si>
   <si>
-    <t xml:space="preserve">BIG OPERATOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHE'S BUBBLES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EVEN MORE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Matthew Heilbronn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SISSY MAYBELLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anne Clelland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SALLY VISION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peter Young</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARMOR DEFIANT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lina Langmaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAABINGA TIGER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Geoff Draheim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE LIDS FLY ON LADBROKES LIVE CHANNELS 5th Grade  300m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAME OF LOVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANDO WHIRLWIND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keith Boan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUTA SUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPICY VIKING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Barry Kitchener</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSUNAMI SEA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anita Watts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOVING JESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIZZARO BOY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reg Hazelgrove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PANAMA KING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LADBROKES BIG BETS COPY NOW 5th Grade H 300m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOLDSTAR JOBLIN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAST LOVE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOAKI RADAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ORLANDO BEACH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chloe Muller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT'S AN ACE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terry Priest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOM GUMP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZABDON JUSTICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AFFLECK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T20:48:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GORSKI SEMI TIPPERS 5th Grade H 300m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FLIGHTS BOOKED</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gary Moore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASTON POSEIDON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mal Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRUSTFUL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANDO WATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRETTY STRAIGHT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EXHIBIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INLAND MARK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GOLDSTAR HECTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14T21:08:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE IPSWICH TRIBUNE 300m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT AIRLEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAPPING ACES</t>
-  </si>
-  <si>
     <t xml:space="preserve">GRANDIOSE GIRL</t>
   </si>
   <si>
@@ -1552,9 +1555,6 @@
   </si>
   <si>
     <t xml:space="preserve">BAREFOOT GYPSY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ashley Bock</t>
   </si>
   <si>
     <t xml:space="preserve">RAYA'S ROMANCE</t>
@@ -26132,28 +26132,28 @@
         <v>400</v>
       </c>
       <c r="K165" t="n">
-        <v>3.66276079866069</v>
+        <v>3.24798607170576</v>
       </c>
       <c r="L165" t="n">
-        <v>3.17495793517255</v>
+        <v>2.926349670812</v>
       </c>
       <c r="M165" t="n">
-        <v>15.3640732711515</v>
+        <v>10.991044716967</v>
       </c>
       <c r="N165" t="s">
         <v>73</v>
       </c>
       <c r="O165" t="n">
-        <v>0.19863110422535</v>
+        <v>0.200189037785146</v>
       </c>
       <c r="P165" t="n">
-        <v>0.187093156230744</v>
+        <v>0.188825874124904</v>
       </c>
       <c r="Q165" t="n">
-        <v>2.02025309961681</v>
+        <v>1.83958430696269</v>
       </c>
       <c r="R165" t="n">
-        <v>1.48640048144129</v>
+        <v>1.39383810869465</v>
       </c>
       <c r="S165" t="n">
         <v>0</v>
@@ -26228,7 +26228,7 @@
         <v>74</v>
       </c>
       <c r="AQ165" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR165"/>
       <c r="AS165" t="s">
@@ -26282,28 +26282,28 @@
         <v>402</v>
       </c>
       <c r="K166" t="n">
-        <v>4.32773018431696</v>
+        <v>3.92371934243885</v>
       </c>
       <c r="L166" t="n">
-        <v>5.41725800335843</v>
+        <v>5.13783714359106</v>
       </c>
       <c r="M166" t="n">
-        <v>-20.1121640941971</v>
+        <v>-23.6309125264258</v>
       </c>
       <c r="N166" t="s">
         <v>73</v>
       </c>
       <c r="O166" t="n">
-        <v>0.183833040072996</v>
+        <v>0.18232672929629</v>
       </c>
       <c r="P166" t="n">
-        <v>0.18379964483693</v>
+        <v>0.182550071369646</v>
       </c>
       <c r="Q166" t="n">
-        <v>2.23891352613036</v>
+        <v>2.06117362239891</v>
       </c>
       <c r="R166" t="n">
-        <v>1.58313571592345</v>
+        <v>1.49400037821756</v>
       </c>
       <c r="S166" t="n">
         <v>0</v>
@@ -26378,7 +26378,7 @@
         <v>73</v>
       </c>
       <c r="AQ166" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR166"/>
       <c r="AS166" t="s">
@@ -26432,79 +26432,79 @@
         <v>404</v>
       </c>
       <c r="K167" t="n">
-        <v>5.39833966785518</v>
+        <v>9.82537583379486</v>
       </c>
       <c r="L167" t="n">
-        <v>6.03949513859533</v>
+        <v>9.0545948392938</v>
       </c>
       <c r="M167" t="n">
-        <v>-10.6160441564535</v>
+        <v>8.51259507665809</v>
       </c>
       <c r="N167" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="O167" t="n">
-        <v>0.197413585263977</v>
+        <v>0.179292898228436</v>
       </c>
       <c r="P167" t="n">
-        <v>0.187512967741441</v>
+        <v>0.17951252399468</v>
       </c>
       <c r="Q167" t="n">
-        <v>2.69806627370869</v>
+        <v>4.46812408961021</v>
       </c>
       <c r="R167" t="n">
-        <v>1.82341102822716</v>
+        <v>2.75248041494749</v>
       </c>
       <c r="S167" t="n">
-        <v>-0.4</v>
+        <v>-1.4</v>
       </c>
       <c r="T167" t="n">
-        <v>100.789769574544</v>
+        <v>100.393010304263</v>
       </c>
       <c r="U167" t="n">
-        <v>97.6051224894067</v>
+        <v>99.0758432019001</v>
       </c>
       <c r="V167" t="n">
-        <v>97.6051224894067</v>
+        <v>97.8539426803568</v>
       </c>
       <c r="W167" t="n">
-        <v>99.9676130032883</v>
+        <v>102.968452071855</v>
       </c>
       <c r="X167" t="n">
-        <v>101.087652848074</v>
+        <v>98.1921222579117</v>
       </c>
       <c r="Y167" t="n">
-        <v>98.1990022768302</v>
+        <v>96.3339290903539</v>
       </c>
       <c r="Z167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AA167" t="n">
-        <v>98.1990022768302</v>
+        <v>96.6517781352547</v>
       </c>
       <c r="AB167" t="n">
-        <v>97.6051224894067</v>
+        <v>99.0758432019001</v>
       </c>
       <c r="AC167" t="n">
-        <v>97.6051224894067</v>
+        <v>97.8539426803568</v>
       </c>
       <c r="AD167" t="n">
-        <v>97.6051224894067</v>
+        <v>99.0758432019001</v>
       </c>
       <c r="AE167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AF167" t="n">
         <v>7</v>
       </c>
       <c r="AG167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AH167" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AI167" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AJ167" t="n">
         <v>2</v>
@@ -26525,10 +26525,10 @@
         <v>1</v>
       </c>
       <c r="AP167" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="AQ167" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR167"/>
       <c r="AS167" t="s">
@@ -26541,7 +26541,7 @@
         <v>0</v>
       </c>
       <c r="AV167" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="AW167" t="s">
         <v>62</v>
@@ -26582,31 +26582,31 @@
         <v>160</v>
       </c>
       <c r="K168" t="n">
-        <v>12.3253434742919</v>
+        <v>11.340996671977</v>
       </c>
       <c r="L168" t="n">
-        <v>13.4727199245588</v>
+        <v>12.8462427745665</v>
       </c>
       <c r="M168" t="n">
-        <v>-8.51629408680394</v>
+        <v>-11.7174035163776</v>
       </c>
       <c r="N168" t="s">
         <v>73</v>
       </c>
       <c r="O168" t="n">
-        <v>0.19350420024036</v>
+        <v>0.191918644879668</v>
       </c>
       <c r="P168" t="n">
-        <v>0.18379964483693</v>
+        <v>0.182550071369646</v>
       </c>
       <c r="Q168" t="n">
-        <v>5.67569765746174</v>
+        <v>5.19477248618253</v>
       </c>
       <c r="R168" t="n">
-        <v>3.47274297429868</v>
+        <v>3.17182675289038</v>
       </c>
       <c r="S168" t="n">
-        <v>-1.5</v>
+        <v>-1.6</v>
       </c>
       <c r="T168" t="n">
         <v>97.8140750474411</v>
@@ -26678,7 +26678,7 @@
         <v>73</v>
       </c>
       <c r="AQ168" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR168"/>
       <c r="AS168" t="s">
@@ -26732,28 +26732,28 @@
         <v>407</v>
       </c>
       <c r="K169" t="n">
-        <v>12.5363759332981</v>
+        <v>11.653682736721</v>
       </c>
       <c r="L169" t="n">
-        <v>10.7825336927224</v>
+        <v>10.2477712880418</v>
       </c>
       <c r="M169" t="n">
-        <v>16.2655855344975</v>
+        <v>13.7191922922768</v>
       </c>
       <c r="N169" t="s">
         <v>73</v>
       </c>
       <c r="O169" t="n">
-        <v>0.180025087398543</v>
+        <v>0.178549978630727</v>
       </c>
       <c r="P169" t="n">
-        <v>0.17999238391777</v>
+        <v>0.178768694353754</v>
       </c>
       <c r="Q169" t="n">
-        <v>5.67889824209335</v>
+        <v>5.23763906767724</v>
       </c>
       <c r="R169" t="n">
-        <v>3.44831668307838</v>
+        <v>3.17717572871052</v>
       </c>
       <c r="S169" t="n">
         <v>-1.7</v>
@@ -26828,7 +26828,7 @@
         <v>74</v>
       </c>
       <c r="AQ169" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR169"/>
       <c r="AS169" t="s">
@@ -26882,28 +26882,28 @@
         <v>409</v>
       </c>
       <c r="K170" t="n">
-        <v>17.3218824957618</v>
+        <v>16.070973689772</v>
       </c>
       <c r="L170" t="n">
-        <v>14.075721323012</v>
+        <v>13.3148715217681</v>
       </c>
       <c r="M170" t="n">
-        <v>23.0621301619748</v>
+        <v>20.699427429683</v>
       </c>
       <c r="N170" t="s">
         <v>73</v>
       </c>
       <c r="O170" t="n">
-        <v>0.181215252245092</v>
+        <v>0.179730391377579</v>
       </c>
       <c r="P170" t="n">
-        <v>0.181182332558157</v>
+        <v>0.179950553053327</v>
       </c>
       <c r="Q170" t="n">
-        <v>7.71297361958066</v>
+        <v>7.14356428527662</v>
       </c>
       <c r="R170" t="n">
-        <v>4.60012437117401</v>
+        <v>4.23242963632646</v>
       </c>
       <c r="S170" t="n">
         <v>-2.2</v>
@@ -26978,7 +26978,7 @@
         <v>74</v>
       </c>
       <c r="AQ170" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR170"/>
       <c r="AS170" t="s">
@@ -27029,31 +27029,31 @@
         <v>410</v>
       </c>
       <c r="J171" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="K171" t="n">
-        <v>19.6080658397667</v>
+        <v>18.2069529263752</v>
       </c>
       <c r="L171" t="n">
-        <v>19.4530247033651</v>
+        <v>18.2263531984691</v>
       </c>
       <c r="M171" t="n">
-        <v>0.797002722023055</v>
+        <v>-0.106440777717265</v>
       </c>
       <c r="N171" t="s">
         <v>73</v>
       </c>
       <c r="O171" t="n">
-        <v>0.183833040072996</v>
+        <v>0.18232672929629</v>
       </c>
       <c r="P171" t="n">
-        <v>0.18379964483693</v>
+        <v>0.182550071369646</v>
       </c>
       <c r="Q171" t="n">
-        <v>8.78234473325117</v>
+        <v>8.07976685416334</v>
       </c>
       <c r="R171" t="n">
-        <v>5.16058237042015</v>
+        <v>4.74110433462924</v>
       </c>
       <c r="S171" t="n">
         <v>-2.2</v>
@@ -27128,7 +27128,7 @@
         <v>73</v>
       </c>
       <c r="AQ171" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR171"/>
       <c r="AS171" t="s">
@@ -27176,37 +27176,37 @@
         <v>1</v>
       </c>
       <c r="I172" t="s">
+        <v>412</v>
+      </c>
+      <c r="J172" t="s">
         <v>411</v>
       </c>
-      <c r="J172" t="s">
-        <v>404</v>
-      </c>
       <c r="K172" t="n">
-        <v>24.3662523283545</v>
+        <v>22.5500035446121</v>
       </c>
       <c r="L172" t="n">
-        <v>22.0039603960396</v>
+        <v>20.9177996235097</v>
       </c>
       <c r="M172" t="n">
-        <v>10.7357579717335</v>
+        <v>7.8029427113735</v>
       </c>
       <c r="N172" t="s">
         <v>73</v>
       </c>
       <c r="O172" t="n">
-        <v>0.182297176574806</v>
+        <v>0.180803450520291</v>
       </c>
       <c r="P172" t="n">
-        <v>0.182264060344756</v>
+        <v>0.181024926645405</v>
       </c>
       <c r="Q172" t="n">
-        <v>10.8772845269323</v>
+        <v>9.97487818616671</v>
       </c>
       <c r="R172" t="n">
-        <v>6.32759489061828</v>
+        <v>5.79068597074252</v>
       </c>
       <c r="S172" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="T172" t="n">
         <v>99.5994917637027</v>
@@ -27278,7 +27278,7 @@
         <v>74</v>
       </c>
       <c r="AQ172" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="AR172"/>
       <c r="AS172" t="s">
@@ -27305,7 +27305,7 @@
         <v>46279</v>
       </c>
       <c r="B173" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C173" t="s">
         <v>380</v>
@@ -27317,19 +27317,19 @@
         <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G173" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H173" t="n">
         <v>3</v>
       </c>
       <c r="I173" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J173" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K173" t="n">
         <v>2.8605013853851</v>
@@ -27455,7 +27455,7 @@
         <v>46279</v>
       </c>
       <c r="B174" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C174" t="s">
         <v>380</v>
@@ -27467,16 +27467,16 @@
         <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G174" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H174" t="n">
         <v>7</v>
       </c>
       <c r="I174" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="J174" t="s">
         <v>160</v>
@@ -27605,7 +27605,7 @@
         <v>46279</v>
       </c>
       <c r="B175" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C175" t="s">
         <v>380</v>
@@ -27617,19 +27617,19 @@
         <v>3</v>
       </c>
       <c r="F175" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G175" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H175" t="n">
         <v>4</v>
       </c>
       <c r="I175" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J175" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K175" t="n">
         <v>8.76266633112171</v>
@@ -27755,7 +27755,7 @@
         <v>46279</v>
       </c>
       <c r="B176" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C176" t="s">
         <v>380</v>
@@ -27767,19 +27767,19 @@
         <v>3</v>
       </c>
       <c r="F176" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G176" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H176" t="n">
         <v>8</v>
       </c>
       <c r="I176" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J176" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K176" t="n">
         <v>9.63570164728472</v>
@@ -27905,7 +27905,7 @@
         <v>46279</v>
       </c>
       <c r="B177" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C177" t="s">
         <v>380</v>
@@ -27917,19 +27917,19 @@
         <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G177" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H177" t="n">
         <v>1</v>
       </c>
       <c r="I177" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J177" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K177" t="n">
         <v>11.3292893233999</v>
@@ -28055,7 +28055,7 @@
         <v>46279</v>
       </c>
       <c r="B178" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C178" t="s">
         <v>380</v>
@@ -28067,16 +28067,16 @@
         <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G178" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H178" t="n">
         <v>2</v>
       </c>
       <c r="I178" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J178" t="s">
         <v>148</v>
@@ -28205,7 +28205,7 @@
         <v>46279</v>
       </c>
       <c r="B179" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C179" t="s">
         <v>380</v>
@@ -28217,19 +28217,19 @@
         <v>3</v>
       </c>
       <c r="F179" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G179" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H179" t="n">
         <v>6</v>
       </c>
       <c r="I179" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J179" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K179" t="n">
         <v>20.4815127640212</v>
@@ -28355,7 +28355,7 @@
         <v>46279</v>
       </c>
       <c r="B180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C180" t="s">
         <v>380</v>
@@ -28367,19 +28367,19 @@
         <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G180" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H180" t="n">
         <v>5</v>
       </c>
       <c r="I180" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J180" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K180" t="n">
         <v>43.8447693235878</v>
@@ -28505,7 +28505,7 @@
         <v>46279</v>
       </c>
       <c r="B181" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C181" t="s">
         <v>380</v>
@@ -28517,16 +28517,16 @@
         <v>4</v>
       </c>
       <c r="F181" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G181" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
       </c>
       <c r="I181" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J181" t="s">
         <v>409</v>
@@ -28655,7 +28655,7 @@
         <v>46279</v>
       </c>
       <c r="B182" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C182" t="s">
         <v>380</v>
@@ -28667,19 +28667,19 @@
         <v>4</v>
       </c>
       <c r="F182" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G182" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H182" t="n">
         <v>5</v>
       </c>
       <c r="I182" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="J182" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="K182" t="n">
         <v>3.12481926237755</v>
@@ -28805,7 +28805,7 @@
         <v>46279</v>
       </c>
       <c r="B183" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C183" t="s">
         <v>380</v>
@@ -28817,19 +28817,19 @@
         <v>4</v>
       </c>
       <c r="F183" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G183" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H183" t="n">
         <v>3</v>
       </c>
       <c r="I183" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J183" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="K183" t="n">
         <v>8.77158677556666</v>
@@ -28945,7 +28945,7 @@
         <v>46279</v>
       </c>
       <c r="B184" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C184" t="s">
         <v>380</v>
@@ -28957,19 +28957,19 @@
         <v>4</v>
       </c>
       <c r="F184" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G184" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H184" t="n">
         <v>7</v>
       </c>
       <c r="I184" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="J184" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K184" t="n">
         <v>14.5856486265173</v>
@@ -29095,7 +29095,7 @@
         <v>46279</v>
       </c>
       <c r="B185" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C185" t="s">
         <v>380</v>
@@ -29107,19 +29107,19 @@
         <v>4</v>
       </c>
       <c r="F185" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G185" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H185" t="n">
         <v>4</v>
       </c>
       <c r="I185" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J185" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="K185" t="n">
         <v>16.9849573188785</v>
@@ -29245,7 +29245,7 @@
         <v>46279</v>
       </c>
       <c r="B186" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C186" t="s">
         <v>380</v>
@@ -29257,19 +29257,19 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G186" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H186" t="n">
         <v>8</v>
       </c>
       <c r="I186" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="J186" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K186" t="n">
         <v>17.1619179167534</v>
@@ -29395,7 +29395,7 @@
         <v>46279</v>
       </c>
       <c r="B187" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C187" t="s">
         <v>380</v>
@@ -29407,16 +29407,16 @@
         <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G187" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H187" t="n">
         <v>2</v>
       </c>
       <c r="I187" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J187" t="s">
         <v>396</v>
@@ -29545,7 +29545,7 @@
         <v>46279</v>
       </c>
       <c r="B188" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C188" t="s">
         <v>380</v>
@@ -29557,19 +29557,19 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G188" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H188" t="n">
         <v>6</v>
       </c>
       <c r="I188" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="J188" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K188" t="n">
         <v>56.3848446775082</v>
@@ -29695,7 +29695,7 @@
         <v>46279</v>
       </c>
       <c r="B189" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C189" t="s">
         <v>380</v>
@@ -29707,100 +29707,100 @@
         <v>5</v>
       </c>
       <c r="F189" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G189" t="s">
         <v>179</v>
       </c>
       <c r="H189" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I189" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J189" t="s">
-        <v>446</v>
+        <v>392</v>
       </c>
       <c r="K189" t="n">
-        <v>4.24857233046118</v>
+        <v>3.3403751357152</v>
       </c>
       <c r="L189" t="n">
-        <v>4.0226861349101</v>
+        <v>3.63943374940864</v>
       </c>
       <c r="M189" t="n">
-        <v>5.61530748299668</v>
+        <v>-8.21717427174028</v>
       </c>
       <c r="N189" t="s">
         <v>73</v>
       </c>
       <c r="O189" t="n">
-        <v>0.199673796205851</v>
+        <v>0.173272962700091</v>
       </c>
       <c r="P189" t="n">
-        <v>0.199673796205851</v>
+        <v>0.173272962700091</v>
       </c>
       <c r="Q189" t="n">
-        <v>2.24903306130338</v>
+        <v>1.81364331521896</v>
       </c>
       <c r="R189" t="n">
-        <v>1.58807430909603</v>
+        <v>1.34371873141016</v>
       </c>
       <c r="S189" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
       <c r="T189" t="n">
-        <v>103.44630156152</v>
+        <v>99.7685742575553</v>
       </c>
       <c r="U189" t="n">
-        <v>100.654340687973</v>
+        <v>99.7685742575553</v>
       </c>
       <c r="V189" t="n">
-        <v>99.9310075988004</v>
+        <v>99.7216458335929</v>
       </c>
       <c r="W189" t="n">
-        <v>100.272267270237</v>
+        <v>103.852347364138</v>
       </c>
       <c r="X189" t="n">
-        <v>99.749116442306</v>
+        <v>101.116493473215</v>
       </c>
       <c r="Y189" t="n">
-        <v>100.615299256907</v>
+        <v>99.9163360693094</v>
       </c>
       <c r="Z189" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AA189" t="n">
-        <v>100.615299256907</v>
+        <v>99.8364076817661</v>
       </c>
       <c r="AB189" t="n">
-        <v>100.654340687973</v>
+        <v>99.7685742575553</v>
       </c>
       <c r="AC189" t="n">
-        <v>99.9310075988004</v>
+        <v>99.7216458335929</v>
       </c>
       <c r="AD189" t="n">
-        <v>100.654340687973</v>
+        <v>103.594086552652</v>
       </c>
       <c r="AE189" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AF189" t="n">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="AG189" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="AH189" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="AI189" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="AJ189" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="AK189" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AL189" t="n">
         <v>0</v>
@@ -29845,7 +29845,7 @@
         <v>46279</v>
       </c>
       <c r="B190" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C190" t="s">
         <v>380</v>
@@ -29857,97 +29857,97 @@
         <v>5</v>
       </c>
       <c r="F190" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G190" t="s">
         <v>179</v>
       </c>
       <c r="H190" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I190" t="s">
         <v>447</v>
       </c>
       <c r="J190" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="K190" t="n">
-        <v>4.25444028727672</v>
+        <v>3.89979249032691</v>
       </c>
       <c r="L190" t="n">
-        <v>4.76478155224165</v>
+        <v>3.42083119548486</v>
       </c>
       <c r="M190" t="n">
-        <v>-10.7106959546725</v>
+        <v>14.0013133496392</v>
       </c>
       <c r="N190" t="s">
         <v>73</v>
       </c>
       <c r="O190" t="n">
-        <v>0.174867000909831</v>
+        <v>0.17091366654821</v>
       </c>
       <c r="P190" t="n">
-        <v>0.174867000909831</v>
+        <v>0.17091366654821</v>
       </c>
       <c r="Q190" t="n">
-        <v>2.19646403011347</v>
+        <v>2.03565236242027</v>
       </c>
       <c r="R190" t="n">
-        <v>1.54381248357745</v>
+        <v>1.44616056009878</v>
       </c>
       <c r="S190" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="T190" t="n">
-        <v>99.7685742575553</v>
+        <v>100.759862700425</v>
       </c>
       <c r="U190" t="n">
-        <v>99.7685742575553</v>
+        <v>99.7928729629646</v>
       </c>
       <c r="V190" t="n">
-        <v>99.7216458335929</v>
+        <v>99.7928729629646</v>
       </c>
       <c r="W190" t="n">
-        <v>103.852347364138</v>
+        <v>102.917669964951</v>
       </c>
       <c r="X190" t="n">
-        <v>101.116493473215</v>
+        <v>100.462502810477</v>
       </c>
       <c r="Y190" t="n">
-        <v>99.9163360693094</v>
+        <v>99.5965761094646</v>
       </c>
       <c r="Z190" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AA190" t="n">
-        <v>99.8364076817661</v>
+        <v>99.5965761094646</v>
       </c>
       <c r="AB190" t="n">
-        <v>99.7685742575553</v>
+        <v>99.7928729629646</v>
       </c>
       <c r="AC190" t="n">
-        <v>99.7216458335929</v>
+        <v>99.7928729629646</v>
       </c>
       <c r="AD190" t="n">
-        <v>103.594086552652</v>
+        <v>102.365727910449</v>
       </c>
       <c r="AE190" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AF190" t="n">
         <v>14</v>
       </c>
       <c r="AG190" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH190" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI190" t="n">
         <v>30</v>
       </c>
-      <c r="AI190" t="n">
-        <v>26</v>
-      </c>
       <c r="AJ190" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK190" t="n">
         <v>0</v>
@@ -29962,7 +29962,7 @@
         <v>0</v>
       </c>
       <c r="AO190" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP190" t="s">
         <v>74</v>
@@ -29995,7 +29995,7 @@
         <v>46279</v>
       </c>
       <c r="B191" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C191" t="s">
         <v>380</v>
@@ -30007,100 +30007,100 @@
         <v>5</v>
       </c>
       <c r="F191" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G191" t="s">
         <v>179</v>
       </c>
       <c r="H191" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I191" t="s">
         <v>448</v>
       </c>
       <c r="J191" t="s">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="K191" t="n">
-        <v>4.84471451413969</v>
+        <v>5.17999352794852</v>
       </c>
       <c r="L191" t="n">
-        <v>4.34533999565501</v>
+        <v>6.80558012929568</v>
       </c>
       <c r="M191" t="n">
-        <v>11.4921851681115</v>
+        <v>-23.8860842200589</v>
       </c>
       <c r="N191" t="s">
         <v>73</v>
       </c>
       <c r="O191" t="n">
-        <v>0.173010412248061</v>
+        <v>0.167573150703366</v>
       </c>
       <c r="P191" t="n">
-        <v>0.173010412248061</v>
+        <v>0.167573150703366</v>
       </c>
       <c r="Q191" t="n">
-        <v>2.44548220633661</v>
+        <v>2.51128798434913</v>
       </c>
       <c r="R191" t="n">
-        <v>1.67310372152379</v>
+        <v>1.65685055360186</v>
       </c>
       <c r="S191" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="T191" t="n">
-        <v>100.759862700425</v>
+        <v>103.169017903056</v>
       </c>
       <c r="U191" t="n">
-        <v>99.7928729629646</v>
+        <v>100.561605011851</v>
       </c>
       <c r="V191" t="n">
-        <v>99.7928729629646</v>
+        <v>99.8736386412305</v>
       </c>
       <c r="W191" t="n">
-        <v>102.917669964951</v>
+        <v>108.511104527305</v>
       </c>
       <c r="X191" t="n">
-        <v>100.462502810477</v>
+        <v>97.2409694181732</v>
       </c>
       <c r="Y191" t="n">
-        <v>99.5965761094646</v>
+        <v>96.7071098830217</v>
       </c>
       <c r="Z191" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA191" t="n">
+        <v>96.8456156496575</v>
+      </c>
+      <c r="AB191" t="n">
+        <v>100.561605011851</v>
+      </c>
+      <c r="AC191" t="n">
+        <v>98.2906900985247</v>
+      </c>
+      <c r="AD191" t="n">
+        <v>100.561605011851</v>
+      </c>
+      <c r="AE191" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF191" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG191" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH191" t="n">
         <v>30</v>
       </c>
-      <c r="AA191" t="n">
-        <v>99.5965761094646</v>
-      </c>
-      <c r="AB191" t="n">
-        <v>99.7928729629646</v>
-      </c>
-      <c r="AC191" t="n">
-        <v>99.7928729629646</v>
-      </c>
-      <c r="AD191" t="n">
-        <v>102.365727910449</v>
-      </c>
-      <c r="AE191" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF191" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG191" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH191" t="n">
-        <v>32</v>
-      </c>
       <c r="AI191" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="AJ191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL191" t="n">
         <v>0</v>
@@ -30112,7 +30112,7 @@
         <v>0</v>
       </c>
       <c r="AO191" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP191" t="s">
         <v>74</v>
@@ -30145,7 +30145,7 @@
         <v>46279</v>
       </c>
       <c r="B192" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C192" t="s">
         <v>380</v>
@@ -30157,100 +30157,100 @@
         <v>5</v>
       </c>
       <c r="F192" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G192" t="s">
         <v>179</v>
       </c>
       <c r="H192" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I192" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J192" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="K192" t="n">
-        <v>6.4656800321312</v>
+        <v>10.3047314458338</v>
       </c>
       <c r="L192" t="n">
-        <v>8.56599571734475</v>
+        <v>7.68405685747215</v>
       </c>
       <c r="M192" t="n">
-        <v>-24.5192240869413</v>
+        <v>34.1053513394192</v>
       </c>
       <c r="N192" t="s">
         <v>73</v>
       </c>
       <c r="O192" t="n">
-        <v>0.169628915407523</v>
+        <v>0.179077343424858</v>
       </c>
       <c r="P192" t="n">
-        <v>0.169628915407523</v>
+        <v>0.179077343424858</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.11353242426911</v>
+        <v>4.75103044952381</v>
       </c>
       <c r="R192" t="n">
-        <v>1.99901823261552</v>
+        <v>2.87025272644265</v>
       </c>
       <c r="S192" t="n">
-        <v>-0.5</v>
+        <v>-1.8</v>
       </c>
       <c r="T192" t="n">
-        <v>103.169017903056</v>
+        <v>96.4683907111822</v>
       </c>
       <c r="U192" t="n">
-        <v>100.561605011851</v>
+        <v>96.8090980257189</v>
       </c>
       <c r="V192" t="n">
-        <v>99.8736386412305</v>
+        <v>96.8090980257189</v>
       </c>
       <c r="W192" t="n">
-        <v>108.511104527305</v>
+        <v>105.205777924253</v>
       </c>
       <c r="X192" t="n">
-        <v>97.2409694181732</v>
+        <v>100.530995723517</v>
       </c>
       <c r="Y192" t="n">
-        <v>96.7071098830217</v>
+        <v>97.5841804864605</v>
       </c>
       <c r="Z192" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AA192" t="n">
-        <v>96.8456156496575</v>
+        <v>97.5264222541914</v>
       </c>
       <c r="AB192" t="n">
-        <v>100.561605011851</v>
+        <v>96.8090980257189</v>
       </c>
       <c r="AC192" t="n">
-        <v>98.2906900985247</v>
+        <v>96.9463430698203</v>
       </c>
       <c r="AD192" t="n">
-        <v>100.561605011851</v>
+        <v>98.8677760787076</v>
       </c>
       <c r="AE192" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AF192" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="AG192" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AH192" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI192" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AJ192" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="AK192" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AL192" t="n">
         <v>0</v>
@@ -30295,7 +30295,7 @@
         <v>46279</v>
       </c>
       <c r="B193" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C193" t="s">
         <v>380</v>
@@ -30307,97 +30307,97 @@
         <v>5</v>
       </c>
       <c r="F193" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G193" t="s">
         <v>179</v>
       </c>
       <c r="H193" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I193" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J193" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K193" t="n">
-        <v>12.6605697013669</v>
+        <v>14.4286224042193</v>
       </c>
       <c r="L193" t="n">
-        <v>9.65235015925104</v>
+        <v>15.3222000919258</v>
       </c>
       <c r="M193" t="n">
-        <v>31.1656694223082</v>
+        <v>-5.83191501445928</v>
       </c>
       <c r="N193" t="s">
         <v>73</v>
       </c>
       <c r="O193" t="n">
-        <v>0.181274240006331</v>
+        <v>0.178310924637809</v>
       </c>
       <c r="P193" t="n">
-        <v>0.181274240006331</v>
+        <v>0.178310924637809</v>
       </c>
       <c r="Q193" t="n">
-        <v>5.82695045736486</v>
+        <v>6.42231470752579</v>
       </c>
       <c r="R193" t="n">
-        <v>3.53930907616971</v>
+        <v>3.73493825523175</v>
       </c>
       <c r="S193" t="n">
-        <v>-1.8</v>
+        <v>-2</v>
       </c>
       <c r="T193" t="n">
-        <v>96.4683907111822</v>
+        <v>86.6835668116686</v>
       </c>
       <c r="U193" t="n">
-        <v>96.8090980257189</v>
+        <v>97.299721666247</v>
       </c>
       <c r="V193" t="n">
-        <v>96.8090980257189</v>
+        <v>95.8786044434745</v>
       </c>
       <c r="W193" t="n">
-        <v>105.205777924253</v>
+        <v>105.965956151524</v>
       </c>
       <c r="X193" t="n">
-        <v>100.530995723517</v>
+        <v>99.4539571852732</v>
       </c>
       <c r="Y193" t="n">
-        <v>97.5841804864605</v>
+        <v>95.2111188251395</v>
       </c>
       <c r="Z193" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AA193" t="n">
-        <v>97.5264222541914</v>
+        <v>92.5545166239818</v>
       </c>
       <c r="AB193" t="n">
-        <v>96.8090980257189</v>
+        <v>95.8786044434745</v>
       </c>
       <c r="AC193" t="n">
-        <v>96.9463430698203</v>
+        <v>95.8786044434745</v>
       </c>
       <c r="AD193" t="n">
-        <v>98.8677760787076</v>
+        <v>95.8786044434745</v>
       </c>
       <c r="AE193" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AF193" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="AG193" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="AH193" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="AI193" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AJ193" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="AK193" t="n">
         <v>11</v>
@@ -30445,7 +30445,7 @@
         <v>46279</v>
       </c>
       <c r="B194" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C194" t="s">
         <v>380</v>
@@ -30457,100 +30457,100 @@
         <v>5</v>
       </c>
       <c r="F194" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G194" t="s">
         <v>179</v>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I194" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="J194" t="s">
-        <v>454</v>
+        <v>392</v>
       </c>
       <c r="K194" t="n">
-        <v>16.9759445660103</v>
+        <v>20.8568832345251</v>
       </c>
       <c r="L194" t="n">
-        <v>18.550918196995</v>
+        <v>22.5293985131786</v>
       </c>
       <c r="M194" t="n">
-        <v>-8.49000364434678</v>
+        <v>-7.423701425829</v>
       </c>
       <c r="N194" t="s">
         <v>73</v>
       </c>
       <c r="O194" t="n">
-        <v>0.180498418897464</v>
+        <v>0.174962065921312</v>
       </c>
       <c r="P194" t="n">
-        <v>0.180498418897464</v>
+        <v>0.174962065921312</v>
       </c>
       <c r="Q194" t="n">
-        <v>7.73511393363466</v>
+        <v>9.22821131357009</v>
       </c>
       <c r="R194" t="n">
-        <v>4.56594050553924</v>
+        <v>5.26081919682627</v>
       </c>
       <c r="S194" t="n">
-        <v>-1.9</v>
+        <v>-2.5</v>
       </c>
       <c r="T194" t="n">
-        <v>86.6835668116686</v>
+        <v>89.8556898288532</v>
       </c>
       <c r="U194" t="n">
-        <v>97.299721666247</v>
+        <v>91.0404664803772</v>
       </c>
       <c r="V194" t="n">
-        <v>95.8786044434745</v>
+        <v>94.8849027464111</v>
       </c>
       <c r="W194" t="n">
-        <v>105.965956151524</v>
+        <v>104.114755956382</v>
       </c>
       <c r="X194" t="n">
-        <v>99.4539571852732</v>
+        <v>99.6588187865577</v>
       </c>
       <c r="Y194" t="n">
-        <v>95.2111188251395</v>
+        <v>95.3372481955984</v>
       </c>
       <c r="Z194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA194" t="n">
+        <v>95.1709152038208</v>
+      </c>
+      <c r="AB194" t="n">
+        <v>91.0404664803772</v>
+      </c>
+      <c r="AC194" t="n">
+        <v>94.8849027464111</v>
+      </c>
+      <c r="AD194" t="n">
+        <v>100.985996563119</v>
+      </c>
+      <c r="AE194" t="n">
         <v>9</v>
-      </c>
-      <c r="AA194" t="n">
-        <v>92.5545166239818</v>
-      </c>
-      <c r="AB194" t="n">
-        <v>95.8786044434745</v>
-      </c>
-      <c r="AC194" t="n">
-        <v>95.8786044434745</v>
-      </c>
-      <c r="AD194" t="n">
-        <v>95.8786044434745</v>
-      </c>
-      <c r="AE194" t="n">
-        <v>3</v>
       </c>
       <c r="AF194" t="n">
         <v>14</v>
       </c>
       <c r="AG194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH194" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI194" t="n">
         <v>9</v>
       </c>
-      <c r="AH194" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI194" t="n">
-        <v>3</v>
-      </c>
       <c r="AJ194" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AK194" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AL194" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="AO194" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP194" t="s">
         <v>74</v>
@@ -30595,7 +30595,7 @@
         <v>46279</v>
       </c>
       <c r="B195" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C195" t="s">
         <v>380</v>
@@ -30607,7 +30607,7 @@
         <v>5</v>
       </c>
       <c r="F195" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G195" t="s">
         <v>179</v>
@@ -30622,31 +30622,31 @@
         <v>456</v>
       </c>
       <c r="K195" t="n">
-        <v>60.1179261987537</v>
+        <v>50.0683280530486</v>
       </c>
       <c r="L195" t="n">
-        <v>50.2805429864253</v>
+        <v>40.4726831242412</v>
       </c>
       <c r="M195" t="n">
-        <v>19.5649900101203</v>
+        <v>23.7089419037309</v>
       </c>
       <c r="N195" t="s">
         <v>73</v>
       </c>
       <c r="O195" t="n">
-        <v>0.173010412248061</v>
+        <v>0.17091366654821</v>
       </c>
       <c r="P195" t="n">
-        <v>0.173010412248061</v>
+        <v>0.17091366654821</v>
       </c>
       <c r="Q195" t="n">
-        <v>26.4878391194323</v>
+        <v>21.5444816752476</v>
       </c>
       <c r="R195" t="n">
-        <v>14.8071630204557</v>
+        <v>11.7753922779563</v>
       </c>
       <c r="S195" t="n">
-        <v>-3.8</v>
+        <v>-3.9</v>
       </c>
       <c r="T195" t="n">
         <v>94.2173589774821</v>
@@ -30745,7 +30745,7 @@
         <v>46279</v>
       </c>
       <c r="B196" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C196" t="s">
         <v>380</v>
@@ -30757,7 +30757,7 @@
         <v>5</v>
       </c>
       <c r="F196" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="G196" t="s">
         <v>179</v>
@@ -30772,31 +30772,31 @@
         <v>458</v>
       </c>
       <c r="K196" t="n">
-        <v>71.5371992531221</v>
+        <v>59.2062914205148</v>
       </c>
       <c r="L196" t="n">
-        <v>57.9085118702953</v>
+        <v>46.5803446669772</v>
       </c>
       <c r="M196" t="n">
-        <v>23.5348603213162</v>
+        <v>27.1057392207075</v>
       </c>
       <c r="N196" t="s">
         <v>73</v>
       </c>
       <c r="O196" t="n">
-        <v>0.183892879955905</v>
+        <v>0.181664247584762</v>
       </c>
       <c r="P196" t="n">
-        <v>0.183892879955905</v>
+        <v>0.181664247584762</v>
       </c>
       <c r="Q196" t="n">
-        <v>31.9068316426556</v>
+        <v>26.1698588116495</v>
       </c>
       <c r="R196" t="n">
-        <v>18.0071444943159</v>
+        <v>14.3667833914966</v>
       </c>
       <c r="S196" t="n">
-        <v>-4</v>
+        <v>-4.1</v>
       </c>
       <c r="T196" t="n">
         <v>95.4787107332003</v>
@@ -30919,7 +30919,7 @@
         <v>461</v>
       </c>
       <c r="J197" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K197" t="n">
         <v>3.20260244889026</v>
@@ -31959,7 +31959,7 @@
         <v>472</v>
       </c>
       <c r="J204" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K204" t="n">
         <v>29.396567491658</v>
@@ -32109,7 +32109,7 @@
         <v>475</v>
       </c>
       <c r="J205" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K205" t="n">
         <v>2.56161643990246</v>
@@ -32249,7 +32249,7 @@
         <v>476</v>
       </c>
       <c r="J206" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K206" t="n">
         <v>5.3011438777363</v>
@@ -33899,7 +33899,7 @@
         <v>493</v>
       </c>
       <c r="J217" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K217" t="n">
         <v>27.7918292796328</v>
@@ -34339,7 +34339,7 @@
         <v>496</v>
       </c>
       <c r="J220" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K220" t="n">
         <v>109.672454234447</v>
@@ -34489,7 +34489,7 @@
         <v>499</v>
       </c>
       <c r="J221" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="K221" t="n">
         <v>2.15037082481545</v>
@@ -34629,7 +34629,7 @@
         <v>500</v>
       </c>
       <c r="J222" t="s">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="K222" t="n">
         <v>4.50786987906567</v>
@@ -34776,7 +34776,7 @@
         <v>2</v>
       </c>
       <c r="I223" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="J223" t="s">
         <v>471</v>
@@ -34916,10 +34916,10 @@
         <v>5</v>
       </c>
       <c r="I224" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="J224" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K224" t="n">
         <v>11.4409735624715</v>
@@ -35066,7 +35066,7 @@
         <v>8</v>
       </c>
       <c r="I225" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="J225" t="s">
         <v>479</v>
@@ -35216,10 +35216,10 @@
         <v>6</v>
       </c>
       <c r="I226" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="J226" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K226" t="n">
         <v>25.9292985941346</v>
@@ -35364,10 +35364,10 @@
         <v>4</v>
       </c>
       <c r="I227" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="J227" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K227" t="n">
         <v>72.9890220190166</v>
@@ -35514,7 +35514,7 @@
         <v>7</v>
       </c>
       <c r="I228" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="J228" t="s">
         <v>466</v>
@@ -35643,7 +35643,7 @@
         <v>46279</v>
       </c>
       <c r="B229" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C229" t="s">
         <v>380</v>
@@ -35655,7 +35655,7 @@
         <v>10</v>
       </c>
       <c r="F229" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G229" t="s">
         <v>151</v>
@@ -35664,10 +35664,10 @@
         <v>7</v>
       </c>
       <c r="I229" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="J229" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="K229" t="n">
         <v>2.55192463833627</v>
@@ -35793,7 +35793,7 @@
         <v>46279</v>
       </c>
       <c r="B230" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C230" t="s">
         <v>380</v>
@@ -35805,7 +35805,7 @@
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G230" t="s">
         <v>151</v>
@@ -35814,10 +35814,10 @@
         <v>4</v>
       </c>
       <c r="I230" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J230" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K230" t="n">
         <v>8.09520976587183</v>
@@ -35943,7 +35943,7 @@
         <v>46279</v>
       </c>
       <c r="B231" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C231" t="s">
         <v>380</v>
@@ -35955,7 +35955,7 @@
         <v>10</v>
       </c>
       <c r="F231" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G231" t="s">
         <v>151</v>
@@ -35964,10 +35964,10 @@
         <v>5</v>
       </c>
       <c r="I231" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="J231" t="s">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="K231" t="n">
         <v>8.12317602110027</v>
@@ -36093,7 +36093,7 @@
         <v>46279</v>
       </c>
       <c r="B232" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C232" t="s">
         <v>380</v>
@@ -36105,7 +36105,7 @@
         <v>10</v>
       </c>
       <c r="F232" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G232" t="s">
         <v>151</v>
@@ -36243,7 +36243,7 @@
         <v>46279</v>
       </c>
       <c r="B233" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C233" t="s">
         <v>380</v>
@@ -36255,7 +36255,7 @@
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G233" t="s">
         <v>151</v>
@@ -36393,7 +36393,7 @@
         <v>46279</v>
       </c>
       <c r="B234" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C234" t="s">
         <v>380</v>
@@ -36405,7 +36405,7 @@
         <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G234" t="s">
         <v>151</v>
@@ -36417,7 +36417,7 @@
         <v>517</v>
       </c>
       <c r="J234" t="s">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="K234" t="n">
         <v>13.4271507620652</v>
@@ -36543,7 +36543,7 @@
         <v>46279</v>
       </c>
       <c r="B235" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C235" t="s">
         <v>380</v>
@@ -36555,7 +36555,7 @@
         <v>10</v>
       </c>
       <c r="F235" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G235" t="s">
         <v>151</v>
@@ -36567,7 +36567,7 @@
         <v>518</v>
       </c>
       <c r="J235" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K235" t="n">
         <v>26.0786078797458</v>
@@ -36693,7 +36693,7 @@
         <v>46279</v>
       </c>
       <c r="B236" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C236" t="s">
         <v>380</v>
@@ -36705,7 +36705,7 @@
         <v>10</v>
       </c>
       <c r="F236" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="G236" t="s">
         <v>151</v>
@@ -36717,7 +36717,7 @@
         <v>519</v>
       </c>
       <c r="J236" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="K236" t="n">
         <v>51.6522494166071</v>
@@ -37297,7 +37297,7 @@
         <v>525</v>
       </c>
       <c r="J240" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="K240" t="n">
         <v>9.36698639361317</v>
@@ -37597,7 +37597,7 @@
         <v>527</v>
       </c>
       <c r="J242" t="s">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="K242" t="n">
         <v>11.6157367981358</v>
@@ -37747,7 +37747,7 @@
         <v>528</v>
       </c>
       <c r="J243" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K243" t="n">
         <v>18.691633541168</v>
@@ -38171,7 +38171,7 @@
         <v>534</v>
       </c>
       <c r="J246" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="K246" t="n">
         <v>4.71232818807317</v>
@@ -38471,7 +38471,7 @@
         <v>536</v>
       </c>
       <c r="J248" t="s">
-        <v>513</v>
+        <v>404</v>
       </c>
       <c r="K248" t="n">
         <v>7.84690092753126</v>
@@ -38771,7 +38771,7 @@
         <v>538</v>
       </c>
       <c r="J250" t="s">
-        <v>446</v>
+        <v>501</v>
       </c>
       <c r="K250" t="n">
         <v>13.2587179497298</v>
@@ -38921,7 +38921,7 @@
         <v>539</v>
       </c>
       <c r="J251" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="K251" t="n">
         <v>30.3309240284919</v>

--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -579,13 +579,13 @@
     <t xml:space="preserve">KING OF ASGARD</t>
   </si>
   <si>
+    <t xml:space="preserve">COOL GENT</t>
+  </si>
+  <si>
     <t xml:space="preserve">HARA'S USAIN</t>
   </si>
   <si>
     <t xml:space="preserve">Peter Carleton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COOL GENT</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-20T14:47:00</t>
@@ -2257,13 +2257,13 @@
         <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>2.22346362237421</v>
+        <v>2.20913004651115</v>
       </c>
       <c r="L2" t="n">
-        <v>1.96831145314622</v>
+        <v>1.95898058727889</v>
       </c>
       <c r="M2" t="n">
-        <v>12.9629977420566</v>
+        <v>12.769368969589</v>
       </c>
       <c r="N2" t="s">
         <v>56</v>
@@ -2275,10 +2275,10 @@
         <v>0.150252541786384</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.18557804458908</v>
+        <v>1.18447688465199</v>
       </c>
       <c r="R2" t="n">
-        <v>1.02816666283624</v>
+        <v>1.02807954658798</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2405,7 +2405,7 @@
         <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>2.30920792133619</v>
+        <v>2.32791528540652</v>
       </c>
       <c r="L3"/>
       <c r="M3"/>
@@ -2419,10 +2419,10 @@
         <v>0.20539451062863</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.23495578771059</v>
+        <v>1.23829877404574</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0535196208309</v>
+        <v>1.05409260991287</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2531,13 +2531,13 @@
         <v>69</v>
       </c>
       <c r="K4" t="n">
-        <v>12.2301608296861</v>
+        <v>12.1579220565681</v>
       </c>
       <c r="L4" t="n">
-        <v>14.9192898702074</v>
+        <v>14.839590443686</v>
       </c>
       <c r="M4" t="n">
-        <v>-18.024510978175</v>
+        <v>-18.071040419171</v>
       </c>
       <c r="N4" t="s">
         <v>70</v>
@@ -2549,10 +2549,10 @@
         <v>0.146373524077069</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.08842104429498</v>
+        <v>4.06931843184608</v>
       </c>
       <c r="R4" t="n">
-        <v>1.31497072166514</v>
+        <v>1.31400851947404</v>
       </c>
       <c r="S4" t="n">
         <v>-2.5</v>
@@ -2681,13 +2681,13 @@
         <v>74</v>
       </c>
       <c r="K5" t="n">
-        <v>28.2188955160274</v>
+        <v>28.1584417661183</v>
       </c>
       <c r="L5" t="n">
-        <v>35.6266476665479</v>
+        <v>35.5001774937877</v>
       </c>
       <c r="M5" t="n">
-        <v>-20.792728577368</v>
+        <v>-20.6808423111522</v>
       </c>
       <c r="N5" t="s">
         <v>56</v>
@@ -2699,10 +2699,10 @@
         <v>0.172638927724989</v>
       </c>
       <c r="Q5" t="n">
-        <v>9.78561685674882</v>
+        <v>9.76138279888378</v>
       </c>
       <c r="R5" t="n">
-        <v>3.14739952407278</v>
+        <v>3.14862154898813</v>
       </c>
       <c r="S5" t="n">
         <v>-4</v>
@@ -2829,7 +2829,7 @@
         <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>3.66851302457671</v>
+        <v>3.6503169338795</v>
       </c>
       <c r="L6"/>
       <c r="M6"/>
@@ -2843,10 +2843,10 @@
         <v>0.229650382268515</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91826994404292</v>
+        <v>1.910737559399</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36043470939885</v>
+        <v>1.35717346654143</v>
       </c>
       <c r="S6" t="n">
         <v>0.1</v>
@@ -2955,7 +2955,7 @@
         <v>80</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7558498805508</v>
+        <v>3.751249773357</v>
       </c>
       <c r="L7"/>
       <c r="M7"/>
@@ -2969,10 +2969,10 @@
         <v>0.242626125632326</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.96416661494154</v>
+        <v>1.96126439094573</v>
       </c>
       <c r="R7" t="n">
-        <v>1.38110237586697</v>
+        <v>1.37958317235305</v>
       </c>
       <c r="S7" t="n">
         <v>-0.1</v>
@@ -3081,7 +3081,7 @@
         <v>82</v>
       </c>
       <c r="K8" t="n">
-        <v>4.04867112845138</v>
+        <v>4.06255674665369</v>
       </c>
       <c r="L8"/>
       <c r="M8"/>
@@ -3095,10 +3095,10 @@
         <v>0.242626125632326</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.07620050293602</v>
+        <v>2.0812501644452</v>
       </c>
       <c r="R8" t="n">
-        <v>1.42568285067118</v>
+        <v>1.42698904910227</v>
       </c>
       <c r="S8" t="n">
         <v>-0.2</v>
@@ -3207,13 +3207,13 @@
         <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>7.24876462671261</v>
+        <v>7.28919797849054</v>
       </c>
       <c r="L9" t="n">
-        <v>4.37533359583497</v>
+        <v>4.39726509255595</v>
       </c>
       <c r="M9" t="n">
-        <v>65.6734159336547</v>
+        <v>65.7666259609931</v>
       </c>
       <c r="N9" t="s">
         <v>70</v>
@@ -3225,13 +3225,13 @@
         <v>0.197991347147252</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.33358742923221</v>
+        <v>3.3503160564631</v>
       </c>
       <c r="R9" t="n">
-        <v>2.06234806141667</v>
+        <v>2.07082388749285</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="T9" t="n">
         <v>97.9871660917011</v>
@@ -3357,13 +3357,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="n">
-        <v>19.8919099062881</v>
+        <v>19.936323139366</v>
       </c>
       <c r="L10" t="n">
-        <v>20.62425242318</v>
+        <v>20.6498038405947</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.55088030278804</v>
+        <v>-3.45514517588803</v>
       </c>
       <c r="N10" t="s">
         <v>56</v>
@@ -3375,10 +3375,10 @@
         <v>0.19032237334576</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.15845405686942</v>
+        <v>8.16859296419396</v>
       </c>
       <c r="R10" t="n">
-        <v>4.44915661527554</v>
+        <v>4.45162934234342</v>
       </c>
       <c r="S10" t="n">
         <v>-2.7</v>
@@ -3505,13 +3505,13 @@
         <v>69</v>
       </c>
       <c r="K11" t="n">
-        <v>50.5915163844657</v>
+        <v>50.3944029030591</v>
       </c>
       <c r="L11" t="n">
-        <v>49.2888122227698</v>
+        <v>49.0952380952381</v>
       </c>
       <c r="M11" t="n">
-        <v>2.64300173395953</v>
+        <v>2.64621347858793</v>
       </c>
       <c r="N11" t="s">
         <v>70</v>
@@ -3523,10 +3523,10 @@
         <v>0.19032237334576</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.276199178281</v>
+        <v>20.1981826916551</v>
       </c>
       <c r="R11" t="n">
-        <v>10.2380907421063</v>
+        <v>10.1920006743375</v>
       </c>
       <c r="S11" t="n">
         <v>-4.2</v>
@@ -3655,13 +3655,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="n">
-        <v>162.031240446844</v>
+        <v>163.119504293805</v>
       </c>
       <c r="L12" t="n">
-        <v>195.708414872798</v>
+        <v>196.477406679764</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.2078315834517</v>
+        <v>-16.9779838555832</v>
       </c>
       <c r="N12" t="s">
         <v>56</v>
@@ -3673,10 +3673,10 @@
         <v>0.180143855816001</v>
       </c>
       <c r="Q12" t="n">
-        <v>62.2749350798621</v>
+        <v>62.9823160781814</v>
       </c>
       <c r="R12" t="n">
-        <v>31.1110561679459</v>
+        <v>31.3587142618979</v>
       </c>
       <c r="S12" t="n">
         <v>-6</v>
@@ -3803,13 +3803,13 @@
         <v>92</v>
       </c>
       <c r="K13" t="n">
-        <v>1.87466902441366</v>
+        <v>1.86872654658372</v>
       </c>
       <c r="L13" t="n">
-        <v>1.64023880205344</v>
+        <v>1.63669541593702</v>
       </c>
       <c r="M13" t="n">
-        <v>14.2924446164024</v>
+        <v>14.1768057994991</v>
       </c>
       <c r="N13" t="s">
         <v>70</v>
@@ -3821,10 +3821,10 @@
         <v>0.193157371877079</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.25086290694439</v>
+        <v>1.24872797092526</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08074976635722</v>
+        <v>1.08012400201133</v>
       </c>
       <c r="S13" t="n">
         <v>1.3</v>
@@ -3951,13 +3951,13 @@
         <v>95</v>
       </c>
       <c r="K14" t="n">
-        <v>5.82017804511116</v>
+        <v>5.87772328823145</v>
       </c>
       <c r="L14" t="n">
-        <v>7.25898236190753</v>
+        <v>7.32920483693661</v>
       </c>
       <c r="M14" t="n">
-        <v>-19.8210196011314</v>
+        <v>-19.8040794465206</v>
       </c>
       <c r="N14" t="s">
         <v>70</v>
@@ -3969,10 +3969,10 @@
         <v>0.169518561320802</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3203172537179</v>
+        <v>2.33487769083767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45692143257537</v>
+        <v>1.46254153673353</v>
       </c>
       <c r="S14" t="n">
         <v>-1.3</v>
@@ -4101,13 +4101,13 @@
         <v>97</v>
       </c>
       <c r="K15" t="n">
-        <v>6.25399307792289</v>
+        <v>6.25436260744786</v>
       </c>
       <c r="L15" t="n">
         <v>9.85581945402582</v>
       </c>
       <c r="M15" t="n">
-        <v>-36.5451740761311</v>
+        <v>-36.541424722496</v>
       </c>
       <c r="N15" t="s">
         <v>70</v>
@@ -4119,10 +4119,10 @@
         <v>0.170935792455123</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52358855124991</v>
+        <v>2.51971234639542</v>
       </c>
       <c r="R15" t="n">
-        <v>1.54168792242153</v>
+        <v>1.54048281847776</v>
       </c>
       <c r="S15" t="n">
         <v>-1.3</v>
@@ -4251,13 +4251,13 @@
         <v>99</v>
       </c>
       <c r="K16" t="n">
-        <v>21.10876502284</v>
+        <v>21.2558581624038</v>
       </c>
       <c r="L16" t="n">
-        <v>23.2953645469369</v>
+        <v>23.4923655156213</v>
       </c>
       <c r="M16" t="n">
-        <v>-9.38641470791828</v>
+        <v>-9.52014539246965</v>
       </c>
       <c r="N16" t="s">
         <v>70</v>
@@ -4269,10 +4269,10 @@
         <v>0.177032637104068</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.72116353692483</v>
+        <v>7.75782673795824</v>
       </c>
       <c r="R16" t="n">
-        <v>3.93518301696403</v>
+        <v>3.95042754215488</v>
       </c>
       <c r="S16" t="n">
         <v>-3.1</v>
@@ -4401,13 +4401,13 @@
         <v>101</v>
       </c>
       <c r="K17" t="n">
-        <v>26.5468869883447</v>
+        <v>26.583952656737</v>
       </c>
       <c r="L17" t="n">
-        <v>18.5507327026526</v>
+        <v>18.564507146835</v>
       </c>
       <c r="M17" t="n">
-        <v>43.1042504566342</v>
+        <v>43.1977291208037</v>
       </c>
       <c r="N17" t="s">
         <v>70</v>
@@ -4419,10 +4419,10 @@
         <v>0.187806814639252</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.58383406570281</v>
+        <v>9.58690692937047</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97219885700326</v>
+        <v>4.97299878884786</v>
       </c>
       <c r="S17" t="n">
         <v>-3.8</v>
@@ -4551,13 +4551,13 @@
         <v>103</v>
       </c>
       <c r="K18" t="n">
-        <v>37.3370657202629</v>
+        <v>37.044557613161</v>
       </c>
       <c r="L18" t="n">
-        <v>38.8678585308978</v>
+        <v>38.5680678750482</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.93845420996877</v>
+        <v>-3.95018559608192</v>
       </c>
       <c r="N18" t="s">
         <v>70</v>
@@ -4569,10 +4569,10 @@
         <v>0.160296137006047</v>
       </c>
       <c r="Q18" t="n">
-        <v>13.2036018244395</v>
+        <v>13.0595624597519</v>
       </c>
       <c r="R18" t="n">
-        <v>6.39063015557783</v>
+        <v>6.32694984945757</v>
       </c>
       <c r="S18" t="n">
         <v>-3.9</v>
@@ -4701,13 +4701,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="n">
-        <v>43.4165504717502</v>
+        <v>43.1092484249099</v>
       </c>
       <c r="L19" t="n">
-        <v>35.0287215411559</v>
+        <v>34.7850434782609</v>
       </c>
       <c r="M19" t="n">
-        <v>23.9455754065683</v>
+        <v>23.9304140926294</v>
       </c>
       <c r="N19" t="s">
         <v>70</v>
@@ -4719,10 +4719,10 @@
         <v>0.18305133845553</v>
       </c>
       <c r="Q19" t="n">
-        <v>15.6932216287972</v>
+        <v>15.565859100951</v>
       </c>
       <c r="R19" t="n">
-        <v>7.81355154061073</v>
+        <v>7.75104473109264</v>
       </c>
       <c r="S19" t="n">
         <v>-4.3</v>
@@ -4851,13 +4851,13 @@
         <v>108</v>
       </c>
       <c r="K20" t="n">
-        <v>2.14045397546509</v>
+        <v>2.14928621478452</v>
       </c>
       <c r="L20" t="n">
-        <v>2.43317680835016</v>
+        <v>2.44304385000611</v>
       </c>
       <c r="M20" t="n">
-        <v>-12.0304793256499</v>
+        <v>-12.024247342955</v>
       </c>
       <c r="N20" t="s">
         <v>70</v>
@@ -4869,10 +4869,10 @@
         <v>0.191187564064103</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.34693233189108</v>
+        <v>1.35041807682331</v>
       </c>
       <c r="R20" t="n">
-        <v>1.12524435579541</v>
+        <v>1.12679994961385</v>
       </c>
       <c r="S20" t="n">
         <v>1.3</v>
@@ -5001,13 +5001,13 @@
         <v>69</v>
       </c>
       <c r="K21" t="n">
-        <v>5.11630331512637</v>
+        <v>5.09045989097056</v>
       </c>
       <c r="L21" t="n">
-        <v>4.89577519949087</v>
+        <v>4.87667625688789</v>
       </c>
       <c r="M21" t="n">
-        <v>4.50445755063342</v>
+        <v>4.38379795625592</v>
       </c>
       <c r="N21" t="s">
         <v>70</v>
@@ -5019,10 +5019,10 @@
         <v>0.16805555791033</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22610372400561</v>
+        <v>2.22119076544419</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44305427591691</v>
+        <v>1.44237111466447</v>
       </c>
       <c r="S21" t="n">
         <v>-1.3</v>
@@ -5151,13 +5151,13 @@
         <v>112</v>
       </c>
       <c r="K22" t="n">
-        <v>5.95896024125622</v>
+        <v>5.96568767060091</v>
       </c>
       <c r="L22" t="n">
-        <v>4.80267012438169</v>
+        <v>4.80636324313933</v>
       </c>
       <c r="M22" t="n">
-        <v>24.0759845446055</v>
+        <v>24.1206161252257</v>
       </c>
       <c r="N22" t="s">
         <v>70</v>
@@ -5169,13 +5169,13 @@
         <v>0.169752349452912</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.56859705955738</v>
+        <v>2.57674488825902</v>
       </c>
       <c r="R22" t="n">
-        <v>1.58957142151242</v>
+        <v>1.59416771372276</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="T22" t="n">
         <v>101.058812072944</v>
@@ -5299,13 +5299,13 @@
         <v>95</v>
       </c>
       <c r="K23" t="n">
-        <v>14.5529213647611</v>
+        <v>14.519123258738</v>
       </c>
       <c r="L23" t="n">
-        <v>14.9642376178363</v>
+        <v>14.932955054502</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.74866159960527</v>
+        <v>-2.77126526031588</v>
       </c>
       <c r="N23" t="s">
         <v>56</v>
@@ -5317,10 +5317,10 @@
         <v>0.207356801467463</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.11940738618514</v>
+        <v>6.11446667301987</v>
       </c>
       <c r="R23" t="n">
-        <v>3.35195744728004</v>
+        <v>3.35337334260892</v>
       </c>
       <c r="S23" t="n">
         <v>-2.8</v>
@@ -5447,13 +5447,13 @@
         <v>84</v>
       </c>
       <c r="K24" t="n">
-        <v>14.9396332229458</v>
+        <v>14.8153744766534</v>
       </c>
       <c r="L24" t="n">
-        <v>13.5161508311934</v>
+        <v>13.4218225741511</v>
       </c>
       <c r="M24" t="n">
-        <v>10.5317143137172</v>
+        <v>10.3827322616092</v>
       </c>
       <c r="N24" t="s">
         <v>70</v>
@@ -5465,10 +5465,10 @@
         <v>0.178061500040455</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.95116606204456</v>
+        <v>5.91428311719978</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1613717838506</v>
+        <v>3.14727811195371</v>
       </c>
       <c r="S24" t="n">
         <v>-2.8</v>
@@ -5597,13 +5597,13 @@
         <v>99</v>
       </c>
       <c r="K25" t="n">
-        <v>29.5068064748872</v>
+        <v>29.1664678098864</v>
       </c>
       <c r="L25" t="n">
-        <v>27.989364679541</v>
+        <v>27.7101690218897</v>
       </c>
       <c r="M25" t="n">
-        <v>5.42149424511735</v>
+        <v>5.25546699786019</v>
       </c>
       <c r="N25" t="s">
         <v>70</v>
@@ -5615,10 +5615,10 @@
         <v>0.169699227217671</v>
       </c>
       <c r="Q25" t="n">
-        <v>11.4167706125514</v>
+        <v>11.2912287345048</v>
       </c>
       <c r="R25" t="n">
-        <v>5.72811171505475</v>
+        <v>5.68183251438816</v>
       </c>
       <c r="S25" t="n">
         <v>-3.7</v>
@@ -5747,13 +5747,13 @@
         <v>122</v>
       </c>
       <c r="K26" t="n">
-        <v>4.45169014585179</v>
+        <v>4.43470223524426</v>
       </c>
       <c r="L26" t="n">
-        <v>5.05116420021213</v>
+        <v>5.03083656119523</v>
       </c>
       <c r="M26" t="n">
-        <v>-11.8680373592917</v>
+        <v>-11.8496062970755</v>
       </c>
       <c r="N26" t="s">
         <v>70</v>
@@ -5765,10 +5765,10 @@
         <v>0.203311042549467</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.37168974169438</v>
+        <v>2.36452679158278</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6920510288411</v>
+        <v>1.68868339304353</v>
       </c>
       <c r="S26" t="n">
         <v>0.2</v>
@@ -5895,13 +5895,13 @@
         <v>125</v>
       </c>
       <c r="K27" t="n">
-        <v>5.13691780206467</v>
+        <v>5.18430723733948</v>
       </c>
       <c r="L27" t="n">
-        <v>5.75784443548851</v>
+        <v>5.81070245773052</v>
       </c>
       <c r="M27" t="n">
-        <v>-10.7840119749807</v>
+        <v>-10.7800257360913</v>
       </c>
       <c r="N27" t="s">
         <v>70</v>
@@ -5913,10 +5913,10 @@
         <v>0.202572255492863</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.65077902359484</v>
+        <v>2.67010770311364</v>
       </c>
       <c r="R27" t="n">
-        <v>1.84203501924867</v>
+        <v>1.85250835285784</v>
       </c>
       <c r="S27" t="n">
         <v>-0.2</v>
@@ -6043,13 +6043,13 @@
         <v>127</v>
       </c>
       <c r="K28" t="n">
-        <v>6.01873157214798</v>
+        <v>6.01654743432191</v>
       </c>
       <c r="L28" t="n">
-        <v>6.17981832787493</v>
+        <v>6.18058216426673</v>
       </c>
       <c r="M28" t="n">
-        <v>-2.60665843525435</v>
+        <v>-2.65403364254573</v>
       </c>
       <c r="N28" t="s">
         <v>70</v>
@@ -6061,10 +6061,10 @@
         <v>0.197316441437677</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.03139282017422</v>
+        <v>3.03092778441602</v>
       </c>
       <c r="R28" t="n">
-        <v>2.04519891409879</v>
+        <v>2.04531328345996</v>
       </c>
       <c r="S28" t="n">
         <v>-0.5</v>
@@ -6191,13 +6191,13 @@
         <v>125</v>
       </c>
       <c r="K29" t="n">
-        <v>8.57845991587812</v>
+        <v>8.58775180213912</v>
       </c>
       <c r="L29" t="n">
-        <v>8.12478674140872</v>
+        <v>8.13271529641376</v>
       </c>
       <c r="M29" t="n">
-        <v>5.58381639923189</v>
+        <v>5.59513630000075</v>
       </c>
       <c r="N29" t="s">
         <v>70</v>
@@ -6209,10 +6209,10 @@
         <v>0.201612446862279</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.15827175205596</v>
+        <v>4.16269844010292</v>
       </c>
       <c r="R29" t="n">
-        <v>2.69164584255158</v>
+        <v>2.69566842085493</v>
       </c>
       <c r="S29" t="n">
         <v>-1</v>
@@ -6339,13 +6339,13 @@
         <v>95</v>
       </c>
       <c r="K30" t="n">
-        <v>10.4732202090661</v>
+        <v>10.5321223864642</v>
       </c>
       <c r="L30" t="n">
-        <v>9.01704084392751</v>
+        <v>9.05951626053085</v>
       </c>
       <c r="M30" t="n">
-        <v>16.1491934032797</v>
+        <v>16.2547986402872</v>
       </c>
       <c r="N30" t="s">
         <v>70</v>
@@ -6357,10 +6357,10 @@
         <v>0.201612446862279</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.99691052561456</v>
+        <v>5.02003140240585</v>
       </c>
       <c r="R30" t="n">
-        <v>3.18648851451585</v>
+        <v>3.20255006095402</v>
       </c>
       <c r="S30" t="n">
         <v>-1.4</v>
@@ -6487,13 +6487,13 @@
         <v>95</v>
       </c>
       <c r="K31" t="n">
-        <v>13.9433581173575</v>
+        <v>13.8404099204425</v>
       </c>
       <c r="L31" t="n">
-        <v>10.7965022131059</v>
+        <v>10.722418784175</v>
       </c>
       <c r="M31" t="n">
-        <v>29.1469944815239</v>
+        <v>29.0791769938078</v>
       </c>
       <c r="N31" t="s">
         <v>70</v>
@@ -6505,10 +6505,10 @@
         <v>0.198412592696258</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5259963234416</v>
+        <v>6.48380267081673</v>
       </c>
       <c r="R31" t="n">
-        <v>4.08484775454231</v>
+        <v>4.05817301473476</v>
       </c>
       <c r="S31" t="n">
         <v>-1.9</v>
@@ -6635,13 +6635,13 @@
         <v>69</v>
       </c>
       <c r="K32" t="n">
-        <v>14.2290654389809</v>
+        <v>14.1153711151003</v>
       </c>
       <c r="L32" t="n">
-        <v>14.5002174858634</v>
+        <v>14.4124513618677</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.8699860684633</v>
+        <v>-2.0612749303247</v>
       </c>
       <c r="N32" t="s">
         <v>70</v>
@@ -6653,10 +6653,10 @@
         <v>0.191905792974315</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.64108914488903</v>
+        <v>6.59983050453432</v>
       </c>
       <c r="R32" t="n">
-        <v>4.0981084662376</v>
+        <v>4.0735749351453</v>
       </c>
       <c r="S32" t="n">
         <v>-1.7</v>
@@ -6785,13 +6785,13 @@
         <v>133</v>
       </c>
       <c r="K33" t="n">
-        <v>16.5292226326289</v>
+        <v>16.4154692389209</v>
       </c>
       <c r="L33" t="n">
-        <v>14.0915879949274</v>
+        <v>14.0165381920112</v>
       </c>
       <c r="M33" t="n">
-        <v>17.298509143036</v>
+        <v>17.1150038193953</v>
       </c>
       <c r="N33" t="s">
         <v>134</v>
@@ -6803,10 +6803,10 @@
         <v>0.203311042549467</v>
       </c>
       <c r="Q33" t="n">
-        <v>7.88571782674148</v>
+        <v>7.84600241787935</v>
       </c>
       <c r="R33" t="n">
-        <v>4.92595605883643</v>
+        <v>4.90259054008625</v>
       </c>
       <c r="S33" t="n">
         <v>-2.1</v>
@@ -6933,13 +6933,13 @@
         <v>139</v>
       </c>
       <c r="K34" t="n">
-        <v>3.1483717446522</v>
+        <v>3.13532501641423</v>
       </c>
       <c r="L34" t="n">
-        <v>2.79328547887049</v>
+        <v>2.78271515623696</v>
       </c>
       <c r="M34" t="n">
-        <v>12.7121366028544</v>
+        <v>12.6714320503469</v>
       </c>
       <c r="N34" t="s">
         <v>70</v>
@@ -6951,13 +6951,13 @@
         <v>0.211525105768024</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.78092087637533</v>
+        <v>1.77544981552341</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35391355863005</v>
+        <v>1.35114967683712</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="T34" t="n">
         <v>105.103069544209</v>
@@ -7081,13 +7081,13 @@
         <v>141</v>
       </c>
       <c r="K35" t="n">
-        <v>6.26861486728349</v>
+        <v>6.250094018728</v>
       </c>
       <c r="L35" t="n">
-        <v>7.84068992551941</v>
+        <v>7.82229174814235</v>
       </c>
       <c r="M35" t="n">
-        <v>-20.0502133507311</v>
+        <v>-20.0989400553581</v>
       </c>
       <c r="N35" t="s">
         <v>70</v>
@@ -7099,13 +7099,13 @@
         <v>0.190011211185027</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.98539654373954</v>
+        <v>2.97638994764346</v>
       </c>
       <c r="R35" t="n">
-        <v>1.94005131432358</v>
+        <v>1.93450928524535</v>
       </c>
       <c r="S35" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="T35" t="n">
         <v>105.615235954165</v>
@@ -7231,13 +7231,13 @@
         <v>125</v>
       </c>
       <c r="K36" t="n">
-        <v>6.32454325302395</v>
+        <v>6.37479889949448</v>
       </c>
       <c r="L36" t="n">
-        <v>6.29971653543307</v>
+        <v>6.34045520826729</v>
       </c>
       <c r="M36" t="n">
-        <v>0.394092614346131</v>
+        <v>0.541659708949793</v>
       </c>
       <c r="N36" t="s">
         <v>134</v>
@@ -7249,10 +7249,10 @@
         <v>0.199701076773208</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.04804372707669</v>
+        <v>3.06730212975106</v>
       </c>
       <c r="R36" t="n">
-        <v>1.99311480040153</v>
+        <v>2.00251059530649</v>
       </c>
       <c r="S36" t="n">
         <v>-1</v>
@@ -7379,13 +7379,13 @@
         <v>144</v>
       </c>
       <c r="K37" t="n">
-        <v>6.74553156066923</v>
+        <v>6.74229397100312</v>
       </c>
       <c r="L37" t="n">
-        <v>6.0791441249772</v>
+        <v>6.07176249165199</v>
       </c>
       <c r="M37" t="n">
-        <v>10.9618627555491</v>
+        <v>11.0434405211507</v>
       </c>
       <c r="N37" t="s">
         <v>134</v>
@@ -7397,13 +7397,13 @@
         <v>0.189895948535514</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.21775564813181</v>
+        <v>3.21410736037801</v>
       </c>
       <c r="R37" t="n">
-        <v>2.08248157736883</v>
+        <v>2.0797891393615</v>
       </c>
       <c r="S37" t="n">
-        <v>-1.1</v>
+        <v>-1.2</v>
       </c>
       <c r="T37" t="n">
         <v>107.640910604179</v>
@@ -7527,13 +7527,13 @@
         <v>65</v>
       </c>
       <c r="K38" t="n">
-        <v>11.8852479341795</v>
+        <v>11.8501557066769</v>
       </c>
       <c r="L38" t="n">
-        <v>17.145208297617</v>
+        <v>17.0924628268672</v>
       </c>
       <c r="M38" t="n">
-        <v>-30.6788944883718</v>
+        <v>-30.6702853374063</v>
       </c>
       <c r="N38" t="s">
         <v>70</v>
@@ -7545,10 +7545,10 @@
         <v>0.246489192855378</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.67720981922902</v>
+        <v>5.65658774634402</v>
       </c>
       <c r="R38" t="n">
-        <v>3.53376997348068</v>
+        <v>3.51945611474224</v>
       </c>
       <c r="S38" t="n">
         <v>-1.9</v>
@@ -7665,13 +7665,13 @@
         <v>147</v>
       </c>
       <c r="K39" t="n">
-        <v>15.6651981720616</v>
+        <v>15.8290434047</v>
       </c>
       <c r="L39" t="n">
-        <v>13.8457704554894</v>
+        <v>14.0322716430476</v>
       </c>
       <c r="M39" t="n">
-        <v>13.1406751427896</v>
+        <v>12.8045679798581</v>
       </c>
       <c r="N39" t="s">
         <v>70</v>
@@ -7683,13 +7683,13 @@
         <v>0.200267049689914</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.96520058227458</v>
+        <v>7.03151813344538</v>
       </c>
       <c r="R39" t="n">
-        <v>4.1359346554992</v>
+        <v>4.17024506069195</v>
       </c>
       <c r="S39" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="T39" t="n">
         <v>100.912349043783</v>
@@ -7813,7 +7813,7 @@
         <v>149</v>
       </c>
       <c r="K40" t="n">
-        <v>24.2586951783112</v>
+        <v>24.3215570412504</v>
       </c>
       <c r="L40"/>
       <c r="M40"/>
@@ -7827,10 +7827,10 @@
         <v>0.242082512194954</v>
       </c>
       <c r="Q40" t="n">
-        <v>11.3662947861527</v>
+        <v>11.3825543719966</v>
       </c>
       <c r="R40" t="n">
-        <v>6.88652198738929</v>
+        <v>6.89766282997759</v>
       </c>
       <c r="S40" t="n">
         <v>-3.2</v>
@@ -7939,7 +7939,7 @@
         <v>82</v>
       </c>
       <c r="K41" t="n">
-        <v>36.6379072898832</v>
+        <v>36.7739483557734</v>
       </c>
       <c r="L41"/>
       <c r="M41"/>
@@ -7953,10 +7953,10 @@
         <v>0.242082512194954</v>
       </c>
       <c r="Q41" t="n">
-        <v>17.5497719180077</v>
+        <v>17.6113295060378</v>
       </c>
       <c r="R41" t="n">
-        <v>10.6328504438891</v>
+        <v>10.6534891855592</v>
       </c>
       <c r="S41" t="n">
         <v>-4</v>
@@ -8065,13 +8065,13 @@
         <v>78</v>
       </c>
       <c r="K42" t="n">
-        <v>3.69308390802721</v>
+        <v>3.7035389277562</v>
       </c>
       <c r="L42" t="n">
-        <v>3.94804784651218</v>
+        <v>3.96369545400499</v>
       </c>
       <c r="M42" t="n">
-        <v>-6.45797488777167</v>
+        <v>-6.56348423504453</v>
       </c>
       <c r="N42" t="s">
         <v>70</v>
@@ -8083,10 +8083,10 @@
         <v>0.190524020107752</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.01737062273679</v>
+        <v>2.02058905208522</v>
       </c>
       <c r="R42" t="n">
-        <v>1.48205978850809</v>
+        <v>1.48373609061404</v>
       </c>
       <c r="S42" t="n">
         <v>0.6</v>
@@ -8215,13 +8215,13 @@
         <v>78</v>
       </c>
       <c r="K43" t="n">
-        <v>5.13626247599693</v>
+        <v>5.10802619173911</v>
       </c>
       <c r="L43" t="n">
-        <v>4.42102471155121</v>
+        <v>4.39808258938388</v>
       </c>
       <c r="M43" t="n">
-        <v>16.1780992215888</v>
+        <v>16.1421162046594</v>
       </c>
       <c r="N43" t="s">
         <v>70</v>
@@ -8233,10 +8233,10 @@
         <v>0.181753859850904</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.60721200147394</v>
+        <v>2.59607223570149</v>
       </c>
       <c r="R43" t="n">
-        <v>1.78824115669603</v>
+        <v>1.78195018762334</v>
       </c>
       <c r="S43" t="n">
         <v>-0.6</v>
@@ -8365,13 +8365,13 @@
         <v>157</v>
       </c>
       <c r="K44" t="n">
-        <v>5.95968033172413</v>
+        <v>5.93307696131606</v>
       </c>
       <c r="L44" t="n">
-        <v>4.95358858784487</v>
+        <v>4.93501110288675</v>
       </c>
       <c r="M44" t="n">
-        <v>20.3103613882674</v>
+        <v>20.2241866861351</v>
       </c>
       <c r="N44" t="s">
         <v>70</v>
@@ -8383,10 +8383,10 @@
         <v>0.1799736670355</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.93486228496814</v>
+        <v>2.92356867239668</v>
       </c>
       <c r="R44" t="n">
-        <v>1.97086501640366</v>
+        <v>1.96442427699035</v>
       </c>
       <c r="S44" t="n">
         <v>-0.8</v>
@@ -8513,13 +8513,13 @@
         <v>112</v>
       </c>
       <c r="K45" t="n">
-        <v>7.77213877447187</v>
+        <v>7.7627575867409</v>
       </c>
       <c r="L45" t="n">
         <v>10.1913787832467</v>
       </c>
       <c r="M45" t="n">
-        <v>-23.7381031578549</v>
+        <v>-23.8301533890404</v>
       </c>
       <c r="N45" t="s">
         <v>70</v>
@@ -8531,10 +8531,10 @@
         <v>0.183786602970441</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.72765967279693</v>
+        <v>3.72343270630626</v>
       </c>
       <c r="R45" t="n">
-        <v>2.37602277815152</v>
+        <v>2.37278296655986</v>
       </c>
       <c r="S45" t="n">
         <v>-0.9</v>
@@ -8663,13 +8663,13 @@
         <v>160</v>
       </c>
       <c r="K46" t="n">
-        <v>9.2639628409457</v>
+        <v>9.34244537186832</v>
       </c>
       <c r="L46" t="n">
-        <v>10.9766216661179</v>
+        <v>11.0689540675152</v>
       </c>
       <c r="M46" t="n">
-        <v>-15.6027863332371</v>
+        <v>-15.5977582445102</v>
       </c>
       <c r="N46" t="s">
         <v>70</v>
@@ -8681,10 +8681,10 @@
         <v>0.19666517367199</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.39067999641976</v>
+        <v>4.42483278211549</v>
       </c>
       <c r="R46" t="n">
-        <v>2.77011155739329</v>
+        <v>2.78775651094896</v>
       </c>
       <c r="S46" t="n">
         <v>-1.2</v>
@@ -8813,13 +8813,13 @@
         <v>162</v>
       </c>
       <c r="K47" t="n">
-        <v>15.7237626312015</v>
+        <v>15.784670116545</v>
       </c>
       <c r="L47" t="n">
-        <v>20.2077187310568</v>
+        <v>20.2650455927052</v>
       </c>
       <c r="M47" t="n">
-        <v>-22.1893235922963</v>
+        <v>-22.1088842641093</v>
       </c>
       <c r="N47" t="s">
         <v>70</v>
@@ -8831,10 +8831,10 @@
         <v>0.212293497831841</v>
       </c>
       <c r="Q47" t="n">
-        <v>7.35046275048517</v>
+        <v>7.38244051085679</v>
       </c>
       <c r="R47" t="n">
-        <v>4.47700981709039</v>
+        <v>4.49457437590318</v>
       </c>
       <c r="S47" t="n">
         <v>-1.8</v>
@@ -8963,13 +8963,13 @@
         <v>164</v>
       </c>
       <c r="K48" t="n">
-        <v>21.3873893014907</v>
+        <v>21.3141143540272</v>
       </c>
       <c r="L48" t="n">
-        <v>16.4028210595375</v>
+        <v>16.3598887616555</v>
       </c>
       <c r="M48" t="n">
-        <v>30.3884814926697</v>
+        <v>30.282758425494</v>
       </c>
       <c r="N48" t="s">
         <v>70</v>
@@ -8981,10 +8981,10 @@
         <v>0.177221835433806</v>
       </c>
       <c r="Q48" t="n">
-        <v>9.60016437863804</v>
+        <v>9.5604476489662</v>
       </c>
       <c r="R48" t="n">
-        <v>5.60945047927793</v>
+        <v>5.5917814558745</v>
       </c>
       <c r="S48" t="n">
         <v>-2.6</v>
@@ -9111,13 +9111,13 @@
         <v>99</v>
       </c>
       <c r="K49" t="n">
-        <v>50.5795292933978</v>
+        <v>51.1702357423563</v>
       </c>
       <c r="L49" t="n">
-        <v>52.7190300474433</v>
+        <v>53.2807671816729</v>
       </c>
       <c r="M49" t="n">
-        <v>-4.05830826576302</v>
+        <v>-3.96115061954774</v>
       </c>
       <c r="N49" t="s">
         <v>70</v>
@@ -9129,10 +9129,10 @@
         <v>0.18762144341904</v>
       </c>
       <c r="Q49" t="n">
-        <v>22.8354429843133</v>
+        <v>23.1326142243827</v>
       </c>
       <c r="R49" t="n">
-        <v>13.3046581625729</v>
+        <v>13.4578658121638</v>
       </c>
       <c r="S49" t="n">
         <v>-3.5</v>
@@ -9261,13 +9261,13 @@
         <v>95</v>
       </c>
       <c r="K50" t="n">
-        <v>1.83167659839468</v>
+        <v>1.82513268243703</v>
       </c>
       <c r="L50" t="n">
-        <v>2.04175088299545</v>
+        <v>2.03444066969099</v>
       </c>
       <c r="M50" t="n">
-        <v>-10.2889283090485</v>
+        <v>-10.2882325531642</v>
       </c>
       <c r="N50" t="s">
         <v>70</v>
@@ -9279,10 +9279,10 @@
         <v>0.170645729197607</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.2096563103165</v>
+        <v>1.20778659194505</v>
       </c>
       <c r="R50" t="n">
-        <v>1.06325180808477</v>
+        <v>1.06277143898247</v>
       </c>
       <c r="S50" t="n">
         <v>1.5</v>
@@ -9411,13 +9411,13 @@
         <v>171</v>
       </c>
       <c r="K51" t="n">
-        <v>4.52098983263148</v>
+        <v>4.56187526955761</v>
       </c>
       <c r="L51" t="n">
-        <v>3.6486920354628</v>
+        <v>3.67686311996765</v>
       </c>
       <c r="M51" t="n">
-        <v>23.9071368230185</v>
+        <v>24.0697605734573</v>
       </c>
       <c r="N51" t="s">
         <v>70</v>
@@ -9429,10 +9429,10 @@
         <v>0.172972180534869</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.8771308524372</v>
+        <v>1.88746557904464</v>
       </c>
       <c r="R51" t="n">
-        <v>1.27568726272212</v>
+        <v>1.27928582191735</v>
       </c>
       <c r="S51" t="n">
         <v>-1.5</v>
@@ -9561,13 +9561,13 @@
         <v>95</v>
       </c>
       <c r="K52" t="n">
-        <v>7.85198233695069</v>
+        <v>7.84974080908787</v>
       </c>
       <c r="L52" t="n">
-        <v>8.23306166131555</v>
+        <v>8.22899695548424</v>
       </c>
       <c r="M52" t="n">
-        <v>-4.62864654780159</v>
+        <v>-4.60877733274184</v>
       </c>
       <c r="N52" t="s">
         <v>70</v>
@@ -9579,10 +9579,10 @@
         <v>0.170351255728534</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.92081481241061</v>
+        <v>2.91398261975251</v>
       </c>
       <c r="R52" t="n">
-        <v>1.59403458170583</v>
+        <v>1.59282307776056</v>
       </c>
       <c r="S52" t="n">
         <v>-2</v>
@@ -9711,13 +9711,13 @@
         <v>174</v>
       </c>
       <c r="K53" t="n">
-        <v>27.339252224148</v>
+        <v>27.5327503398588</v>
       </c>
       <c r="L53" t="n">
-        <v>28.0367255396692</v>
+        <v>28.1471995496763</v>
       </c>
       <c r="M53" t="n">
-        <v>-2.48771317654159</v>
+        <v>-2.18298523351536</v>
       </c>
       <c r="N53" t="s">
         <v>70</v>
@@ -9729,10 +9729,10 @@
         <v>0.172560424311876</v>
       </c>
       <c r="Q53" t="n">
-        <v>9.9311674761109</v>
+        <v>9.96682083595682</v>
       </c>
       <c r="R53" t="n">
-        <v>4.68517779683525</v>
+        <v>4.70395394842847</v>
       </c>
       <c r="S53" t="n">
         <v>-3.8</v>
@@ -9861,13 +9861,13 @@
         <v>80</v>
       </c>
       <c r="K54" t="n">
-        <v>33.6830701043513</v>
+        <v>33.7374922845357</v>
       </c>
       <c r="L54" t="n">
-        <v>28.0524544179523</v>
+        <v>28.0053206384766</v>
       </c>
       <c r="M54" t="n">
-        <v>20.0717399002195</v>
+        <v>20.4681521774244</v>
       </c>
       <c r="N54" t="s">
         <v>70</v>
@@ -9879,10 +9879,10 @@
         <v>0.166478560752897</v>
       </c>
       <c r="Q54" t="n">
-        <v>11.8038676626938</v>
+        <v>11.8055816966406</v>
       </c>
       <c r="R54" t="n">
-        <v>5.40845390105342</v>
+        <v>5.41085567171526</v>
       </c>
       <c r="S54" t="n">
         <v>-4.1</v>
@@ -10011,13 +10011,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="n">
-        <v>46.7545062813758</v>
+        <v>46.4120121440041</v>
       </c>
       <c r="L55" t="n">
-        <v>45.4783992723965</v>
+        <v>45.1091565178169</v>
       </c>
       <c r="M55" t="n">
-        <v>2.80596289534276</v>
+        <v>2.8882287472447</v>
       </c>
       <c r="N55" t="s">
         <v>70</v>
@@ -10029,10 +10029,10 @@
         <v>0.172055287772107</v>
       </c>
       <c r="Q55" t="n">
-        <v>16.5003521873567</v>
+        <v>16.3199944159838</v>
       </c>
       <c r="R55" t="n">
-        <v>7.63170464011699</v>
+        <v>7.567316212805</v>
       </c>
       <c r="S55" t="n">
         <v>-4.4</v>
@@ -10161,13 +10161,13 @@
         <v>80</v>
       </c>
       <c r="K56" t="n">
-        <v>56.0193991531557</v>
+        <v>55.5967978030875</v>
       </c>
       <c r="L56" t="n">
-        <v>46.7540906965872</v>
+        <v>46.3639313861845</v>
       </c>
       <c r="M56" t="n">
-        <v>19.8171075910686</v>
+        <v>19.9138988883376</v>
       </c>
       <c r="N56" t="s">
         <v>70</v>
@@ -10179,10 +10179,10 @@
         <v>0.156163331194045</v>
       </c>
       <c r="Q56" t="n">
-        <v>19.1552823432024</v>
+        <v>18.9601829633147</v>
       </c>
       <c r="R56" t="n">
-        <v>8.41101235972938</v>
+        <v>8.33238636572007</v>
       </c>
       <c r="S56" t="n">
         <v>-4.8</v>
@@ -10311,13 +10311,13 @@
         <v>80</v>
       </c>
       <c r="K57" t="n">
-        <v>2.93671805350339</v>
+        <v>2.9325837892534</v>
       </c>
       <c r="L57" t="n">
-        <v>3.28919585594475</v>
+        <v>3.28293339460985</v>
       </c>
       <c r="M57" t="n">
-        <v>-10.7162302848065</v>
+        <v>-10.6718462802714</v>
       </c>
       <c r="N57" t="s">
         <v>70</v>
@@ -10329,10 +10329,10 @@
         <v>0.208737572772627</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.663022225636</v>
+        <v>1.66242670749889</v>
       </c>
       <c r="R57" t="n">
-        <v>1.29058798230358</v>
+        <v>1.29070959555154</v>
       </c>
       <c r="S57" t="n">
         <v>0.5</v>
@@ -10461,13 +10461,13 @@
         <v>141</v>
       </c>
       <c r="K58" t="n">
-        <v>3.86429656481089</v>
+        <v>3.89210036880959</v>
       </c>
       <c r="L58" t="n">
-        <v>3.47165619467491</v>
+        <v>3.49470594401929</v>
       </c>
       <c r="M58" t="n">
-        <v>11.3098863515993</v>
+        <v>11.3713265481002</v>
       </c>
       <c r="N58" t="s">
         <v>70</v>
@@ -10479,10 +10479,10 @@
         <v>0.193779814339126</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.93942153005013</v>
+        <v>1.95026112315195</v>
       </c>
       <c r="R58" t="n">
-        <v>1.40219267248178</v>
+        <v>1.40781708595859</v>
       </c>
       <c r="S58" t="n">
         <v>-0.5</v>
@@ -10611,13 +10611,13 @@
         <v>183</v>
       </c>
       <c r="K59" t="n">
-        <v>11.3543292243615</v>
+        <v>11.2680827853101</v>
       </c>
       <c r="L59" t="n">
-        <v>11.3092841795771</v>
+        <v>11.2381166423194</v>
       </c>
       <c r="M59" t="n">
-        <v>0.398301466911799</v>
+        <v>0.266647374684315</v>
       </c>
       <c r="N59" t="s">
         <v>70</v>
@@ -10629,10 +10629,10 @@
         <v>0.247328769145524</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.33913316253662</v>
+        <v>5.30170076632329</v>
       </c>
       <c r="R59" t="n">
-        <v>3.2102171899229</v>
+        <v>3.1919352624958</v>
       </c>
       <c r="S59" t="n">
         <v>-2.2</v>
@@ -10749,13 +10749,13 @@
         <v>185</v>
       </c>
       <c r="K60" t="n">
-        <v>12.2194724812146</v>
+        <v>12.230151958231</v>
       </c>
       <c r="L60" t="n">
-        <v>13.0609899438422</v>
+        <v>13.071232518625</v>
       </c>
       <c r="M60" t="n">
-        <v>-6.44298377263838</v>
+        <v>-6.43459260016659</v>
       </c>
       <c r="N60" t="s">
         <v>70</v>
@@ -10767,10 +10767,10 @@
         <v>0.19823529604799</v>
       </c>
       <c r="Q60" t="n">
-        <v>5.35380141222848</v>
+        <v>5.3577423305194</v>
       </c>
       <c r="R60" t="n">
-        <v>3.09691639140136</v>
+        <v>3.1025557726843</v>
       </c>
       <c r="S60" t="n">
         <v>-2.2</v>
@@ -10899,13 +10899,13 @@
         <v>149</v>
       </c>
       <c r="K61" t="n">
-        <v>12.4359299748728</v>
+        <v>12.3830554258969</v>
       </c>
       <c r="L61" t="n">
-        <v>10.4185852692989</v>
+        <v>10.3560111835974</v>
       </c>
       <c r="M61" t="n">
-        <v>19.3629427933805</v>
+        <v>19.573600359858</v>
       </c>
       <c r="N61" t="s">
         <v>70</v>
@@ -10917,10 +10917,10 @@
         <v>0.247328769145524</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.90199585076457</v>
+        <v>5.88231067794508</v>
       </c>
       <c r="R61" t="n">
-        <v>3.55914815826886</v>
+        <v>3.54993096101002</v>
       </c>
       <c r="S61" t="n">
         <v>-2.5</v>
@@ -11037,7 +11037,7 @@
         <v>82</v>
       </c>
       <c r="K62" t="n">
-        <v>18.5070475554669</v>
+        <v>18.3964536539411</v>
       </c>
       <c r="L62"/>
       <c r="M62"/>
@@ -11051,10 +11051,10 @@
         <v>0.247328769145524</v>
       </c>
       <c r="Q62" t="n">
-        <v>8.59101554507611</v>
+        <v>8.53851024769376</v>
       </c>
       <c r="R62" t="n">
-        <v>5.05332790756438</v>
+        <v>5.02619216484635</v>
       </c>
       <c r="S62" t="n">
         <v>-3</v>
@@ -11154,88 +11154,88 @@
         <v>137</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I63" t="s">
         <v>188</v>
       </c>
       <c r="J63" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="K63" t="n">
-        <v>20.7509064043979</v>
+        <v>20.6281173586989</v>
       </c>
       <c r="L63" t="n">
-        <v>17.9193692886579</v>
+        <v>24.8961911874533</v>
       </c>
       <c r="M63" t="n">
-        <v>15.801544519383</v>
+        <v>-17.1434810916192</v>
       </c>
       <c r="N63" t="s">
         <v>70</v>
       </c>
       <c r="O63" t="n">
-        <v>0.248609235417987</v>
+        <v>0.299471718865888</v>
       </c>
       <c r="P63" t="n">
-        <v>0.189534921131426</v>
+        <v>0.216900707774602</v>
       </c>
       <c r="Q63" t="n">
-        <v>8.69750524708969</v>
+        <v>9.18742336012009</v>
       </c>
       <c r="R63" t="n">
-        <v>4.81740466038712</v>
+        <v>5.20388486545388</v>
       </c>
       <c r="S63" t="n">
-        <v>-3.1</v>
+        <v>-3</v>
       </c>
       <c r="T63" t="n">
-        <v>98.5890350570534</v>
+        <v>97.8679930045661</v>
       </c>
       <c r="U63" t="n">
-        <v>100.729136210841</v>
+        <v>103.097681634727</v>
       </c>
       <c r="V63" t="n">
-        <v>98.7176834471495</v>
+        <v>98.7311717616341</v>
       </c>
       <c r="W63" t="n">
-        <v>104.924422247245</v>
+        <v>103.306580301625</v>
       </c>
       <c r="X63" t="n">
-        <v>99.6297459943047</v>
+        <v>99.9992774700519</v>
       </c>
       <c r="Y63" t="n">
-        <v>100.612057187348</v>
+        <v>97.8541281814309</v>
       </c>
       <c r="Z63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AA63" t="n">
-        <v>100.612057187348</v>
+        <v>97.8541281814309</v>
       </c>
       <c r="AB63" t="n">
-        <v>100.729136210841</v>
+        <v>97.8519834002231</v>
       </c>
       <c r="AC63" t="n">
-        <v>98.7176834471495</v>
+        <v>97.8519834002231</v>
       </c>
       <c r="AD63" t="n">
-        <v>106.090550889462</v>
+        <v>97.8519834002231</v>
       </c>
       <c r="AE63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH63" t="n">
         <v>7</v>
       </c>
-      <c r="AG63" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>37</v>
-      </c>
       <c r="AI63" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="AJ63" t="n">
         <v>0</v>
@@ -11304,88 +11304,88 @@
         <v>137</v>
       </c>
       <c r="H64" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I64" t="s">
+        <v>189</v>
+      </c>
+      <c r="J64" t="s">
         <v>190</v>
       </c>
-      <c r="J64" t="s">
-        <v>162</v>
-      </c>
       <c r="K64" t="n">
-        <v>20.7643392729644</v>
+        <v>20.8461964821253</v>
       </c>
       <c r="L64" t="n">
-        <v>25.045830202855</v>
+        <v>17.9902860226659</v>
       </c>
       <c r="M64" t="n">
-        <v>-17.094625712996</v>
+        <v>15.8747362652333</v>
       </c>
       <c r="N64" t="s">
         <v>70</v>
       </c>
       <c r="O64" t="n">
-        <v>0.299471718865888</v>
+        <v>0.248609235417987</v>
       </c>
       <c r="P64" t="n">
-        <v>0.216900707774602</v>
+        <v>0.189534921131426</v>
       </c>
       <c r="Q64" t="n">
-        <v>9.24405890586449</v>
+        <v>8.73429138858726</v>
       </c>
       <c r="R64" t="n">
-        <v>5.23156953349066</v>
+        <v>4.84282999952389</v>
       </c>
       <c r="S64" t="n">
-        <v>-3</v>
+        <v>-3.1</v>
       </c>
       <c r="T64" t="n">
-        <v>97.8679930045661</v>
+        <v>98.5890350570534</v>
       </c>
       <c r="U64" t="n">
-        <v>103.097681634727</v>
+        <v>100.729136210841</v>
       </c>
       <c r="V64" t="n">
-        <v>98.7311717616341</v>
+        <v>98.7176834471495</v>
       </c>
       <c r="W64" t="n">
-        <v>103.306580301625</v>
+        <v>104.924422247245</v>
       </c>
       <c r="X64" t="n">
-        <v>99.9992774700519</v>
+        <v>99.6297459943047</v>
       </c>
       <c r="Y64" t="n">
-        <v>97.8541281814309</v>
+        <v>100.612057187348</v>
       </c>
       <c r="Z64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AA64" t="n">
-        <v>97.8541281814309</v>
+        <v>100.612057187348</v>
       </c>
       <c r="AB64" t="n">
-        <v>97.8519834002231</v>
+        <v>100.729136210841</v>
       </c>
       <c r="AC64" t="n">
-        <v>97.8519834002231</v>
+        <v>98.7176834471495</v>
       </c>
       <c r="AD64" t="n">
-        <v>97.8519834002231</v>
+        <v>106.090550889462</v>
       </c>
       <c r="AE64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AF64" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="AG64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AH64" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="AI64" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AJ64" t="n">
         <v>0</v>
@@ -11463,13 +11463,13 @@
         <v>127</v>
       </c>
       <c r="K65" t="n">
-        <v>1.8153136613204</v>
+        <v>1.81090952750063</v>
       </c>
       <c r="L65" t="n">
-        <v>1.86078704995814</v>
+        <v>1.85574585737878</v>
       </c>
       <c r="M65" t="n">
-        <v>-2.44377177059356</v>
+        <v>-2.41608136695445</v>
       </c>
       <c r="N65" t="s">
         <v>70</v>
@@ -11481,10 +11481,10 @@
         <v>0.19915089912733</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.22220416651601</v>
+        <v>1.22097061614247</v>
       </c>
       <c r="R65" t="n">
-        <v>1.08296433017747</v>
+        <v>1.08250409930567</v>
       </c>
       <c r="S65" t="n">
         <v>1.5</v>
@@ -11611,13 +11611,13 @@
         <v>84</v>
       </c>
       <c r="K66" t="n">
-        <v>4.79446025801147</v>
+        <v>4.8213063409336</v>
       </c>
       <c r="L66" t="n">
-        <v>4.35366331461408</v>
+        <v>4.3780589239592</v>
       </c>
       <c r="M66" t="n">
-        <v>10.1247366078528</v>
+        <v>10.1242908026821</v>
       </c>
       <c r="N66" t="s">
         <v>70</v>
@@ -11629,10 +11629,10 @@
         <v>0.187141559519977</v>
       </c>
       <c r="Q66" t="n">
-        <v>1.86207735499613</v>
+        <v>1.86652440861273</v>
       </c>
       <c r="R66" t="n">
-        <v>1.29532598966162</v>
+        <v>1.29685525637266</v>
       </c>
       <c r="S66" t="n">
         <v>-1.5</v>
@@ -11761,13 +11761,13 @@
         <v>196</v>
       </c>
       <c r="K67" t="n">
-        <v>11.993464346855</v>
+        <v>11.9543914226335</v>
       </c>
       <c r="L67" t="n">
-        <v>11.3297836184434</v>
+        <v>11.2863108001354</v>
       </c>
       <c r="M67" t="n">
-        <v>5.85784116239587</v>
+        <v>5.91938884484802</v>
       </c>
       <c r="N67" t="s">
         <v>70</v>
@@ -11779,10 +11779,10 @@
         <v>0.211573927350887</v>
       </c>
       <c r="Q67" t="n">
-        <v>4.45406356289578</v>
+        <v>4.43124569710542</v>
       </c>
       <c r="R67" t="n">
-        <v>2.25524498329736</v>
+        <v>2.24594864697336</v>
       </c>
       <c r="S67" t="n">
         <v>-2.9</v>
@@ -11908,16 +11908,16 @@
         <v>197</v>
       </c>
       <c r="J68" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K68" t="n">
-        <v>22.1548589007101</v>
+        <v>22.2235001330399</v>
       </c>
       <c r="L68" t="n">
-        <v>19.5366282477046</v>
+        <v>19.6132575014709</v>
       </c>
       <c r="M68" t="n">
-        <v>13.4016505806884</v>
+        <v>13.3085624933711</v>
       </c>
       <c r="N68" t="s">
         <v>70</v>
@@ -11929,13 +11929,13 @@
         <v>0.18235284919104</v>
       </c>
       <c r="Q68" t="n">
-        <v>7.79415683591367</v>
+        <v>7.80896526480163</v>
       </c>
       <c r="R68" t="n">
-        <v>3.747808920707</v>
+        <v>3.75343312153791</v>
       </c>
       <c r="S68" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="T68" t="n">
         <v>102.228962922941</v>
@@ -12059,13 +12059,13 @@
         <v>183</v>
       </c>
       <c r="K69" t="n">
-        <v>23.456740767876</v>
+        <v>23.4608769685107</v>
       </c>
       <c r="L69" t="n">
-        <v>28.8623376623377</v>
+        <v>28.8790066416402</v>
       </c>
       <c r="M69" t="n">
-        <v>-18.7288949277156</v>
+        <v>-18.7614821394763</v>
       </c>
       <c r="N69" t="s">
         <v>70</v>
@@ -12077,10 +12077,10 @@
         <v>0.245513628824079</v>
       </c>
       <c r="Q69" t="n">
-        <v>9.19169862312834</v>
+        <v>9.17833337748664</v>
       </c>
       <c r="R69" t="n">
-        <v>4.59530872273478</v>
+        <v>4.5892191158549</v>
       </c>
       <c r="S69" t="n">
         <v>-4</v>
@@ -12197,7 +12197,7 @@
         <v>82</v>
       </c>
       <c r="K70" t="n">
-        <v>27.7595873849763</v>
+        <v>28.0120703521444</v>
       </c>
       <c r="L70"/>
       <c r="M70"/>
@@ -12211,13 +12211,13 @@
         <v>0.245513628824079</v>
       </c>
       <c r="Q70" t="n">
-        <v>11.0695322449829</v>
+        <v>11.1697946355082</v>
       </c>
       <c r="R70" t="n">
-        <v>5.55614561542417</v>
+        <v>5.60628615010999</v>
       </c>
       <c r="S70" t="n">
-        <v>-4.3</v>
+        <v>-4.4</v>
       </c>
       <c r="T70"/>
       <c r="U70"/>
@@ -12323,13 +12323,13 @@
         <v>78</v>
       </c>
       <c r="K71" t="n">
-        <v>35.3993925955585</v>
+        <v>35.3343727750991</v>
       </c>
       <c r="L71" t="n">
-        <v>38.3907869481766</v>
+        <v>38.361334867664</v>
       </c>
       <c r="M71" t="n">
-        <v>-7.7919589318556</v>
+        <v>-7.89065892260283</v>
       </c>
       <c r="N71" t="s">
         <v>70</v>
@@ -12341,10 +12341,10 @@
         <v>0.199647452563919</v>
       </c>
       <c r="Q71" t="n">
-        <v>12.5817120246248</v>
+        <v>12.5353025007466</v>
       </c>
       <c r="R71" t="n">
-        <v>5.94699576085644</v>
+        <v>5.9273122456165</v>
       </c>
       <c r="S71" t="n">
         <v>-4.5</v>
@@ -12473,13 +12473,13 @@
         <v>202</v>
       </c>
       <c r="K72" t="n">
-        <v>194.663903015833</v>
+        <v>195.853832393744</v>
       </c>
       <c r="L72" t="n">
-        <v>281.712676056338</v>
+        <v>283.308781869688</v>
       </c>
       <c r="M72" t="n">
-        <v>-30.8998424419839</v>
+        <v>-30.8691276347977</v>
       </c>
       <c r="N72" t="s">
         <v>56</v>
@@ -12491,10 +12491,10 @@
         <v>0.192587407496825</v>
       </c>
       <c r="Q72" t="n">
-        <v>74.9409511165987</v>
+        <v>75.5165164878644</v>
       </c>
       <c r="R72" t="n">
-        <v>34.937558009593</v>
+        <v>35.1280830881255</v>
       </c>
       <c r="S72" t="n">
         <v>-7.4</v>
@@ -12621,13 +12621,13 @@
         <v>80</v>
       </c>
       <c r="K73" t="n">
-        <v>3.00960744534986</v>
+        <v>3.0131732344379</v>
       </c>
       <c r="L73" t="n">
-        <v>2.59078780342478</v>
+        <v>2.59589876703439</v>
       </c>
       <c r="M73" t="n">
-        <v>16.1657253971722</v>
+        <v>16.0743736505647</v>
       </c>
       <c r="N73" t="s">
         <v>70</v>
@@ -12639,10 +12639,10 @@
         <v>0.176974919810992</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.6530613184387</v>
+        <v>1.65408874634103</v>
       </c>
       <c r="R73" t="n">
-        <v>1.24531070150691</v>
+        <v>1.24583662132381</v>
       </c>
       <c r="S73" t="n">
         <v>0.4</v>
@@ -12769,13 +12769,13 @@
         <v>147</v>
       </c>
       <c r="K74" t="n">
-        <v>4.16171462533814</v>
+        <v>4.13766969404729</v>
       </c>
       <c r="L74" t="n">
-        <v>4.25543593889622</v>
+        <v>4.23130949862492</v>
       </c>
       <c r="M74" t="n">
-        <v>-2.20239042259879</v>
+        <v>-2.21302186966154</v>
       </c>
       <c r="N74" t="s">
         <v>70</v>
@@ -12787,10 +12787,10 @@
         <v>0.172395285301765</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.05604622924251</v>
+        <v>2.0469954503199</v>
       </c>
       <c r="R74" t="n">
-        <v>1.40634704766106</v>
+        <v>1.40234609084046</v>
       </c>
       <c r="S74" t="n">
         <v>-0.4</v>
@@ -12917,13 +12917,13 @@
         <v>196</v>
       </c>
       <c r="K75" t="n">
-        <v>4.56899655894572</v>
+        <v>4.58364451352412</v>
       </c>
       <c r="L75" t="n">
-        <v>5.04245449503353</v>
+        <v>5.05417698488907</v>
       </c>
       <c r="M75" t="n">
-        <v>-9.38943398605041</v>
+        <v>-9.30977432669544</v>
       </c>
       <c r="N75" t="s">
         <v>70</v>
@@ -12935,10 +12935,10 @@
         <v>0.203911481692859</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.26055948296349</v>
+        <v>2.26601358708297</v>
       </c>
       <c r="R75" t="n">
-        <v>1.50647012582724</v>
+        <v>1.50847685971449</v>
       </c>
       <c r="S75" t="n">
         <v>-0.5</v>
@@ -13067,13 +13067,13 @@
         <v>99</v>
       </c>
       <c r="K76" t="n">
-        <v>13.2663236871998</v>
+        <v>13.2510164073578</v>
       </c>
       <c r="L76" t="n">
-        <v>13.0472276581866</v>
+        <v>12.9896090401351</v>
       </c>
       <c r="M76" t="n">
-        <v>1.67925351464064</v>
+        <v>2.01243444983614</v>
       </c>
       <c r="N76" t="s">
         <v>70</v>
@@ -13085,10 +13085,10 @@
         <v>0.18524483213304</v>
       </c>
       <c r="Q76" t="n">
-        <v>5.78320657815706</v>
+        <v>5.77385805990373</v>
       </c>
       <c r="R76" t="n">
-        <v>3.28613700730006</v>
+        <v>3.27912407171145</v>
       </c>
       <c r="S76" t="n">
         <v>-2.2</v>
@@ -13215,13 +13215,13 @@
         <v>108</v>
       </c>
       <c r="K77" t="n">
-        <v>19.3038698166778</v>
+        <v>19.2226819733115</v>
       </c>
       <c r="L77" t="n">
-        <v>20.7182515019681</v>
+        <v>20.6668733209341</v>
       </c>
       <c r="M77" t="n">
-        <v>-6.8267425229196</v>
+        <v>-6.98795277445158</v>
       </c>
       <c r="N77" t="s">
         <v>70</v>
@@ -13233,10 +13233,10 @@
         <v>0.243911593402784</v>
       </c>
       <c r="Q77" t="n">
-        <v>9.25096756952637</v>
+        <v>9.2141085108375</v>
       </c>
       <c r="R77" t="n">
-        <v>5.45434561908735</v>
+        <v>5.42932448737319</v>
       </c>
       <c r="S77" t="n">
         <v>-3</v>
@@ -13353,13 +13353,13 @@
         <v>202</v>
       </c>
       <c r="K78" t="n">
-        <v>21.6342294810194</v>
+        <v>21.7677864283004</v>
       </c>
       <c r="L78" t="n">
-        <v>30.4065065369413</v>
+        <v>30.686406873274</v>
       </c>
       <c r="M78" t="n">
-        <v>-28.8499997369455</v>
+        <v>-29.0637495676994</v>
       </c>
       <c r="N78" t="s">
         <v>56</v>
@@ -13371,10 +13371,10 @@
         <v>0.182353522655851</v>
       </c>
       <c r="Q78" t="n">
-        <v>9.31530558678639</v>
+        <v>9.37790086684894</v>
       </c>
       <c r="R78" t="n">
-        <v>5.09745660169825</v>
+        <v>5.12510319728638</v>
       </c>
       <c r="S78" t="n">
         <v>-2.8</v>
@@ -13501,7 +13501,7 @@
         <v>139</v>
       </c>
       <c r="K79" t="n">
-        <v>28.4302731386547</v>
+        <v>28.6962213360577</v>
       </c>
       <c r="L79"/>
       <c r="M79"/>
@@ -13515,10 +13515,10 @@
         <v>0.220034856910108</v>
       </c>
       <c r="Q79" t="n">
-        <v>12.8268358681657</v>
+        <v>12.9440262681496</v>
       </c>
       <c r="R79" t="n">
-        <v>7.23080901073319</v>
+        <v>7.29644896962883</v>
       </c>
       <c r="S79" t="n">
         <v>-3.3</v>
@@ -27687,13 +27687,13 @@
         <v>401</v>
       </c>
       <c r="K176" t="n">
-        <v>2.85211815438601</v>
+        <v>2.85159183627471</v>
       </c>
       <c r="L176" t="n">
-        <v>2.95034958845916</v>
+        <v>2.95052367605842</v>
       </c>
       <c r="M176" t="n">
-        <v>-3.32948456201252</v>
+        <v>-3.35302646735123</v>
       </c>
       <c r="N176" t="s">
         <v>70</v>
@@ -27705,10 +27705,10 @@
         <v>0.187194832940143</v>
       </c>
       <c r="Q176" t="n">
-        <v>1.62397882436055</v>
+        <v>1.6237296321439</v>
       </c>
       <c r="R176" t="n">
-        <v>1.25226092740241</v>
+        <v>1.25206047483633</v>
       </c>
       <c r="S176" t="n">
         <v>0.6</v>
@@ -27837,13 +27837,13 @@
         <v>65</v>
       </c>
       <c r="K177" t="n">
-        <v>5.0045700800725</v>
+        <v>5.00362122084192</v>
       </c>
       <c r="L177" t="n">
         <v>6.03730757621491</v>
       </c>
       <c r="M177" t="n">
-        <v>-17.105928149347</v>
+        <v>-17.1216447451739</v>
       </c>
       <c r="N177" t="s">
         <v>70</v>
@@ -27855,10 +27855,10 @@
         <v>0.186913506106322</v>
       </c>
       <c r="Q177" t="n">
-        <v>2.4013901117598</v>
+        <v>2.40070849871161</v>
       </c>
       <c r="R177" t="n">
-        <v>1.60269074604331</v>
+        <v>1.6023726994537</v>
       </c>
       <c r="S177" t="n">
         <v>-0.6</v>
@@ -27987,7 +27987,7 @@
         <v>65</v>
       </c>
       <c r="K178" t="n">
-        <v>7.18396346429251</v>
+        <v>7.1815329483469</v>
       </c>
       <c r="L178"/>
       <c r="M178"/>
@@ -28001,10 +28001,10 @@
         <v>0.234282348625883</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.47864006379387</v>
+        <v>3.47751164292797</v>
       </c>
       <c r="R178" t="n">
-        <v>2.2030654665027</v>
+        <v>2.20245361886935</v>
       </c>
       <c r="S178" t="n">
         <v>-1.4</v>
@@ -28113,13 +28113,13 @@
         <v>405</v>
       </c>
       <c r="K179" t="n">
-        <v>7.29316914084234</v>
+        <v>7.29525800477796</v>
       </c>
       <c r="L179" t="n">
-        <v>7.95418754473873</v>
+        <v>7.94281629735525</v>
       </c>
       <c r="M179" t="n">
-        <v>-8.31031956662388</v>
+        <v>-8.15275424150145</v>
       </c>
       <c r="N179" t="s">
         <v>70</v>
@@ -28131,10 +28131,10 @@
         <v>0.193266489451609</v>
       </c>
       <c r="Q179" t="n">
-        <v>3.35829024422385</v>
+        <v>3.35911212649544</v>
       </c>
       <c r="R179" t="n">
-        <v>2.08132541988665</v>
+        <v>2.08183013582911</v>
       </c>
       <c r="S179" t="n">
         <v>-1.2</v>
@@ -28263,13 +28263,13 @@
         <v>407</v>
       </c>
       <c r="K180" t="n">
-        <v>8.18787290693326</v>
+        <v>8.18739842388551</v>
       </c>
       <c r="L180" t="n">
         <v>6.47175305765871</v>
       </c>
       <c r="M180" t="n">
-        <v>26.5170786645465</v>
+        <v>26.5097470645377</v>
       </c>
       <c r="N180" t="s">
         <v>134</v>
@@ -28281,10 +28281,10 @@
         <v>0.204229353511527</v>
       </c>
       <c r="Q180" t="n">
-        <v>3.80553957419967</v>
+        <v>3.80465320239584</v>
       </c>
       <c r="R180" t="n">
-        <v>2.36656088655731</v>
+        <v>2.3658978924395</v>
       </c>
       <c r="S180" t="n">
         <v>-1.6</v>
@@ -28413,13 +28413,13 @@
         <v>409</v>
       </c>
       <c r="K181" t="n">
-        <v>45.5485052823103</v>
+        <v>45.80533900801</v>
       </c>
       <c r="L181" t="n">
-        <v>35.4764100744945</v>
+        <v>35.6789154477346</v>
       </c>
       <c r="M181" t="n">
-        <v>28.3909651136235</v>
+        <v>28.3820946718784</v>
       </c>
       <c r="N181" t="s">
         <v>56</v>
@@ -28431,13 +28431,13 @@
         <v>0.188446254355155</v>
       </c>
       <c r="Q181" t="n">
-        <v>19.3588208276555</v>
+        <v>19.4730115032891</v>
       </c>
       <c r="R181" t="n">
-        <v>10.5305010301106</v>
+        <v>10.5757947722355</v>
       </c>
       <c r="S181" t="n">
-        <v>-3.9</v>
+        <v>-4</v>
       </c>
       <c r="T181" t="n">
         <v>88.8318989557384</v>
@@ -28563,13 +28563,13 @@
         <v>409</v>
       </c>
       <c r="K182" t="n">
-        <v>54.596479340958</v>
+        <v>54.5872049238299</v>
       </c>
       <c r="L182" t="n">
         <v>41.8268506900878</v>
       </c>
       <c r="M182" t="n">
-        <v>30.5297397250525</v>
+        <v>30.5075663675679</v>
       </c>
       <c r="N182" t="s">
         <v>56</v>
@@ -28581,10 +28581,10 @@
         <v>0.187778522082662</v>
       </c>
       <c r="Q182" t="n">
-        <v>23.4441463926291</v>
+        <v>23.4432259728298</v>
       </c>
       <c r="R182" t="n">
-        <v>12.7240054798249</v>
+        <v>12.7209387254139</v>
       </c>
       <c r="S182" t="n">
         <v>-4.2</v>
@@ -28713,13 +28713,13 @@
         <v>412</v>
       </c>
       <c r="K183" t="n">
-        <v>92.1672847966924</v>
+        <v>92.1464304395819</v>
       </c>
       <c r="L183" t="n">
-        <v>94.974358974359</v>
+        <v>94.7943127962085</v>
       </c>
       <c r="M183" t="n">
-        <v>-2.95561266007007</v>
+        <v>-2.7932924228473</v>
       </c>
       <c r="N183" t="s">
         <v>70</v>
@@ -28731,10 +28731,10 @@
         <v>0.188052398615449</v>
       </c>
       <c r="Q183" t="n">
-        <v>39.2491014479437</v>
+        <v>39.2385345610783</v>
       </c>
       <c r="R183" t="n">
-        <v>21.2722056968086</v>
+        <v>21.2685701996077</v>
       </c>
       <c r="S183" t="n">
         <v>-4.5</v>
@@ -28863,13 +28863,13 @@
         <v>416</v>
       </c>
       <c r="K184" t="n">
-        <v>2.18329231639779</v>
+        <v>2.18302711115809</v>
       </c>
       <c r="L184" t="n">
-        <v>1.83563077036031</v>
+        <v>1.83556338674449</v>
       </c>
       <c r="M184" t="n">
-        <v>18.9396229160639</v>
+        <v>18.929541029354</v>
       </c>
       <c r="N184" t="s">
         <v>70</v>
@@ -28881,10 +28881,10 @@
         <v>0.174717416363514</v>
       </c>
       <c r="Q184" t="n">
-        <v>1.3189923633451</v>
+        <v>1.31882204757005</v>
       </c>
       <c r="R184" t="n">
-        <v>1.09696830629137</v>
+        <v>1.09684126576006</v>
       </c>
       <c r="S184" t="n">
         <v>0.3</v>
@@ -29013,13 +29013,13 @@
         <v>418</v>
       </c>
       <c r="K185" t="n">
-        <v>3.37405954492771</v>
+        <v>3.3734296330396</v>
       </c>
       <c r="L185" t="n">
-        <v>3.9170811954095</v>
+        <v>3.91677437042259</v>
       </c>
       <c r="M185" t="n">
-        <v>-13.8629153543758</v>
+        <v>-13.8722501220915</v>
       </c>
       <c r="N185" t="s">
         <v>70</v>
@@ -29031,10 +29031,10 @@
         <v>0.165373458246832</v>
       </c>
       <c r="Q185" t="n">
-        <v>1.58364149979848</v>
+        <v>1.58331069439539</v>
       </c>
       <c r="R185" t="n">
-        <v>1.1833570308101</v>
+        <v>1.18316280773287</v>
       </c>
       <c r="S185" t="n">
         <v>-0.3</v>
@@ -29163,13 +29163,13 @@
         <v>420</v>
       </c>
       <c r="K186" t="n">
-        <v>9.68837507410253</v>
+        <v>9.68750571973709</v>
       </c>
       <c r="L186" t="n">
         <v>11.8815492455744</v>
       </c>
       <c r="M186" t="n">
-        <v>-18.4586548954363</v>
+        <v>-18.4659717389512</v>
       </c>
       <c r="N186" t="s">
         <v>70</v>
@@ -29181,10 +29181,10 @@
         <v>0.23254750028524</v>
       </c>
       <c r="Q186" t="n">
-        <v>4.15421782758695</v>
+        <v>4.15327688778189</v>
       </c>
       <c r="R186" t="n">
-        <v>2.19018138794176</v>
+        <v>2.1890362121001</v>
       </c>
       <c r="S186" t="n">
         <v>-1.8</v>
@@ -29303,13 +29303,13 @@
         <v>405</v>
       </c>
       <c r="K187" t="n">
-        <v>15.6779933071275</v>
+        <v>15.6835844315843</v>
       </c>
       <c r="L187" t="n">
-        <v>16.3543744889616</v>
+        <v>16.3436836084328</v>
       </c>
       <c r="M187" t="n">
-        <v>-4.13578142221592</v>
+        <v>-4.03886414264575</v>
       </c>
       <c r="N187" t="s">
         <v>70</v>
@@ -29321,13 +29321,13 @@
         <v>0.179449227253595</v>
       </c>
       <c r="Q187" t="n">
-        <v>6.07134111616846</v>
+        <v>6.07247457799178</v>
       </c>
       <c r="R187" t="n">
-        <v>2.95092017790687</v>
+        <v>2.9502969367139</v>
       </c>
       <c r="S187" t="n">
-        <v>-2.5</v>
+        <v>-2.6</v>
       </c>
       <c r="T187" t="n">
         <v>88.3334215792237</v>
@@ -29453,13 +29453,13 @@
         <v>423</v>
       </c>
       <c r="K188" t="n">
-        <v>21.4130828068557</v>
+        <v>21.4058733612146</v>
       </c>
       <c r="L188" t="n">
-        <v>38.1851851851852</v>
+        <v>38.156047310187</v>
       </c>
       <c r="M188" t="n">
-        <v>-43.923061514539</v>
+        <v>-43.8991329809479</v>
       </c>
       <c r="N188" t="s">
         <v>70</v>
@@ -29471,10 +29471,10 @@
         <v>0.174562420465804</v>
       </c>
       <c r="Q188" t="n">
-        <v>8.24423835337383</v>
+        <v>8.2416965644134</v>
       </c>
       <c r="R188" t="n">
-        <v>3.83249261290603</v>
+        <v>3.83070468468648</v>
       </c>
       <c r="S188" t="n">
         <v>-2.6</v>
@@ -29603,13 +29603,13 @@
         <v>412</v>
       </c>
       <c r="K189" t="n">
-        <v>40.1040934543865</v>
+        <v>40.2888953304916</v>
       </c>
       <c r="L189" t="n">
-        <v>44.3490022172949</v>
+        <v>44.5465478841871</v>
       </c>
       <c r="M189" t="n">
-        <v>-9.57159924841094</v>
+        <v>-9.55776093978055</v>
       </c>
       <c r="N189" t="s">
         <v>70</v>
@@ -29621,10 +29621,10 @@
         <v>0.175547411606377</v>
       </c>
       <c r="Q189" t="n">
-        <v>15.1274364551541</v>
+        <v>15.1952772106215</v>
       </c>
       <c r="R189" t="n">
-        <v>6.71327115006486</v>
+        <v>6.74430498757563</v>
       </c>
       <c r="S189" t="n">
         <v>-3.7</v>
@@ -29753,13 +29753,13 @@
         <v>426</v>
       </c>
       <c r="K190" t="n">
-        <v>143.646033234817</v>
+        <v>143.622564691924</v>
       </c>
       <c r="L190" t="n">
         <v>169.79117147708</v>
       </c>
       <c r="M190" t="n">
-        <v>-15.3984085360952</v>
+        <v>-15.4122305403191</v>
       </c>
       <c r="N190" t="s">
         <v>70</v>
@@ -29771,10 +29771,10 @@
         <v>0.188715143005266</v>
       </c>
       <c r="Q190" t="n">
-        <v>56.9472598797364</v>
+        <v>56.9339996100045</v>
       </c>
       <c r="R190" t="n">
-        <v>26.3177767763144</v>
+        <v>26.3116158295548</v>
       </c>
       <c r="S190" t="n">
         <v>-5.4</v>
@@ -29903,13 +29903,13 @@
         <v>430</v>
       </c>
       <c r="K191" t="n">
-        <v>3.36342057741453</v>
+        <v>3.36288141963488</v>
       </c>
       <c r="L191" t="n">
-        <v>3.00459666516449</v>
+        <v>3.00477721359252</v>
       </c>
       <c r="M191" t="n">
-        <v>11.9424985193609</v>
+        <v>11.9178288633988</v>
       </c>
       <c r="N191" t="s">
         <v>70</v>
@@ -29921,10 +29921,10 @@
         <v>0.185716487376662</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.7825335516116</v>
+        <v>1.782093407645</v>
       </c>
       <c r="R191" t="n">
-        <v>1.2877989970071</v>
+        <v>1.28755616843643</v>
       </c>
       <c r="S191" t="n">
         <v>0</v>
@@ -30053,13 +30053,13 @@
         <v>144</v>
       </c>
       <c r="K192" t="n">
-        <v>3.89579103972251</v>
+        <v>3.89496481685305</v>
       </c>
       <c r="L192" t="n">
-        <v>4.87012417823229</v>
+        <v>4.86917571449438</v>
       </c>
       <c r="M192" t="n">
-        <v>-20.0063304928588</v>
+        <v>-20.0077170092945</v>
       </c>
       <c r="N192" t="s">
         <v>56</v>
@@ -30071,10 +30071,10 @@
         <v>0.186456574546621</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.97625109859407</v>
+        <v>1.97573774526507</v>
       </c>
       <c r="R192" t="n">
-        <v>1.36865239672122</v>
+        <v>1.3683380042648</v>
       </c>
       <c r="S192" t="n">
         <v>0</v>
@@ -30203,13 +30203,13 @@
         <v>407</v>
       </c>
       <c r="K193" t="n">
-        <v>4.19514619376521</v>
+        <v>4.19436631113361</v>
       </c>
       <c r="L193" t="n">
-        <v>3.9992002239373</v>
+        <v>3.99856063332134</v>
       </c>
       <c r="M193" t="n">
-        <v>4.89962889717495</v>
+        <v>4.89690405543821</v>
       </c>
       <c r="N193" t="s">
         <v>70</v>
@@ -30221,10 +30221,10 @@
         <v>0.196880857489732</v>
       </c>
       <c r="Q193" t="n">
-        <v>2.08363077033339</v>
+        <v>2.08312341168658</v>
       </c>
       <c r="R193" t="n">
-        <v>1.41639390930227</v>
+        <v>1.41604552320531</v>
       </c>
       <c r="S193" t="n">
         <v>-0.2</v>
@@ -30353,13 +30353,13 @@
         <v>65</v>
       </c>
       <c r="K194" t="n">
-        <v>7.61699041896023</v>
+        <v>7.61943507708455</v>
       </c>
       <c r="L194" t="n">
-        <v>8.18061349693252</v>
+        <v>8.17392725786678</v>
       </c>
       <c r="M194" t="n">
-        <v>-6.88974094893528</v>
+        <v>-6.7836691383395</v>
       </c>
       <c r="N194" t="s">
         <v>56</v>
@@ -30371,10 +30371,10 @@
         <v>0.232633017434707</v>
       </c>
       <c r="Q194" t="n">
-        <v>3.60951895406199</v>
+        <v>3.61095607611628</v>
       </c>
       <c r="R194" t="n">
-        <v>2.19150078367868</v>
+        <v>2.19179981989417</v>
       </c>
       <c r="S194" t="n">
         <v>-1</v>
@@ -30489,13 +30489,13 @@
         <v>405</v>
       </c>
       <c r="K195" t="n">
-        <v>31.8572194879379</v>
+        <v>31.9796050941019</v>
       </c>
       <c r="L195" t="n">
-        <v>28.6802408947519</v>
+        <v>28.8124459809853</v>
       </c>
       <c r="M195" t="n">
-        <v>11.0772381753853</v>
+        <v>10.9923298952362</v>
       </c>
       <c r="N195" t="s">
         <v>134</v>
@@ -30507,10 +30507,10 @@
         <v>0.232633017434707</v>
       </c>
       <c r="Q195" t="n">
-        <v>14.2133186407331</v>
+        <v>14.274482813462</v>
       </c>
       <c r="R195" t="n">
-        <v>7.87339394456099</v>
+        <v>7.9067056894848</v>
       </c>
       <c r="S195" t="n">
         <v>-3.2</v>
@@ -30629,13 +30629,13 @@
         <v>412</v>
       </c>
       <c r="K196" t="n">
-        <v>34.5141900059116</v>
+        <v>34.4996595523164</v>
       </c>
       <c r="L196" t="n">
         <v>25.3891850723534</v>
       </c>
       <c r="M196" t="n">
-        <v>35.9405191917505</v>
+        <v>35.8832883135091</v>
       </c>
       <c r="N196" t="s">
         <v>70</v>
@@ -30647,10 +30647,10 @@
         <v>0.196868306180608</v>
       </c>
       <c r="Q196" t="n">
-        <v>14.5889183203442</v>
+        <v>14.5858130257943</v>
       </c>
       <c r="R196" t="n">
-        <v>7.59879875732716</v>
+        <v>7.59473868620113</v>
       </c>
       <c r="S196" t="n">
         <v>-3.3</v>
@@ -30779,13 +30779,13 @@
         <v>437</v>
       </c>
       <c r="K197" t="n">
-        <v>80.3682168403628</v>
+        <v>80.3488026926726</v>
       </c>
       <c r="L197" t="n">
         <v>97.951028403526</v>
       </c>
       <c r="M197" t="n">
-        <v>-17.9506145568251</v>
+        <v>-17.970434815996</v>
       </c>
       <c r="N197" t="s">
         <v>70</v>
@@ -30797,10 +30797,10 @@
         <v>0.185433000216354</v>
       </c>
       <c r="Q197" t="n">
-        <v>34.2105177079708</v>
+        <v>34.2005774961477</v>
       </c>
       <c r="R197" t="n">
-        <v>17.5527211421426</v>
+        <v>17.5420199161073</v>
       </c>
       <c r="S197" t="n">
         <v>-4.1</v>
@@ -30929,13 +30929,13 @@
         <v>412</v>
       </c>
       <c r="K198" t="n">
-        <v>282.980864543069</v>
+        <v>282.932584596311</v>
       </c>
       <c r="L198" t="n">
         <v>196.479371316306</v>
       </c>
       <c r="M198" t="n">
-        <v>44.0257379933827</v>
+        <v>44.0011654662852</v>
       </c>
       <c r="N198" t="s">
         <v>70</v>
@@ -30947,10 +30947,10 @@
         <v>0.197792001316156</v>
       </c>
       <c r="Q198" t="n">
-        <v>126.855897380499</v>
+        <v>126.828261737371</v>
       </c>
       <c r="R198" t="n">
-        <v>66.9881855326774</v>
+        <v>66.9691987197235</v>
       </c>
       <c r="S198" t="n">
         <v>-6.2</v>
@@ -31079,13 +31079,13 @@
         <v>443</v>
       </c>
       <c r="K199" t="n">
-        <v>1.97037537845439</v>
+        <v>1.96999855644682</v>
       </c>
       <c r="L199" t="n">
-        <v>2.1412696713414</v>
+        <v>2.14108630028474</v>
       </c>
       <c r="M199" t="n">
-        <v>-7.98097947093015</v>
+        <v>-7.99069817107155</v>
       </c>
       <c r="N199" t="s">
         <v>70</v>
@@ -31097,10 +31097,10 @@
         <v>0.203170498775645</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.3057371187078</v>
+        <v>1.30557762390839</v>
       </c>
       <c r="R199" t="n">
-        <v>1.12317635774197</v>
+        <v>1.1230736285259</v>
       </c>
       <c r="S199" t="n">
         <v>1.5</v>
@@ -31229,13 +31229,13 @@
         <v>445</v>
       </c>
       <c r="K200" t="n">
-        <v>5.38445558082081</v>
+        <v>5.38337497846799</v>
       </c>
       <c r="L200" t="n">
-        <v>5.00615708064274</v>
+        <v>5.00515489715229</v>
       </c>
       <c r="M200" t="n">
-        <v>7.55666460488904</v>
+        <v>7.55661091589559</v>
       </c>
       <c r="N200" t="s">
         <v>70</v>
@@ -31247,10 +31247,10 @@
         <v>0.170993446779269</v>
       </c>
       <c r="Q200" t="n">
-        <v>2.2666047988546</v>
+        <v>2.26604557323042</v>
       </c>
       <c r="R200" t="n">
-        <v>1.51124545333208</v>
+        <v>1.51083623659464</v>
       </c>
       <c r="S200" t="n">
         <v>-1.5</v>
@@ -31379,13 +31379,13 @@
         <v>426</v>
       </c>
       <c r="K201" t="n">
-        <v>10.7017134846164</v>
+        <v>10.7002924240257</v>
       </c>
       <c r="L201" t="n">
         <v>11.0056124133377</v>
       </c>
       <c r="M201" t="n">
-        <v>-2.76130866059748</v>
+        <v>-2.77422080521361</v>
       </c>
       <c r="N201" t="s">
         <v>70</v>
@@ -31397,10 +31397,10 @@
         <v>0.17369004545643</v>
       </c>
       <c r="Q201" t="n">
-        <v>4.16454842586716</v>
+        <v>4.16325154569152</v>
       </c>
       <c r="R201" t="n">
-        <v>2.34980248210553</v>
+        <v>2.34874312489469</v>
       </c>
       <c r="S201" t="n">
         <v>-2.3</v>
@@ -31529,13 +31529,13 @@
         <v>448</v>
       </c>
       <c r="K202" t="n">
-        <v>14.7395645029865</v>
+        <v>14.7345909788989</v>
       </c>
       <c r="L202" t="n">
-        <v>14.8445895799317</v>
+        <v>14.8357810413885</v>
       </c>
       <c r="M202" t="n">
-        <v>-0.707497343592478</v>
+        <v>-0.682067645830597</v>
       </c>
       <c r="N202" t="s">
         <v>70</v>
@@ -31547,10 +31547,10 @@
         <v>0.186427572711682</v>
       </c>
       <c r="Q202" t="n">
-        <v>5.7524261859231</v>
+        <v>5.75043458851813</v>
       </c>
       <c r="R202" t="n">
-        <v>3.15369043336825</v>
+        <v>3.15199308717938</v>
       </c>
       <c r="S202" t="n">
         <v>-2.7</v>
@@ -31679,13 +31679,13 @@
         <v>450</v>
       </c>
       <c r="K203" t="n">
-        <v>15.2438538018705</v>
+        <v>15.2421135803311</v>
       </c>
       <c r="L203" t="n">
-        <v>12.3268827807223</v>
+        <v>12.3208081803622</v>
       </c>
       <c r="M203" t="n">
-        <v>23.6634928151501</v>
+        <v>23.7103391044191</v>
       </c>
       <c r="N203" t="s">
         <v>70</v>
@@ -31697,10 +31697,10 @@
         <v>0.176908415355309</v>
       </c>
       <c r="Q203" t="n">
-        <v>5.86965428822427</v>
+        <v>5.8675470305344</v>
       </c>
       <c r="R203" t="n">
-        <v>3.22565161194963</v>
+        <v>3.22408929176354</v>
       </c>
       <c r="S203" t="n">
         <v>-3</v>
@@ -31829,13 +31829,13 @@
         <v>452</v>
       </c>
       <c r="K204" t="n">
-        <v>25.3469245222577</v>
+        <v>25.4641466030264</v>
       </c>
       <c r="L204" t="n">
-        <v>23.9310839913855</v>
+        <v>24.0230602930579</v>
       </c>
       <c r="M204" t="n">
-        <v>5.91632427257318</v>
+        <v>5.99876240740618</v>
       </c>
       <c r="N204" t="s">
         <v>70</v>
@@ -31847,10 +31847,10 @@
         <v>0.191024367078196</v>
       </c>
       <c r="Q204" t="n">
-        <v>9.82765958487944</v>
+        <v>9.86894412182788</v>
       </c>
       <c r="R204" t="n">
-        <v>5.22876261459097</v>
+        <v>5.25306374552246</v>
       </c>
       <c r="S204" t="n">
         <v>-3.5</v>
@@ -31979,13 +31979,13 @@
         <v>412</v>
       </c>
       <c r="K205" t="n">
-        <v>27.3880503445247</v>
+        <v>27.3849076272774</v>
       </c>
       <c r="L205" t="n">
         <v>22.348156424581</v>
       </c>
       <c r="M205" t="n">
-        <v>22.5517211540556</v>
+        <v>22.5376586193768</v>
       </c>
       <c r="N205" t="s">
         <v>70</v>
@@ -31997,10 +31997,10 @@
         <v>0.177473590226765</v>
       </c>
       <c r="Q205" t="n">
-        <v>10.3182939458503</v>
+        <v>10.31554684302</v>
       </c>
       <c r="R205" t="n">
-        <v>5.41810947111723</v>
+        <v>5.41515633867157</v>
       </c>
       <c r="S205" t="n">
         <v>-3.8</v>
@@ -32129,13 +32129,13 @@
         <v>423</v>
       </c>
       <c r="K206" t="n">
-        <v>255.74765739614</v>
+        <v>255.730074379915</v>
       </c>
       <c r="L206" t="n">
         <v>136.065306122449</v>
       </c>
       <c r="M206" t="n">
-        <v>87.9594914268487</v>
+        <v>87.9465689437221</v>
       </c>
       <c r="N206" t="s">
         <v>70</v>
@@ -32147,10 +32147,10 @@
         <v>0.176420293632951</v>
       </c>
       <c r="Q206" t="n">
-        <v>100.380198395238</v>
+        <v>100.367868360571</v>
       </c>
       <c r="R206" t="n">
-        <v>51.3490977762865</v>
+        <v>51.3214341112059</v>
       </c>
       <c r="S206" t="n">
         <v>-7.4</v>
@@ -32279,13 +32279,13 @@
         <v>458</v>
       </c>
       <c r="K207" t="n">
-        <v>1.79811694311266</v>
+        <v>1.79750854384682</v>
       </c>
       <c r="L207" t="n">
-        <v>2.37250017792328</v>
+        <v>2.3718249733191</v>
       </c>
       <c r="M207" t="n">
-        <v>-24.2100396937967</v>
+        <v>-24.2141151194891</v>
       </c>
       <c r="N207" t="s">
         <v>70</v>
@@ -32297,10 +32297,10 @@
         <v>0.188190522008761</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.25650798458323</v>
+        <v>1.25626016770054</v>
       </c>
       <c r="R207" t="n">
-        <v>1.11415469543619</v>
+        <v>1.11407835205362</v>
       </c>
       <c r="S207" t="n">
         <v>2.8</v>
@@ -32429,13 +32429,13 @@
         <v>460</v>
       </c>
       <c r="K208" t="n">
-        <v>11.0093508986232</v>
+        <v>11.0077499345496</v>
       </c>
       <c r="L208" t="n">
-        <v>8.90781152578605</v>
+        <v>8.89355269008448</v>
       </c>
       <c r="M208" t="n">
-        <v>23.5920951712288</v>
+        <v>23.7722462343115</v>
       </c>
       <c r="N208" t="s">
         <v>70</v>
@@ -32447,10 +32447,10 @@
         <v>0.178984129528918</v>
       </c>
       <c r="Q208" t="n">
-        <v>4.06946191261038</v>
+        <v>4.06915641011798</v>
       </c>
       <c r="R208" t="n">
-        <v>2.41147532612271</v>
+        <v>2.41071236793513</v>
       </c>
       <c r="S208" t="n">
         <v>-2.8</v>
@@ -32579,13 +32579,13 @@
         <v>412</v>
       </c>
       <c r="K209" t="n">
-        <v>14.3266683027487</v>
+        <v>14.3208896497051</v>
       </c>
       <c r="L209" t="n">
-        <v>10.3410195429635</v>
+        <v>10.3367441860465</v>
       </c>
       <c r="M209" t="n">
-        <v>38.5421257858197</v>
+        <v>38.5435238789869</v>
       </c>
       <c r="N209" t="s">
         <v>70</v>
@@ -32597,10 +32597,10 @@
         <v>0.17352800491969</v>
       </c>
       <c r="Q209" t="n">
-        <v>5.23514410179231</v>
+        <v>5.23169910496615</v>
       </c>
       <c r="R209" t="n">
-        <v>3.00150590181668</v>
+        <v>2.99925784334925</v>
       </c>
       <c r="S209" t="n">
         <v>-3.3</v>
@@ -32729,13 +32729,13 @@
         <v>463</v>
       </c>
       <c r="K210" t="n">
-        <v>14.9941516607892</v>
+        <v>15.0643354023178</v>
       </c>
       <c r="L210" t="n">
-        <v>10.508353472733</v>
+        <v>10.5549340369393</v>
       </c>
       <c r="M210" t="n">
-        <v>42.6879263216255</v>
+        <v>42.7231600841542</v>
       </c>
       <c r="N210" t="s">
         <v>70</v>
@@ -32747,10 +32747,10 @@
         <v>0.174989987675964</v>
       </c>
       <c r="Q210" t="n">
-        <v>5.55086820318103</v>
+        <v>5.57156215881706</v>
       </c>
       <c r="R210" t="n">
-        <v>3.18005904908674</v>
+        <v>3.19249242195306</v>
       </c>
       <c r="S210" t="n">
         <v>-3.4</v>
@@ -32879,13 +32879,13 @@
         <v>465</v>
       </c>
       <c r="K211" t="n">
-        <v>15.3706394299929</v>
+        <v>15.3650603532867</v>
       </c>
       <c r="L211" t="n">
         <v>17.9902860226659</v>
       </c>
       <c r="M211" t="n">
-        <v>-14.5614504926299</v>
+        <v>-14.5924620991115</v>
       </c>
       <c r="N211" t="s">
         <v>134</v>
@@ -32897,10 +32897,10 @@
         <v>0.215681772259698</v>
       </c>
       <c r="Q211" t="n">
-        <v>5.71226392200966</v>
+        <v>5.70807873292118</v>
       </c>
       <c r="R211" t="n">
-        <v>3.2952214883952</v>
+        <v>3.29305091397045</v>
       </c>
       <c r="S211" t="n">
         <v>-3</v>
@@ -33019,13 +33019,13 @@
         <v>467</v>
       </c>
       <c r="K212" t="n">
-        <v>15.8869890486814</v>
+        <v>15.8769320130346</v>
       </c>
       <c r="L212" t="n">
-        <v>10.6766307248852</v>
+        <v>10.66752</v>
       </c>
       <c r="M212" t="n">
-        <v>48.8015222972148</v>
+        <v>48.8343308757297</v>
       </c>
       <c r="N212" t="s">
         <v>70</v>
@@ -33037,10 +33037,10 @@
         <v>0.18084127285078</v>
       </c>
       <c r="Q212" t="n">
-        <v>5.91813863848876</v>
+        <v>5.9152607031684</v>
       </c>
       <c r="R212" t="n">
-        <v>3.3731150919961</v>
+        <v>3.37061074440635</v>
       </c>
       <c r="S212" t="n">
         <v>-3.5</v>
@@ -33169,13 +33169,13 @@
         <v>469</v>
       </c>
       <c r="K213" t="n">
-        <v>17.3368980397765</v>
+        <v>17.3335937135058</v>
       </c>
       <c r="L213" t="n">
-        <v>11.7532024914796</v>
+        <v>11.7504406062742</v>
       </c>
       <c r="M213" t="n">
-        <v>47.5078647912747</v>
+        <v>47.5144149424529</v>
       </c>
       <c r="N213" t="s">
         <v>70</v>
@@ -33187,10 +33187,10 @@
         <v>0.174429391711906</v>
       </c>
       <c r="Q213" t="n">
-        <v>6.38067104102166</v>
+        <v>6.37586172991678</v>
       </c>
       <c r="R213" t="n">
-        <v>3.57979815554514</v>
+        <v>3.57709800676741</v>
       </c>
       <c r="S213" t="n">
         <v>-3.6</v>
@@ -33319,13 +33319,13 @@
         <v>471</v>
       </c>
       <c r="K214" t="n">
-        <v>32.4106413482609</v>
+        <v>32.4036929263119</v>
       </c>
       <c r="L214" t="n">
-        <v>24.9707865168539</v>
+        <v>24.9832625530852</v>
       </c>
       <c r="M214" t="n">
-        <v>29.7942350609802</v>
+        <v>29.701606655494</v>
       </c>
       <c r="N214" t="s">
         <v>70</v>
@@ -33337,10 +33337,10 @@
         <v>0.176849415013767</v>
       </c>
       <c r="Q214" t="n">
-        <v>11.5627279418709</v>
+        <v>11.5575008133315</v>
       </c>
       <c r="R214" t="n">
-        <v>6.21612068738765</v>
+        <v>6.2102893405311</v>
       </c>
       <c r="S214" t="n">
         <v>-4.3</v>
@@ -33469,13 +33469,13 @@
         <v>450</v>
       </c>
       <c r="K215" t="n">
-        <v>2.65698056754335</v>
+        <v>2.66526957660431</v>
       </c>
       <c r="L215" t="n">
-        <v>3.51979727589484</v>
+        <v>3.53247854190951</v>
       </c>
       <c r="M215" t="n">
-        <v>-24.5132500743848</v>
+        <v>-24.5495890496315</v>
       </c>
       <c r="N215" t="s">
         <v>134</v>
@@ -33487,10 +33487,10 @@
         <v>0.181207132599753</v>
       </c>
       <c r="Q215" t="n">
-        <v>1.60148309612092</v>
+        <v>1.60502141771495</v>
       </c>
       <c r="R215" t="n">
-        <v>1.28126028700833</v>
+        <v>1.2830721409513</v>
       </c>
       <c r="S215" t="n">
         <v>1.6</v>
@@ -33619,13 +33619,13 @@
         <v>476</v>
       </c>
       <c r="K216" t="n">
-        <v>7.73162055803664</v>
+        <v>7.71906637480456</v>
       </c>
       <c r="L216" t="n">
-        <v>7.32391065543757</v>
+        <v>7.31748006146192</v>
       </c>
       <c r="M216" t="n">
-        <v>5.56683337332042</v>
+        <v>5.48804110116579</v>
       </c>
       <c r="N216" t="s">
         <v>70</v>
@@ -33637,10 +33637,10 @@
         <v>0.18811847909317</v>
       </c>
       <c r="Q216" t="n">
-        <v>3.57132225700408</v>
+        <v>3.56811862210962</v>
       </c>
       <c r="R216" t="n">
-        <v>2.29075607588825</v>
+        <v>2.28970366273487</v>
       </c>
       <c r="S216" t="n">
         <v>-1.6</v>
@@ -33769,13 +33769,13 @@
         <v>478</v>
       </c>
       <c r="K217" t="n">
-        <v>7.89773696205342</v>
+        <v>7.88294492797294</v>
       </c>
       <c r="L217" t="n">
-        <v>5.43079011675265</v>
+        <v>5.42313323572474</v>
       </c>
       <c r="M217" t="n">
-        <v>45.4251921408424</v>
+        <v>45.3577587960454</v>
       </c>
       <c r="N217" t="s">
         <v>70</v>
@@ -33787,10 +33787,10 @@
         <v>0.182546182482874</v>
       </c>
       <c r="Q217" t="n">
-        <v>3.73851004371893</v>
+        <v>3.73467048218772</v>
       </c>
       <c r="R217" t="n">
-        <v>2.41765853942883</v>
+        <v>2.41668736310773</v>
       </c>
       <c r="S217" t="n">
         <v>-2</v>
@@ -33919,13 +33919,13 @@
         <v>476</v>
       </c>
       <c r="K218" t="n">
-        <v>9.82346800006635</v>
+        <v>9.80438644866946</v>
       </c>
       <c r="L218" t="n">
-        <v>9.99780065980206</v>
+        <v>9.97984233110468</v>
       </c>
       <c r="M218" t="n">
-        <v>-1.74371009852839</v>
+        <v>-1.75810274966337</v>
       </c>
       <c r="N218" t="s">
         <v>70</v>
@@ -33937,10 +33937,10 @@
         <v>0.18811847909317</v>
       </c>
       <c r="Q218" t="n">
-        <v>4.4660708724233</v>
+        <v>4.46099152610691</v>
       </c>
       <c r="R218" t="n">
-        <v>2.76982863017811</v>
+        <v>2.76852512427627</v>
       </c>
       <c r="S218" t="n">
         <v>-1.9</v>
@@ -34069,13 +34069,13 @@
         <v>463</v>
       </c>
       <c r="K219" t="n">
-        <v>11.8360358537595</v>
+        <v>11.8149595022957</v>
       </c>
       <c r="L219" t="n">
-        <v>9.73503358317921</v>
+        <v>9.72367525522606</v>
       </c>
       <c r="M219" t="n">
-        <v>21.5818697760897</v>
+        <v>21.5071379100783</v>
       </c>
       <c r="N219" t="s">
         <v>70</v>
@@ -34087,10 +34087,10 @@
         <v>0.171945512109682</v>
       </c>
       <c r="Q219" t="n">
-        <v>5.28142269543887</v>
+        <v>5.27689193109189</v>
       </c>
       <c r="R219" t="n">
-        <v>3.20702690227749</v>
+        <v>3.20555165813249</v>
       </c>
       <c r="S219" t="n">
         <v>-2.3</v>
@@ -34219,13 +34219,13 @@
         <v>482</v>
       </c>
       <c r="K220" t="n">
-        <v>12.4319397451354</v>
+        <v>12.4074192009046</v>
       </c>
       <c r="L220" t="n">
-        <v>14.0480404551201</v>
+        <v>14.0322716430476</v>
       </c>
       <c r="M220" t="n">
-        <v>-11.5041006263308</v>
+        <v>-11.579397003393</v>
       </c>
       <c r="N220" t="s">
         <v>70</v>
@@ -34237,10 +34237,10 @@
         <v>0.169866924461876</v>
       </c>
       <c r="Q220" t="n">
-        <v>5.45823534145809</v>
+        <v>5.45233975147733</v>
       </c>
       <c r="R220" t="n">
-        <v>3.26335522018576</v>
+        <v>3.26158885164882</v>
       </c>
       <c r="S220" t="n">
         <v>-2.1</v>
@@ -34369,13 +34369,13 @@
         <v>478</v>
       </c>
       <c r="K221" t="n">
-        <v>12.9117292460095</v>
+        <v>12.8826240209978</v>
       </c>
       <c r="L221" t="n">
-        <v>11.4727543879775</v>
+        <v>11.4491127647396</v>
       </c>
       <c r="M221" t="n">
-        <v>12.54254043423</v>
+        <v>12.5207191658824</v>
       </c>
       <c r="N221" t="s">
         <v>70</v>
@@ -34387,10 +34387,10 @@
         <v>0.1685793373242</v>
       </c>
       <c r="Q221" t="n">
-        <v>5.63972411423054</v>
+        <v>5.63489777556186</v>
       </c>
       <c r="R221" t="n">
-        <v>3.39519400121233</v>
+        <v>3.39324446559406</v>
       </c>
       <c r="S221" t="n">
         <v>-2.4</v>
@@ -34519,13 +34519,13 @@
         <v>418</v>
       </c>
       <c r="K222" t="n">
-        <v>42.5465546817227</v>
+        <v>42.4746771486682</v>
       </c>
       <c r="L222" t="n">
-        <v>29.3020802812775</v>
+        <v>29.2335574393452</v>
       </c>
       <c r="M222" t="n">
-        <v>45.1997751467078</v>
+        <v>45.294246985835</v>
       </c>
       <c r="N222" t="s">
         <v>70</v>
@@ -34537,10 +34537,10 @@
         <v>0.169706732998836</v>
       </c>
       <c r="Q222" t="n">
-        <v>18.4135603457647</v>
+        <v>18.3855762813115</v>
       </c>
       <c r="R222" t="n">
-        <v>10.4665444532005</v>
+        <v>10.4570651876894</v>
       </c>
       <c r="S222" t="n">
         <v>-4.2</v>
@@ -34669,13 +34669,13 @@
         <v>488</v>
       </c>
       <c r="K223" t="n">
-        <v>1.78975784205403</v>
+        <v>1.78901038120346</v>
       </c>
       <c r="L223" t="n">
-        <v>2.18381919423518</v>
+        <v>2.18343776608519</v>
       </c>
       <c r="M223" t="n">
-        <v>-18.0445960554514</v>
+        <v>-18.0645123487502</v>
       </c>
       <c r="N223" t="s">
         <v>70</v>
@@ -34687,10 +34687,10 @@
         <v>0.1724676050814</v>
       </c>
       <c r="Q223" t="n">
-        <v>1.19569159242616</v>
+        <v>1.19539989029947</v>
       </c>
       <c r="R223" t="n">
-        <v>1.06548828491553</v>
+        <v>1.06541695839863</v>
       </c>
       <c r="S223" t="n">
         <v>1.5</v>
@@ -34819,13 +34819,13 @@
         <v>476</v>
       </c>
       <c r="K224" t="n">
-        <v>4.22821027045987</v>
+        <v>4.22701113817273</v>
       </c>
       <c r="L224" t="n">
-        <v>3.25028437713283</v>
+        <v>3.24943951652208</v>
       </c>
       <c r="M224" t="n">
-        <v>30.087394820194</v>
+        <v>30.0843150543378</v>
       </c>
       <c r="N224" t="s">
         <v>70</v>
@@ -34837,10 +34837,10 @@
         <v>0.171798614809405</v>
       </c>
       <c r="Q224" t="n">
-        <v>1.71646148983677</v>
+        <v>1.71516234979349</v>
       </c>
       <c r="R224" t="n">
-        <v>1.23771467962075</v>
+        <v>1.23724446581121</v>
       </c>
       <c r="S224" t="n">
         <v>-1.5</v>
@@ -34969,13 +34969,13 @@
         <v>407</v>
       </c>
       <c r="K225" t="n">
-        <v>13.8993582925716</v>
+        <v>13.9670049920436</v>
       </c>
       <c r="L225" t="n">
-        <v>14.3257412978083</v>
+        <v>14.3627746660922</v>
       </c>
       <c r="M225" t="n">
-        <v>-2.97634165222581</v>
+        <v>-2.75552379849634</v>
       </c>
       <c r="N225" t="s">
         <v>134</v>
@@ -34987,10 +34987,10 @@
         <v>0.216150844783042</v>
       </c>
       <c r="Q225" t="n">
-        <v>5.13463619744257</v>
+        <v>5.15931050081523</v>
       </c>
       <c r="R225" t="n">
-        <v>2.52575934723138</v>
+        <v>2.53507275546193</v>
       </c>
       <c r="S225" t="n">
         <v>-3</v>
@@ -35109,13 +35109,13 @@
         <v>492</v>
       </c>
       <c r="K226" t="n">
-        <v>26.0612516696833</v>
+        <v>26.0493122274204</v>
       </c>
       <c r="L226" t="n">
-        <v>22.5091154625253</v>
+        <v>22.4989876265467</v>
       </c>
       <c r="M226" t="n">
-        <v>15.7808786981072</v>
+        <v>15.779930456447</v>
       </c>
       <c r="N226" t="s">
         <v>70</v>
@@ -35127,10 +35127,10 @@
         <v>0.177056724029938</v>
       </c>
       <c r="Q226" t="n">
-        <v>8.83956039578594</v>
+        <v>8.83250316336939</v>
       </c>
       <c r="R226" t="n">
-        <v>4.01739123183965</v>
+        <v>4.0126225360701</v>
       </c>
       <c r="S226" t="n">
         <v>-3.8</v>
@@ -35259,13 +35259,13 @@
         <v>426</v>
       </c>
       <c r="K227" t="n">
-        <v>32.4134231371539</v>
+        <v>32.3973083596543</v>
       </c>
       <c r="L227" t="n">
         <v>26.9636020490698</v>
       </c>
       <c r="M227" t="n">
-        <v>20.2117694741458</v>
+        <v>20.1520045455942</v>
       </c>
       <c r="N227" t="s">
         <v>70</v>
@@ -35277,10 +35277,10 @@
         <v>0.17284540997986</v>
       </c>
       <c r="Q227" t="n">
-        <v>10.8871623737473</v>
+        <v>10.8798374350678</v>
       </c>
       <c r="R227" t="n">
-        <v>4.88160733807067</v>
+        <v>4.87488313601576</v>
       </c>
       <c r="S227" t="n">
         <v>-4.2</v>
@@ -35409,13 +35409,13 @@
         <v>495</v>
       </c>
       <c r="K228" t="n">
-        <v>41.0999020643144</v>
+        <v>41.0902668609316</v>
       </c>
       <c r="L228" t="n">
         <v>36.1692585895118</v>
       </c>
       <c r="M228" t="n">
-        <v>13.6321386367383</v>
+        <v>13.6054994305215</v>
       </c>
       <c r="N228" t="s">
         <v>70</v>
@@ -35427,10 +35427,10 @@
         <v>0.216150844783042</v>
       </c>
       <c r="Q228" t="n">
-        <v>15.5965350700522</v>
+        <v>15.5873953319713</v>
       </c>
       <c r="R228" t="n">
-        <v>7.43888023804596</v>
+        <v>7.42853087930555</v>
       </c>
       <c r="S228" t="n">
         <v>-4.7</v>
@@ -35549,13 +35549,13 @@
         <v>497</v>
       </c>
       <c r="K229" t="n">
-        <v>43.2550434224989</v>
+        <v>43.2450647473713</v>
       </c>
       <c r="L229" t="n">
         <v>29.8798924409919</v>
       </c>
       <c r="M229" t="n">
-        <v>44.7630492911605</v>
+        <v>44.7296533371846</v>
       </c>
       <c r="N229" t="s">
         <v>70</v>
@@ -35567,10 +35567,10 @@
         <v>0.166171592745999</v>
       </c>
       <c r="Q229" t="n">
-        <v>14.4472403867145</v>
+        <v>14.4340684512149</v>
       </c>
       <c r="R229" t="n">
-        <v>6.3217292004051</v>
+        <v>6.31463688362892</v>
       </c>
       <c r="S229" t="n">
         <v>-4.8</v>
@@ -35699,13 +35699,13 @@
         <v>499</v>
       </c>
       <c r="K230" t="n">
-        <v>61.955824275841</v>
+        <v>61.9406754161051</v>
       </c>
       <c r="L230" t="n">
         <v>45.4788540245566</v>
       </c>
       <c r="M230" t="n">
-        <v>36.2299591858394</v>
+        <v>36.1966495080545</v>
       </c>
       <c r="N230" t="s">
         <v>70</v>
@@ -35717,10 +35717,10 @@
         <v>0.167241450127236</v>
       </c>
       <c r="Q230" t="n">
-        <v>20.8329014273164</v>
+        <v>20.8185627520096</v>
       </c>
       <c r="R230" t="n">
-        <v>8.99116717263235</v>
+        <v>8.97975721441214</v>
       </c>
       <c r="S230" t="n">
         <v>-5.2</v>
@@ -35849,13 +35849,13 @@
         <v>476</v>
       </c>
       <c r="K231" t="n">
-        <v>3.26907890783938</v>
+        <v>3.26730783961947</v>
       </c>
       <c r="L231" t="n">
-        <v>3.59108046967575</v>
+        <v>3.59082259164841</v>
       </c>
       <c r="M231" t="n">
-        <v>-8.96670415924843</v>
+        <v>-9.00948859967023</v>
       </c>
       <c r="N231" t="s">
         <v>70</v>
@@ -35867,10 +35867,10 @@
         <v>0.193136876989485</v>
       </c>
       <c r="Q231" t="n">
-        <v>1.80758155130422</v>
+        <v>1.80689202521944</v>
       </c>
       <c r="R231" t="n">
-        <v>1.3549548240865</v>
+        <v>1.35454430982152</v>
       </c>
       <c r="S231" t="n">
         <v>0.5</v>
@@ -35999,13 +35999,13 @@
         <v>504</v>
       </c>
       <c r="K232" t="n">
-        <v>4.36780803099814</v>
+        <v>4.36559746394355</v>
       </c>
       <c r="L232" t="n">
         <v>4.05432359022175</v>
       </c>
       <c r="M232" t="n">
-        <v>7.73210213246049</v>
+        <v>7.67757843682062</v>
       </c>
       <c r="N232" t="s">
         <v>70</v>
@@ -36017,10 +36017,10 @@
         <v>0.169666220804436</v>
       </c>
       <c r="Q232" t="n">
-        <v>2.19459838067693</v>
+        <v>2.19338524660524</v>
       </c>
       <c r="R232" t="n">
-        <v>1.52602868376781</v>
+        <v>1.52529404488189</v>
       </c>
       <c r="S232" t="n">
         <v>-0.5</v>
@@ -36149,13 +36149,13 @@
         <v>65</v>
       </c>
       <c r="K233" t="n">
-        <v>5.1578414573078</v>
+        <v>5.15875166733387</v>
       </c>
       <c r="L233" t="n">
-        <v>6.19666646012764</v>
+        <v>6.18593431063277</v>
       </c>
       <c r="M233" t="n">
-        <v>-16.764255580063</v>
+        <v>-16.6051333835427</v>
       </c>
       <c r="N233" t="s">
         <v>70</v>
@@ -36167,10 +36167,10 @@
         <v>0.216551644970076</v>
       </c>
       <c r="Q233" t="n">
-        <v>2.62084638251945</v>
+        <v>2.62111291242809</v>
       </c>
       <c r="R233" t="n">
-        <v>1.77318486573817</v>
+        <v>1.77296660137091</v>
       </c>
       <c r="S233" t="n">
         <v>-0.6</v>
@@ -36285,13 +36285,13 @@
         <v>507</v>
       </c>
       <c r="K234" t="n">
-        <v>12.6161265421028</v>
+        <v>12.6724031881622</v>
       </c>
       <c r="L234" t="n">
-        <v>9.71045732595398</v>
+        <v>9.73313868613139</v>
       </c>
       <c r="M234" t="n">
-        <v>29.9230934096442</v>
+        <v>30.198526876217</v>
       </c>
       <c r="N234" t="s">
         <v>70</v>
@@ -36303,10 +36303,10 @@
         <v>0.215177694694682</v>
       </c>
       <c r="Q234" t="n">
-        <v>5.84653978050789</v>
+        <v>5.86888313602106</v>
       </c>
       <c r="R234" t="n">
-        <v>3.5468979799726</v>
+        <v>3.56052641242984</v>
       </c>
       <c r="S234" t="n">
         <v>-2.1</v>
@@ -36435,13 +36435,13 @@
         <v>497</v>
       </c>
       <c r="K235" t="n">
-        <v>13.4050350205888</v>
+        <v>13.3966302369054</v>
       </c>
       <c r="L235" t="n">
-        <v>11.0080352228949</v>
+        <v>11.0128840436075</v>
       </c>
       <c r="M235" t="n">
-        <v>21.7750011619562</v>
+        <v>21.6450675759321</v>
       </c>
       <c r="N235" t="s">
         <v>70</v>
@@ -36453,10 +36453,10 @@
         <v>0.168447822580275</v>
       </c>
       <c r="Q235" t="n">
-        <v>5.83163102423831</v>
+        <v>5.82908817683995</v>
       </c>
       <c r="R235" t="n">
-        <v>3.42186871981843</v>
+        <v>3.41985196552311</v>
       </c>
       <c r="S235" t="n">
         <v>-2.1</v>
@@ -36585,13 +36585,13 @@
         <v>412</v>
       </c>
       <c r="K236" t="n">
-        <v>14.3883719546993</v>
+        <v>14.3806340533686</v>
       </c>
       <c r="L236" t="n">
-        <v>17.0983074029749</v>
+        <v>17.1100085543199</v>
       </c>
       <c r="M236" t="n">
-        <v>-15.8491445054035</v>
+        <v>-15.9519178046364</v>
       </c>
       <c r="N236" t="s">
         <v>70</v>
@@ -36603,10 +36603,10 @@
         <v>0.168248716337851</v>
       </c>
       <c r="Q236" t="n">
-        <v>6.3135691767465</v>
+        <v>6.30905264069641</v>
       </c>
       <c r="R236" t="n">
-        <v>3.62480185207921</v>
+        <v>3.62230248659424</v>
       </c>
       <c r="S236" t="n">
         <v>-1.9</v>
@@ -36735,13 +36735,13 @@
         <v>511</v>
       </c>
       <c r="K237" t="n">
-        <v>34.2350621702898</v>
+        <v>34.2206940412495</v>
       </c>
       <c r="L237" t="n">
         <v>26.5625498007968</v>
       </c>
       <c r="M237" t="n">
-        <v>28.8846982952774</v>
+        <v>28.8306066167749</v>
       </c>
       <c r="N237" t="s">
         <v>70</v>
@@ -36753,10 +36753,10 @@
         <v>0.192528697242977</v>
       </c>
       <c r="Q237" t="n">
-        <v>15.2229712403388</v>
+        <v>15.2188555565345</v>
       </c>
       <c r="R237" t="n">
-        <v>8.6736331677049</v>
+        <v>8.66823602120589</v>
       </c>
       <c r="S237" t="n">
         <v>-3.4</v>
@@ -36885,13 +36885,13 @@
         <v>69</v>
       </c>
       <c r="K238" t="n">
-        <v>53.4666713077435</v>
+        <v>53.443805651237</v>
       </c>
       <c r="L238" t="n">
-        <v>42.4662420382166</v>
+        <v>42.4302078913874</v>
       </c>
       <c r="M238" t="n">
-        <v>25.9039386146468</v>
+        <v>25.9569733620966</v>
       </c>
       <c r="N238" t="s">
         <v>70</v>
@@ -36903,10 +36903,10 @@
         <v>0.179709883282015</v>
       </c>
       <c r="Q238" t="n">
-        <v>23.2801329012391</v>
+        <v>23.2688260286124</v>
       </c>
       <c r="R238" t="n">
-        <v>12.9246092478092</v>
+        <v>12.9186045955521</v>
       </c>
       <c r="S238" t="n">
         <v>-4</v>
@@ -37035,13 +37035,13 @@
         <v>516</v>
       </c>
       <c r="K239" t="n">
-        <v>4.0549010031526</v>
+        <v>4.05653145291013</v>
       </c>
       <c r="L239" t="n">
-        <v>5.13783714359106</v>
+        <v>5.13519897304236</v>
       </c>
       <c r="M239" t="n">
-        <v>-21.0776657603739</v>
+        <v>-21.0053695250132</v>
       </c>
       <c r="N239" t="s">
         <v>70</v>
@@ -37053,10 +37053,10 @@
         <v>0.177606160997436</v>
       </c>
       <c r="Q239" t="n">
-        <v>2.18344738731209</v>
+        <v>2.18364803232583</v>
       </c>
       <c r="R239" t="n">
-        <v>1.58172852849766</v>
+        <v>1.58189562377398</v>
       </c>
       <c r="S239" t="n">
         <v>0.4</v>
@@ -37185,13 +37185,13 @@
         <v>518</v>
       </c>
       <c r="K240" t="n">
-        <v>4.89817375253386</v>
+        <v>4.89566579751613</v>
       </c>
       <c r="L240" t="n">
         <v>4.65868542413938</v>
       </c>
       <c r="M240" t="n">
-        <v>5.14068469086904</v>
+        <v>5.08685072722059</v>
       </c>
       <c r="N240" t="s">
         <v>70</v>
@@ -37203,10 +37203,10 @@
         <v>0.173372793804622</v>
       </c>
       <c r="Q240" t="n">
-        <v>2.5162947170135</v>
+        <v>2.51539720426764</v>
       </c>
       <c r="R240" t="n">
-        <v>1.75501364257552</v>
+        <v>1.75444659313199</v>
       </c>
       <c r="S240" t="n">
         <v>-0.4</v>
@@ -37335,13 +37335,13 @@
         <v>460</v>
       </c>
       <c r="K241" t="n">
-        <v>6.34165253925741</v>
+        <v>6.33887656205313</v>
       </c>
       <c r="L241" t="n">
         <v>5.90331149282805</v>
       </c>
       <c r="M241" t="n">
-        <v>7.42534164022863</v>
+        <v>7.37831757233631</v>
       </c>
       <c r="N241" t="s">
         <v>70</v>
@@ -37353,10 +37353,10 @@
         <v>0.183044900313929</v>
       </c>
       <c r="Q241" t="n">
-        <v>3.16609402563931</v>
+        <v>3.16475315728278</v>
       </c>
       <c r="R241" t="n">
-        <v>2.11799033880838</v>
+        <v>2.11701437846577</v>
       </c>
       <c r="S241" t="n">
         <v>-0.8</v>
@@ -37485,13 +37485,13 @@
         <v>521</v>
       </c>
       <c r="K242" t="n">
-        <v>8.97461921857823</v>
+        <v>8.97121992735698</v>
       </c>
       <c r="L242" t="n">
-        <v>9.14400658315809</v>
+        <v>9.14066355908966</v>
       </c>
       <c r="M242" t="n">
-        <v>-1.85244141109701</v>
+        <v>-1.85373447602919</v>
       </c>
       <c r="N242" t="s">
         <v>70</v>
@@ -37503,13 +37503,13 @@
         <v>0.199709303016835</v>
       </c>
       <c r="Q242" t="n">
-        <v>4.42089330392249</v>
+        <v>4.41896021928303</v>
       </c>
       <c r="R242" t="n">
-        <v>2.87382097532278</v>
+        <v>2.87262936371385</v>
       </c>
       <c r="S242" t="n">
-        <v>-1.3</v>
+        <v>-1.2</v>
       </c>
       <c r="T242" t="n">
         <v>99.4246525215036</v>
@@ -37635,13 +37635,13 @@
         <v>437</v>
       </c>
       <c r="K243" t="n">
-        <v>10.9539172031582</v>
+        <v>10.9487352684931</v>
       </c>
       <c r="L243" t="n">
-        <v>8.79036652896194</v>
+        <v>8.788821513314</v>
       </c>
       <c r="M243" t="n">
-        <v>24.6127470005713</v>
+        <v>24.5756925647778</v>
       </c>
       <c r="N243" t="s">
         <v>70</v>
@@ -37653,10 +37653,10 @@
         <v>0.177606160997436</v>
       </c>
       <c r="Q243" t="n">
-        <v>5.20771308287873</v>
+        <v>5.20542413932214</v>
       </c>
       <c r="R243" t="n">
-        <v>3.27424477066379</v>
+        <v>3.2725937250905</v>
       </c>
       <c r="S243" t="n">
         <v>-1.7</v>
@@ -37785,13 +37785,13 @@
         <v>426</v>
       </c>
       <c r="K244" t="n">
-        <v>12.0108708851473</v>
+        <v>12.0051718375544</v>
       </c>
       <c r="L244" t="n">
-        <v>12.9998700116989</v>
+        <v>12.9931142003378</v>
       </c>
       <c r="M244" t="n">
-        <v>-7.6077616596293</v>
+        <v>-7.60358407961756</v>
       </c>
       <c r="N244" t="s">
         <v>70</v>
@@ -37803,10 +37803,10 @@
         <v>0.170067945698638</v>
       </c>
       <c r="Q244" t="n">
-        <v>5.55576670468897</v>
+        <v>5.55341758593862</v>
       </c>
       <c r="R244" t="n">
-        <v>3.44328809821294</v>
+        <v>3.44179246163765</v>
       </c>
       <c r="S244" t="n">
         <v>-1.5</v>
@@ -37935,13 +37935,13 @@
         <v>511</v>
       </c>
       <c r="K245" t="n">
-        <v>17.4602826480372</v>
+        <v>17.5293960311831</v>
       </c>
       <c r="L245" t="n">
-        <v>16.148554819958</v>
+        <v>16.2061254253768</v>
       </c>
       <c r="M245" t="n">
-        <v>8.12288060884598</v>
+        <v>8.16524968845578</v>
       </c>
       <c r="N245" t="s">
         <v>70</v>
@@ -37953,10 +37953,10 @@
         <v>0.173565126025119</v>
       </c>
       <c r="Q245" t="n">
-        <v>8.04469233997158</v>
+        <v>8.07838378700713</v>
       </c>
       <c r="R245" t="n">
-        <v>4.89755642564998</v>
+        <v>4.91802331062506</v>
       </c>
       <c r="S245" t="n">
         <v>-2.2</v>
@@ -38085,13 +38085,13 @@
         <v>412</v>
       </c>
       <c r="K246" t="n">
-        <v>20.7074093965002</v>
+        <v>20.6961213296309</v>
       </c>
       <c r="L246" t="n">
-        <v>16.850547598989</v>
+        <v>16.844871147044</v>
       </c>
       <c r="M246" t="n">
-        <v>22.8886436767344</v>
+        <v>22.8630432905556</v>
       </c>
       <c r="N246" t="s">
         <v>70</v>
@@ -38103,10 +38103,10 @@
         <v>0.168080912316412</v>
       </c>
       <c r="Q246" t="n">
-        <v>9.41334851072812</v>
+        <v>9.41110166046623</v>
       </c>
       <c r="R246" t="n">
-        <v>5.62264717502488</v>
+        <v>5.61980147881245</v>
       </c>
       <c r="S246" t="n">
         <v>-2.5</v>
@@ -38235,13 +38235,13 @@
         <v>405</v>
       </c>
       <c r="K247" t="n">
-        <v>3.93730693719727</v>
+        <v>3.93374598144663</v>
       </c>
       <c r="L247" t="n">
-        <v>4.91560579995085</v>
+        <v>4.90981393293731</v>
       </c>
       <c r="M247" t="n">
-        <v>-19.9018982108647</v>
+        <v>-19.8799377088968</v>
       </c>
       <c r="N247" t="s">
         <v>70</v>
@@ -38253,10 +38253,10 @@
         <v>0.196105466582142</v>
       </c>
       <c r="Q247" t="n">
-        <v>2.16537391212465</v>
+        <v>2.16416151161107</v>
       </c>
       <c r="R247" t="n">
-        <v>1.5925468409951</v>
+        <v>1.59194383656913</v>
       </c>
       <c r="S247" t="n">
         <v>0.8</v>
@@ -38385,13 +38385,13 @@
         <v>460</v>
       </c>
       <c r="K248" t="n">
-        <v>6.35065290550858</v>
+        <v>6.37634601570034</v>
       </c>
       <c r="L248" t="n">
-        <v>5.84807905970411</v>
+        <v>5.86935853043019</v>
       </c>
       <c r="M248" t="n">
-        <v>8.59382783087572</v>
+        <v>8.63786873201955</v>
       </c>
       <c r="N248" t="s">
         <v>70</v>
@@ -38403,10 +38403,10 @@
         <v>0.180091937394646</v>
       </c>
       <c r="Q248" t="n">
-        <v>3.16416385807109</v>
+        <v>3.17647286160964</v>
       </c>
       <c r="R248" t="n">
-        <v>2.12466010074264</v>
+        <v>2.13138346067711</v>
       </c>
       <c r="S248" t="n">
         <v>-0.8</v>
@@ -38535,13 +38535,13 @@
         <v>492</v>
       </c>
       <c r="K249" t="n">
-        <v>6.99152377453606</v>
+        <v>6.98717785882445</v>
       </c>
       <c r="L249" t="n">
-        <v>6.01334856593109</v>
+        <v>6.0111799002224</v>
       </c>
       <c r="M249" t="n">
-        <v>16.2667305558648</v>
+        <v>16.2363791269321</v>
       </c>
       <c r="N249" t="s">
         <v>70</v>
@@ -38553,10 +38553,10 @@
         <v>0.164517817527216</v>
       </c>
       <c r="Q249" t="n">
-        <v>3.40994646340918</v>
+        <v>3.4067744399178</v>
       </c>
       <c r="R249" t="n">
-        <v>2.2513735086371</v>
+        <v>2.2501247918767</v>
       </c>
       <c r="S249" t="n">
         <v>-1</v>
@@ -38685,13 +38685,13 @@
         <v>452</v>
       </c>
       <c r="K250" t="n">
-        <v>7.30164032708513</v>
+        <v>7.29592412709578</v>
       </c>
       <c r="L250" t="n">
-        <v>6.30845896675708</v>
+        <v>6.30448212822291</v>
       </c>
       <c r="M250" t="n">
-        <v>15.7436446137115</v>
+        <v>15.7259863492125</v>
       </c>
       <c r="N250" t="s">
         <v>70</v>
@@ -38703,10 +38703,10 @@
         <v>0.189489506990543</v>
       </c>
       <c r="Q250" t="n">
-        <v>3.62675998776663</v>
+        <v>3.6242380465167</v>
       </c>
       <c r="R250" t="n">
-        <v>2.40916686935359</v>
+        <v>2.40779670232562</v>
       </c>
       <c r="S250" t="n">
         <v>-1.1</v>
@@ -38835,13 +38835,13 @@
         <v>465</v>
       </c>
       <c r="K251" t="n">
-        <v>9.83164061044053</v>
+        <v>9.82394726916247</v>
       </c>
       <c r="L251" t="n">
-        <v>14.5508511567001</v>
+        <v>14.5423876690417</v>
       </c>
       <c r="M251" t="n">
-        <v>-32.4325394812837</v>
+        <v>-32.4461189404545</v>
       </c>
       <c r="N251" t="s">
         <v>70</v>
@@ -38853,10 +38853,10 @@
         <v>0.214364328553209</v>
       </c>
       <c r="Q251" t="n">
-        <v>4.8621633372681</v>
+        <v>4.85854992970045</v>
       </c>
       <c r="R251" t="n">
-        <v>3.16453177557463</v>
+        <v>3.16247473821577</v>
       </c>
       <c r="S251" t="n">
         <v>-1.2</v>
@@ -38975,13 +38975,13 @@
         <v>458</v>
       </c>
       <c r="K252" t="n">
-        <v>13.483566776386</v>
+        <v>13.4763815488911</v>
       </c>
       <c r="L252" t="n">
-        <v>14.123428894224</v>
+        <v>14.1154551870148</v>
       </c>
       <c r="M252" t="n">
-        <v>-4.53050121631376</v>
+        <v>-4.52747452814445</v>
       </c>
       <c r="N252" t="s">
         <v>70</v>
@@ -38993,10 +38993,10 @@
         <v>0.177488777054795</v>
       </c>
       <c r="Q252" t="n">
-        <v>6.28794059929255</v>
+        <v>6.28298345691213</v>
       </c>
       <c r="R252" t="n">
-        <v>3.90185375278922</v>
+        <v>3.89878273616911</v>
       </c>
       <c r="S252" t="n">
         <v>-1.8</v>
@@ -39125,13 +39125,13 @@
         <v>416</v>
       </c>
       <c r="K253" t="n">
-        <v>14.0835454731045</v>
+        <v>14.0742402267247</v>
       </c>
       <c r="L253" t="n">
-        <v>11.7228929785488</v>
+        <v>11.7146538596697</v>
       </c>
       <c r="M253" t="n">
-        <v>20.1371154618172</v>
+        <v>20.1421774413534</v>
       </c>
       <c r="N253" t="s">
         <v>70</v>
@@ -39143,10 +39143,10 @@
         <v>0.17377590686129</v>
       </c>
       <c r="Q253" t="n">
-        <v>6.55471124160047</v>
+        <v>6.55017747336449</v>
       </c>
       <c r="R253" t="n">
-        <v>4.05208714293797</v>
+        <v>4.04905195355199</v>
       </c>
       <c r="S253" t="n">
         <v>-2</v>
@@ -39275,13 +39275,13 @@
         <v>412</v>
       </c>
       <c r="K254" t="n">
-        <v>16.2106922779779</v>
+        <v>16.1996166393393</v>
       </c>
       <c r="L254" t="n">
-        <v>13.1710786250494</v>
+        <v>13.157216155769</v>
       </c>
       <c r="M254" t="n">
-        <v>23.0779402314679</v>
+        <v>23.1234362007217</v>
       </c>
       <c r="N254" t="s">
         <v>70</v>
@@ -39293,10 +39293,10 @@
         <v>0.164517817527216</v>
       </c>
       <c r="Q254" t="n">
-        <v>7.35876160364927</v>
+        <v>7.3524312839965</v>
       </c>
       <c r="R254" t="n">
-        <v>4.4827056057341</v>
+        <v>4.47925743477836</v>
       </c>
       <c r="S254" t="n">
         <v>-2.2</v>
@@ -39425,13 +39425,13 @@
         <v>518</v>
       </c>
       <c r="K255" t="n">
-        <v>3.63273674797348</v>
+        <v>3.63244680110512</v>
       </c>
       <c r="L255" t="n">
-        <v>3.31229092836088</v>
+        <v>3.31316879244658</v>
       </c>
       <c r="M255" t="n">
-        <v>9.67444667582922</v>
+        <v>9.63663576049729</v>
       </c>
       <c r="N255" t="s">
         <v>70</v>
@@ -39443,10 +39443,10 @@
         <v>0.176784306884189</v>
       </c>
       <c r="Q255" t="n">
-        <v>1.95828809329119</v>
+        <v>1.95808984402817</v>
       </c>
       <c r="R255" t="n">
-        <v>1.42600774174052</v>
+        <v>1.42582854884388</v>
       </c>
       <c r="S255" t="n">
         <v>0.4</v>
@@ -39575,13 +39575,13 @@
         <v>463</v>
       </c>
       <c r="K256" t="n">
-        <v>5.11229189362217</v>
+        <v>5.11206107436454</v>
       </c>
       <c r="L256" t="n">
-        <v>4.95702602230483</v>
+        <v>4.95899241334854</v>
       </c>
       <c r="M256" t="n">
-        <v>3.13223837475733</v>
+        <v>3.08668875160958</v>
       </c>
       <c r="N256" t="s">
         <v>70</v>
@@ -39593,10 +39593,10 @@
         <v>0.174245627996578</v>
       </c>
       <c r="Q256" t="n">
-        <v>2.52747553798514</v>
+        <v>2.52720810248458</v>
       </c>
       <c r="R256" t="n">
-        <v>1.69931156180899</v>
+        <v>1.69910271483511</v>
       </c>
       <c r="S256" t="n">
         <v>-0.4</v>
@@ -39725,13 +39725,13 @@
         <v>405</v>
       </c>
       <c r="K257" t="n">
-        <v>5.78149124751395</v>
+        <v>5.78283379009306</v>
       </c>
       <c r="L257" t="n">
-        <v>5.00515489715229</v>
+        <v>4.99715185129666</v>
       </c>
       <c r="M257" t="n">
-        <v>15.5107357577157</v>
+        <v>15.7225948335458</v>
       </c>
       <c r="N257" t="s">
         <v>70</v>
@@ -39743,10 +39743,10 @@
         <v>0.18951087463712</v>
       </c>
       <c r="Q257" t="n">
-        <v>2.83764148279192</v>
+        <v>2.83890775221477</v>
       </c>
       <c r="R257" t="n">
-        <v>1.88310172954912</v>
+        <v>1.88374876587802</v>
       </c>
       <c r="S257" t="n">
         <v>-0.7</v>
@@ -39875,13 +39875,13 @@
         <v>465</v>
       </c>
       <c r="K258" t="n">
-        <v>6.4706190162318</v>
+        <v>6.4697929433855</v>
       </c>
       <c r="L258" t="n">
-        <v>10.0058029014507</v>
+        <v>10.0218458763403</v>
       </c>
       <c r="M258" t="n">
-        <v>-35.3313364258491</v>
+        <v>-35.4431007698945</v>
       </c>
       <c r="N258" t="s">
         <v>70</v>
@@ -39893,10 +39893,10 @@
         <v>0.221397049460689</v>
       </c>
       <c r="Q258" t="n">
-        <v>3.24134088564549</v>
+        <v>3.24094140827017</v>
       </c>
       <c r="R258" t="n">
-        <v>2.12758078412011</v>
+        <v>2.12728866729165</v>
       </c>
       <c r="S258" t="n">
         <v>-0.5</v>
@@ -40015,13 +40015,13 @@
         <v>543</v>
       </c>
       <c r="K259" t="n">
-        <v>7.00649080751641</v>
+        <v>7.00607134209546</v>
       </c>
       <c r="L259" t="n">
-        <v>8.25489063144862</v>
+        <v>8.25761704235819</v>
       </c>
       <c r="M259" t="n">
-        <v>-15.1231540146175</v>
+        <v>-15.1562574752839</v>
       </c>
       <c r="N259" t="s">
         <v>70</v>
@@ -40033,10 +40033,10 @@
         <v>0.196671125441828</v>
       </c>
       <c r="Q259" t="n">
-        <v>3.35631300649079</v>
+        <v>3.35571520255905</v>
       </c>
       <c r="R259" t="n">
-        <v>2.14734093538204</v>
+        <v>2.14705820751765</v>
       </c>
       <c r="S259" t="n">
         <v>-0.7</v>
@@ -40165,13 +40165,13 @@
         <v>185</v>
       </c>
       <c r="K260" t="n">
-        <v>37.8432218712381</v>
+        <v>37.8478142651468</v>
       </c>
       <c r="L260" t="n">
-        <v>28.6802408947519</v>
+        <v>28.6309762381907</v>
       </c>
       <c r="M260" t="n">
-        <v>31.9487587643062</v>
+        <v>32.1918398809673</v>
       </c>
       <c r="N260" t="s">
         <v>70</v>
@@ -40183,10 +40183,10 @@
         <v>0.176722948258275</v>
       </c>
       <c r="Q260" t="n">
-        <v>16.4969858780675</v>
+        <v>16.4936944104953</v>
       </c>
       <c r="R260" t="n">
-        <v>9.16006556513554</v>
+        <v>9.16393153634909</v>
       </c>
       <c r="S260" t="n">
         <v>-3.3</v>
@@ -40315,13 +40315,13 @@
         <v>412</v>
       </c>
       <c r="K261" t="n">
-        <v>38.0613081562365</v>
+        <v>38.0647781118391</v>
       </c>
       <c r="L261" t="n">
-        <v>32.8217919264851</v>
+        <v>32.8433497536946</v>
       </c>
       <c r="M261" t="n">
-        <v>15.9635288697429</v>
+        <v>15.8979775123492</v>
       </c>
       <c r="N261" t="s">
         <v>70</v>
@@ -40333,10 +40333,10 @@
         <v>0.177677817670378</v>
       </c>
       <c r="Q261" t="n">
-        <v>16.5508224664971</v>
+        <v>16.5497316033187</v>
       </c>
       <c r="R261" t="n">
-        <v>9.16686667111415</v>
+        <v>9.16573686017125</v>
       </c>
       <c r="S261" t="n">
         <v>-3.2</v>
@@ -40465,13 +40465,13 @@
         <v>437</v>
       </c>
       <c r="K262" t="n">
-        <v>161.682228015206</v>
+        <v>162.031320313041</v>
       </c>
       <c r="L262" t="n">
         <v>98.5300492610837</v>
       </c>
       <c r="M262" t="n">
-        <v>64.0943338887231</v>
+        <v>64.4486342269986</v>
       </c>
       <c r="N262" t="s">
         <v>70</v>
@@ -40483,10 +40483,10 @@
         <v>0.177839776776265</v>
       </c>
       <c r="Q262" t="n">
-        <v>72.487458588674</v>
+        <v>72.7171048023508</v>
       </c>
       <c r="R262" t="n">
-        <v>39.5859615817427</v>
+        <v>39.6980373350354</v>
       </c>
       <c r="S262" t="n">
         <v>-5.6</v>
@@ -40615,13 +40615,13 @@
         <v>430</v>
       </c>
       <c r="K263" t="n">
-        <v>2.29505018822807</v>
+        <v>2.29470248095313</v>
       </c>
       <c r="L263" t="n">
-        <v>2.45798412269275</v>
+        <v>2.45870928088506</v>
       </c>
       <c r="M263" t="n">
-        <v>-6.62876269054946</v>
+        <v>-6.67044295179539</v>
       </c>
       <c r="N263" t="s">
         <v>70</v>
@@ -40633,10 +40633,10 @@
         <v>0.190058861590915</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.41512638683052</v>
+        <v>1.41499131718918</v>
       </c>
       <c r="R263" t="n">
-        <v>1.16503673532899</v>
+        <v>1.16499325844766</v>
       </c>
       <c r="S263" t="n">
         <v>1.1</v>
@@ -40765,13 +40765,13 @@
         <v>516</v>
       </c>
       <c r="K264" t="n">
-        <v>5.00117042972376</v>
+        <v>5.0033685181603</v>
       </c>
       <c r="L264" t="n">
-        <v>5.00014999250037</v>
+        <v>4.99066819701582</v>
       </c>
       <c r="M264" t="n">
-        <v>0.0204081322543015</v>
+        <v>0.254481376904114</v>
       </c>
       <c r="N264" t="s">
         <v>70</v>
@@ -40783,10 +40783,10 @@
         <v>0.180690619111856</v>
       </c>
       <c r="Q264" t="n">
-        <v>2.30093997313213</v>
+        <v>2.30136221530733</v>
       </c>
       <c r="R264" t="n">
-        <v>1.55310223517013</v>
+        <v>1.55341260443379</v>
       </c>
       <c r="S264" t="n">
         <v>-1.1</v>
@@ -40915,13 +40915,13 @@
         <v>437</v>
       </c>
       <c r="K265" t="n">
-        <v>9.1628209218066</v>
+        <v>9.16135978260445</v>
       </c>
       <c r="L265" t="n">
-        <v>9.68600484261501</v>
+        <v>9.68975874430772</v>
       </c>
       <c r="M265" t="n">
-        <v>-5.40144186699746</v>
+        <v>-5.45316943018502</v>
       </c>
       <c r="N265" t="s">
         <v>70</v>
@@ -40933,10 +40933,10 @@
         <v>0.181267877108457</v>
       </c>
       <c r="Q265" t="n">
-        <v>3.91363179432254</v>
+        <v>3.91311651485717</v>
       </c>
       <c r="R265" t="n">
-        <v>2.30546325930827</v>
+        <v>2.30516066204917</v>
       </c>
       <c r="S265" t="n">
         <v>-1.8</v>
@@ -41065,7 +41065,7 @@
         <v>553</v>
       </c>
       <c r="K266" t="n">
-        <v>9.95147016005963</v>
+        <v>9.94933907297275</v>
       </c>
       <c r="L266"/>
       <c r="M266"/>
@@ -41079,10 +41079,10 @@
         <v>0.214994378547606</v>
       </c>
       <c r="Q266" t="n">
-        <v>4.44498522548655</v>
+        <v>4.44418784676502</v>
       </c>
       <c r="R266" t="n">
-        <v>2.65870185140942</v>
+        <v>2.65812892081032</v>
       </c>
       <c r="S266" t="n">
         <v>-2</v>
@@ -41191,13 +41191,13 @@
         <v>458</v>
       </c>
       <c r="K267" t="n">
-        <v>15.6415120789105</v>
+        <v>15.6385572931679</v>
       </c>
       <c r="L267" t="n">
-        <v>12.2483772198408</v>
+        <v>12.2513781697905</v>
       </c>
       <c r="M267" t="n">
-        <v>27.7027299059116</v>
+        <v>27.6473313976177</v>
       </c>
       <c r="N267" t="s">
         <v>70</v>
@@ -41209,10 +41209,10 @@
         <v>0.179891267433642</v>
       </c>
       <c r="Q267" t="n">
-        <v>6.48315248105897</v>
+        <v>6.48194148634075</v>
       </c>
       <c r="R267" t="n">
-        <v>3.64264608916839</v>
+        <v>3.64200617419584</v>
       </c>
       <c r="S267" t="n">
         <v>-2.8</v>
@@ -41341,13 +41341,13 @@
         <v>412</v>
       </c>
       <c r="K268" t="n">
-        <v>19.8283435944315</v>
+        <v>19.8326065690159</v>
       </c>
       <c r="L268" t="n">
         <v>16.6763381690845</v>
       </c>
       <c r="M268" t="n">
-        <v>18.9010644506496</v>
+        <v>18.926627464191</v>
       </c>
       <c r="N268" t="s">
         <v>70</v>
@@ -41359,10 +41359,10 @@
         <v>0.172340143762939</v>
       </c>
       <c r="Q268" t="n">
-        <v>8.03492512402322</v>
+        <v>8.03387062741174</v>
       </c>
       <c r="R268" t="n">
-        <v>4.39981378893619</v>
+        <v>4.39915764854533</v>
       </c>
       <c r="S268" t="n">
         <v>-3</v>
@@ -41491,13 +41491,13 @@
         <v>478</v>
       </c>
       <c r="K269" t="n">
-        <v>29.7046914631995</v>
+        <v>29.69902859562</v>
       </c>
       <c r="L269" t="n">
-        <v>22.4989876265467</v>
+        <v>22.5395537525355</v>
       </c>
       <c r="M269" t="n">
-        <v>32.0267914106089</v>
+        <v>31.7640487548657</v>
       </c>
       <c r="N269" t="s">
         <v>70</v>
@@ -41509,10 +41509,10 @@
         <v>0.174079500807642</v>
       </c>
       <c r="Q269" t="n">
-        <v>11.9905004111556</v>
+        <v>11.9897204951872</v>
       </c>
       <c r="R269" t="n">
-        <v>6.44221166228903</v>
+        <v>6.44059595883462</v>
       </c>
       <c r="S269" t="n">
         <v>-3.6</v>
@@ -41641,13 +41641,13 @@
         <v>482</v>
       </c>
       <c r="K270" t="n">
-        <v>149.877480642474</v>
+        <v>150.435908535639</v>
       </c>
       <c r="L270" t="n">
-        <v>94.258246936852</v>
+        <v>95.1550903901047</v>
       </c>
       <c r="M270" t="n">
-        <v>59.0072863787542</v>
+        <v>58.0954922315778</v>
       </c>
       <c r="N270" t="s">
         <v>70</v>
@@ -41659,10 +41659,10 @@
         <v>0.173125064025821</v>
       </c>
       <c r="Q270" t="n">
-        <v>61.9095044106157</v>
+        <v>62.3429560511155</v>
       </c>
       <c r="R270" t="n">
-        <v>32.3882552259851</v>
+        <v>32.559588768692</v>
       </c>
       <c r="S270" t="n">
         <v>-5.9</v>

--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -264,7 +264,7 @@
     <t xml:space="preserve">Corey Mutton</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T12:07:00</t>
+    <t xml:space="preserve">2026-10-11T12:08:00</t>
   </si>
   <si>
     <t xml:space="preserve">WYNNUM HAULAGE 366m</t>
@@ -393,7 +393,7 @@
     <t xml:space="preserve">Claude Dacey</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-11T13:10:00</t>
+    <t xml:space="preserve">2026-10-11T13:07:00</t>
   </si>
   <si>
     <t xml:space="preserve">BETDELUXE TREVOR MCSHERRY CLASSIC 366m</t>

--- a/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
+++ b/files/Straight_Greyhound_upcoming_rated_prices_LOGIT.xlsx
@@ -207,7 +207,10 @@
     <t xml:space="preserve">SPECIALIST_ENSEMBLE_2026_lw0.65_mp200_sp100_STUDENT</t>
   </si>
   <si>
-    <t xml:space="preserve">BORN CHEEKY</t>
+    <t xml:space="preserve">LIL MISS RIPLEY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Ayre</t>
   </si>
   <si>
     <t xml:space="preserve">NO VALID FORM</t>
@@ -216,12 +219,6 @@
     <t xml:space="preserve">UNRESOLVED_IDENTITY</t>
   </si>
   <si>
-    <t xml:space="preserve">LIL MISS RIPLEY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ryan Ayre</t>
-  </si>
-  <si>
     <t xml:space="preserve">JUNGLE GIRL</t>
   </si>
   <si>
@@ -253,6 +250,9 @@
   </si>
   <si>
     <t xml:space="preserve">MOOSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKULI HONEY</t>
   </si>
   <si>
     <t xml:space="preserve">BYE BRUNETTE</t>
@@ -2218,31 +2218,31 @@
         <v>55</v>
       </c>
       <c r="K2" t="n">
-        <v>1.99100280549116</v>
+        <v>1.6015890015584</v>
       </c>
       <c r="L2" t="n">
-        <v>1.95798500303463</v>
+        <v>1.65721576880375</v>
       </c>
       <c r="M2" t="n">
-        <v>1.68631539084083</v>
+        <v>-3.35663999175594</v>
       </c>
       <c r="N2" t="s">
         <v>56</v>
       </c>
       <c r="O2" t="n">
-        <v>0.290254193344962</v>
+        <v>0.28990846015942</v>
       </c>
       <c r="P2" t="n">
-        <v>0.208595945424019</v>
+        <v>0.208347478589237</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.27675932604122</v>
+        <v>1.15511330623846</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09882785854631</v>
+        <v>1.05946440602648</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="T2" t="n">
         <v>101.177689925278</v>
@@ -2357,36 +2357,36 @@
         <v>53</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
         <v>64</v>
       </c>
       <c r="J3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K3" t="n">
-        <v>4.89666134446384</v>
+        <v>5.71733707099611</v>
       </c>
       <c r="L3"/>
       <c r="M3"/>
       <c r="N3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O3" t="n">
-        <v>0.361932049000329</v>
+        <v>0.361500937501789</v>
       </c>
       <c r="P3" t="n">
-        <v>0.256404462811728</v>
+        <v>0.256099049371552</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.08130136819155</v>
+        <v>1.90160935326797</v>
       </c>
       <c r="R3" t="n">
-        <v>1.39197717988954</v>
+        <v>1.32323721192474</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.3</v>
+        <v>-1.9</v>
       </c>
       <c r="T3"/>
       <c r="U3"/>
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="AV3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW3" t="s">
         <v>62</v>
@@ -2483,64 +2483,86 @@
         <v>53</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K4" t="n">
-        <v>7.01884292369817</v>
-      </c>
-      <c r="L4"/>
-      <c r="M4"/>
+        <v>14.6174440131611</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11.456982472219</v>
+      </c>
+      <c r="M4" t="n">
+        <v>27.5854619539273</v>
+      </c>
       <c r="N4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="O4" t="n">
-        <v>0.361932049000329</v>
+        <v>0.273752612205847</v>
       </c>
       <c r="P4" t="n">
-        <v>0.256404462811728</v>
+        <v>0.208831537440992</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.91598428781178</v>
+        <v>4.58739836730685</v>
       </c>
       <c r="R4" t="n">
-        <v>1.65431078183454</v>
+        <v>2.14803020915659</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="T4"/>
-      <c r="U4"/>
-      <c r="V4"/>
+        <v>-3.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>94.6979660133337</v>
+      </c>
+      <c r="U4" t="n">
+        <v>94.759593163851</v>
+      </c>
+      <c r="V4" t="n">
+        <v>97.5152804590392</v>
+      </c>
       <c r="W4" t="n">
-        <v>100</v>
+        <v>102.699400332022</v>
       </c>
       <c r="X4"/>
-      <c r="Y4"/>
+      <c r="Y4" t="n">
+        <v>97.4454498695828</v>
+      </c>
       <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4"/>
-      <c r="AB4"/>
-      <c r="AC4"/>
-      <c r="AD4"/>
+        <v>6</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>97.4454498695828</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>94.759593163851</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>97.5152804590392</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>100.153362455467</v>
+      </c>
       <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4"/>
+        <v>6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>14</v>
+      </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -2561,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="AQ4" t="s">
         <v>58</v>
@@ -2577,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="AV4" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="AW4" t="s">
         <v>62</v>
@@ -2609,86 +2631,86 @@
         <v>53</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K5" t="n">
-        <v>18.2955675968905</v>
+        <v>17.0612233189551</v>
       </c>
       <c r="L5" t="n">
-        <v>14.4918127807564</v>
+        <v>14.0519881972741</v>
       </c>
       <c r="M5" t="n">
-        <v>26.2476121771669</v>
+        <v>21.4150131599509</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>0.274079078576012</v>
+        <v>0.277197469400351</v>
       </c>
       <c r="P5" t="n">
-        <v>0.209080581544918</v>
+        <v>0.20089089235942</v>
       </c>
       <c r="Q5" t="n">
-        <v>6.83736488911661</v>
+        <v>5.40854167237559</v>
       </c>
       <c r="R5" t="n">
-        <v>3.48020514165414</v>
+        <v>2.51784976398628</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.6</v>
+        <v>-3.9</v>
       </c>
       <c r="T5" t="n">
-        <v>94.6979660133337</v>
+        <v>95.7477434471261</v>
       </c>
       <c r="U5" t="n">
-        <v>94.759593163851</v>
+        <v>94.7252696398541</v>
       </c>
       <c r="V5" t="n">
-        <v>97.5152804590392</v>
+        <v>94.7252696398541</v>
       </c>
       <c r="W5" t="n">
-        <v>102.699400332022</v>
+        <v>99.9899189429049</v>
       </c>
       <c r="X5"/>
       <c r="Y5" t="n">
-        <v>97.4454498695828</v>
+        <v>94.7528244877193</v>
       </c>
       <c r="Z5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="n">
-        <v>97.4454498695828</v>
+        <v>94.7528244877193</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.759593163851</v>
+        <v>94.7252696398541</v>
       </c>
       <c r="AC5" t="n">
-        <v>97.5152804590392</v>
+        <v>94.7252696398541</v>
       </c>
       <c r="AD5" t="n">
-        <v>100.153362455467</v>
+        <v>94.7252696398541</v>
       </c>
       <c r="AE5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AG5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -2709,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="AQ5" t="s">
         <v>58</v>
@@ -2725,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="AV5" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="AW5" t="s">
         <v>62</v>
@@ -2757,92 +2779,82 @@
         <v>53</v>
       </c>
       <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J6" t="s">
+        <v>77</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31.4757511062759</v>
+      </c>
+      <c r="L6" t="n">
+        <v>30.1865378810746</v>
+      </c>
+      <c r="M6" t="n">
+        <v>4.27082174935218</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.37993183845387</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.269156100469423</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>11.46451463793</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.49412769031291</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>90.2722299361183</v>
+      </c>
+      <c r="U6" t="n">
+        <v>90.9346313138877</v>
+      </c>
+      <c r="V6" t="n">
+        <v>90.2722299361183</v>
+      </c>
+      <c r="W6" t="n">
+        <v>100.57394922912</v>
+      </c>
+      <c r="X6" t="n">
+        <v>98.22514463352</v>
+      </c>
+      <c r="Y6"/>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6"/>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>3</v>
       </c>
-      <c r="I6" t="s">
-        <v>74</v>
-      </c>
-      <c r="J6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K6" t="n">
-        <v>21.3302370292902</v>
-      </c>
-      <c r="L6" t="n">
-        <v>17.842640499554</v>
-      </c>
-      <c r="M6" t="n">
-        <v>19.5464148359844</v>
-      </c>
-      <c r="N6" t="s">
-        <v>76</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.277528043968845</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.201130466768954</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>7.9276334487013</v>
-      </c>
-      <c r="R6" t="n">
-        <v>4.03215345286732</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-3.9</v>
-      </c>
-      <c r="T6" t="n">
-        <v>95.7477434471261</v>
-      </c>
-      <c r="U6" t="n">
-        <v>94.7252696398541</v>
-      </c>
-      <c r="V6" t="n">
-        <v>94.7252696398541</v>
-      </c>
-      <c r="W6" t="n">
-        <v>99.9899189429049</v>
-      </c>
-      <c r="X6"/>
-      <c r="Y6" t="n">
-        <v>94.7528244877193</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>94.7528244877193</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>94.7252696398541</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>94.7252696398541</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>94.7252696398541</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -2854,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="AQ6" t="s">
         <v>58</v>
@@ -2873,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AV6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="AW6" t="s">
         <v>62</v>
@@ -2905,55 +2917,55 @@
         <v>53</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I7" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" t="s">
         <v>77</v>
       </c>
-      <c r="J7" t="s">
-        <v>78</v>
-      </c>
       <c r="K7" t="n">
-        <v>36.7745251203044</v>
+        <v>58.9573648118149</v>
       </c>
       <c r="L7" t="n">
-        <v>32.8865504768168</v>
+        <v>65.3220117570216</v>
       </c>
       <c r="M7" t="n">
-        <v>11.8223851000376</v>
+        <v>-9.74349499351196</v>
       </c>
       <c r="N7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O7" t="n">
-        <v>0.385446444812744</v>
+        <v>0.361500937501789</v>
       </c>
       <c r="P7" t="n">
-        <v>0.273062827395018</v>
+        <v>0.256099049371552</v>
       </c>
       <c r="Q7" t="n">
-        <v>15.642106046081</v>
+        <v>22.0570703338276</v>
       </c>
       <c r="R7" t="n">
-        <v>8.39932729510259</v>
+        <v>10.440917702694</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.1</v>
+        <v>-6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>90.2722299361183</v>
+        <v>89.6298208029044</v>
       </c>
       <c r="U7" t="n">
-        <v>90.9346313138877</v>
+        <v>88.5736503834198</v>
       </c>
       <c r="V7" t="n">
-        <v>90.2722299361183</v>
+        <v>88.0412101551669</v>
       </c>
       <c r="W7" t="n">
-        <v>100.57394922912</v>
+        <v>101.41339867474</v>
       </c>
       <c r="X7" t="n">
-        <v>98.22514463352</v>
+        <v>93.2696810465002</v>
       </c>
       <c r="Y7"/>
       <c r="Z7" t="n">
@@ -2977,10 +2989,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2995,7 +3007,7 @@
         <v>1</v>
       </c>
       <c r="AP7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ7" t="s">
         <v>58</v>
@@ -3011,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="AV7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW7" t="s">
         <v>62</v>
@@ -3043,55 +3055,55 @@
         <v>53</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
         <v>79</v>
       </c>
       <c r="J8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K8" t="n">
-        <v>73.5816756114548</v>
+        <v>71.347038730637</v>
       </c>
       <c r="L8" t="n">
-        <v>79.0577075098814</v>
+        <v>83.5488721804511</v>
       </c>
       <c r="M8" t="n">
-        <v>-6.92662622141196</v>
+        <v>-14.6044262853247</v>
       </c>
       <c r="N8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O8" t="n">
-        <v>0.361932049000329</v>
+        <v>0.361500937501789</v>
       </c>
       <c r="P8" t="n">
-        <v>0.256404462811728</v>
+        <v>0.256099049371552</v>
       </c>
       <c r="Q8" t="n">
-        <v>30.0547052367</v>
+        <v>25.4290177202369</v>
       </c>
       <c r="R8" t="n">
-        <v>15.8811207076266</v>
+        <v>11.9559862732135</v>
       </c>
       <c r="S8" t="n">
-        <v>-6.2</v>
+        <v>-6.3</v>
       </c>
       <c r="T8" t="n">
-        <v>89.6298208029044</v>
+        <v>86.4177751368349</v>
       </c>
       <c r="U8" t="n">
-        <v>88.5736503834198</v>
+        <v>86.4177751368349</v>
       </c>
       <c r="V8" t="n">
-        <v>88.0412101551669</v>
+        <v>85.7758131148366</v>
       </c>
       <c r="W8" t="n">
-        <v>101.41339867474</v>
+        <v>100.283794842289</v>
       </c>
       <c r="X8" t="n">
-        <v>93.2696810465002</v>
+        <v>94.4997587008307</v>
       </c>
       <c r="Y8"/>
       <c r="Z8" t="n">
@@ -3109,16 +3121,16 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -3133,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="AP8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ8" t="s">
         <v>58</v>
@@ -3149,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW8" t="s">
         <v>62</v>
@@ -3190,28 +3202,28 @@
         <v>81</v>
       </c>
       <c r="K9" t="n">
-        <v>114.636806011216</v>
+        <v>91.3932117726729</v>
       </c>
       <c r="L9" t="n">
-        <v>95.5186246418338</v>
+        <v>75.5918367346939</v>
       </c>
       <c r="M9" t="n">
-        <v>20.0151346829685</v>
+        <v>20.9035468914949</v>
       </c>
       <c r="N9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>0.279823048635</v>
+        <v>0.279489740396185</v>
       </c>
       <c r="P9" t="n">
-        <v>0.213462355617384</v>
+        <v>0.213208092210023</v>
       </c>
       <c r="Q9" t="n">
-        <v>42.0837580986618</v>
+        <v>29.722334132063</v>
       </c>
       <c r="R9" t="n">
-        <v>20.1269596854955</v>
+        <v>13.1117060903101</v>
       </c>
       <c r="S9" t="n">
         <v>-6.9</v>
@@ -3283,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ9" t="s">
         <v>58</v>
@@ -3299,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="AV9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW9" t="s">
         <v>62</v>
@@ -3340,13 +3352,13 @@
         <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>1.71007980899038</v>
+        <v>1.71253073283792</v>
       </c>
       <c r="L10" t="n">
-        <v>1.64727973513861</v>
+        <v>1.64972534270302</v>
       </c>
       <c r="M10" t="n">
-        <v>3.81235029559159</v>
+        <v>3.80702099368795</v>
       </c>
       <c r="N10" t="s">
         <v>56</v>
@@ -3358,10 +3370,10 @@
         <v>0.213913265676542</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.20238876154848</v>
+        <v>1.2033041445601</v>
       </c>
       <c r="R10" t="n">
-        <v>1.07806903132521</v>
+        <v>1.07843091702628</v>
       </c>
       <c r="S10" t="n">
         <v>2.2</v>
@@ -3485,19 +3497,19 @@
         <v>87</v>
       </c>
       <c r="J11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K11" t="n">
-        <v>7.341335316119</v>
+        <v>7.31651059147305</v>
       </c>
       <c r="L11" t="n">
-        <v>7.15928126565967</v>
+        <v>7.13374705756473</v>
       </c>
       <c r="M11" t="n">
-        <v>2.54290959809844</v>
+        <v>2.56195702529864</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O11" t="n">
         <v>0.256907078082931</v>
@@ -3506,10 +3518,10 @@
         <v>0.195501706276337</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.6229628067276</v>
+        <v>2.61881172301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.60558831814293</v>
+        <v>1.60419942261315</v>
       </c>
       <c r="S11" t="n">
         <v>-2.2</v>
@@ -3579,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ11" t="s">
         <v>58</v>
@@ -3595,7 +3607,7 @@
         <v>0</v>
       </c>
       <c r="AV11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW11" t="s">
         <v>62</v>
@@ -3636,16 +3648,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="n">
-        <v>9.60976343082807</v>
+        <v>9.59401545430368</v>
       </c>
       <c r="L12" t="n">
-        <v>9.53637837322399</v>
+        <v>9.51641450185555</v>
       </c>
       <c r="M12" t="n">
-        <v>0.769527536891057</v>
+        <v>0.815443173823449</v>
       </c>
       <c r="N12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O12" t="n">
         <v>0.263562913598163</v>
@@ -3654,10 +3666,10 @@
         <v>0.200566678443054</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.37258892320242</v>
+        <v>3.37190157971908</v>
       </c>
       <c r="R12" t="n">
-        <v>1.92144396163367</v>
+        <v>1.92157160252948</v>
       </c>
       <c r="S12" t="n">
         <v>-2.6</v>
@@ -3729,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ12" t="s">
         <v>58</v>
@@ -3745,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="AV12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW12" t="s">
         <v>62</v>
@@ -3786,12 +3798,12 @@
         <v>91</v>
       </c>
       <c r="K13" t="n">
-        <v>11.8070317361638</v>
+        <v>11.8205428853565</v>
       </c>
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O13" t="n">
         <v>0.354297669916018</v>
@@ -3800,10 +3812,10 @@
         <v>0.250382230054194</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.39679866350819</v>
+        <v>4.40891793578149</v>
       </c>
       <c r="R13" t="n">
-        <v>2.45323711131819</v>
+        <v>2.46016721424068</v>
       </c>
       <c r="S13" t="n">
         <v>-2.9</v>
@@ -3871,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW13" t="s">
         <v>62</v>
@@ -3912,16 +3924,16 @@
         <v>93</v>
       </c>
       <c r="K14" t="n">
-        <v>24.4166091696825</v>
+        <v>24.3484867297489</v>
       </c>
       <c r="L14" t="n">
-        <v>25.8085161290323</v>
+        <v>25.7952024761413</v>
       </c>
       <c r="M14" t="n">
-        <v>-5.3932080108393</v>
+        <v>-5.60846827130186</v>
       </c>
       <c r="N14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O14" t="n">
         <v>0.258096016922108</v>
@@ -3930,10 +3942,10 @@
         <v>0.196406467536524</v>
       </c>
       <c r="Q14" t="n">
-        <v>8.30612657223882</v>
+        <v>8.28923391788618</v>
       </c>
       <c r="R14" t="n">
-        <v>4.23467709559497</v>
+        <v>4.22795216739749</v>
       </c>
       <c r="S14" t="n">
         <v>-4</v>
@@ -4005,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ14" t="s">
         <v>58</v>
@@ -4021,7 +4033,7 @@
         <v>0</v>
       </c>
       <c r="AV14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW14" t="s">
         <v>62</v>
@@ -4062,16 +4074,16 @@
         <v>95</v>
       </c>
       <c r="K15" t="n">
-        <v>26.8004772177489</v>
+        <v>26.6780440431229</v>
       </c>
       <c r="L15" t="n">
-        <v>31.0487426265135</v>
+        <v>30.8761963569003</v>
       </c>
       <c r="M15" t="n">
-        <v>-13.6825682761688</v>
+        <v>-13.5967276061163</v>
       </c>
       <c r="N15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O15" t="n">
         <v>0.254820316339081</v>
@@ -4080,10 +4092,10 @@
         <v>0.193913717792099</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.0345296961286</v>
+        <v>8.99882232575291</v>
       </c>
       <c r="R15" t="n">
-        <v>4.5324798884952</v>
+        <v>4.51934665376019</v>
       </c>
       <c r="S15" t="n">
         <v>-4.1</v>
@@ -4155,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="AP15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ15" t="s">
         <v>58</v>
@@ -4171,7 +4183,7 @@
         <v>0</v>
       </c>
       <c r="AV15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW15" t="s">
         <v>62</v>
@@ -4212,16 +4224,16 @@
         <v>97</v>
       </c>
       <c r="K16" t="n">
-        <v>144.143095504741</v>
+        <v>144.215891767105</v>
       </c>
       <c r="L16" t="n">
         <v>142.258890469417</v>
       </c>
       <c r="M16" t="n">
-        <v>1.32449018061815</v>
+        <v>1.37566185932601</v>
       </c>
       <c r="N16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O16" t="n">
         <v>0.289598418373052</v>
@@ -4230,10 +4242,10 @@
         <v>0.220379233415219</v>
       </c>
       <c r="Q16" t="n">
-        <v>55.9652748795888</v>
+        <v>56.3680102754807</v>
       </c>
       <c r="R16" t="n">
-        <v>28.1862323555398</v>
+        <v>28.2839768753996</v>
       </c>
       <c r="S16" t="n">
         <v>-7.3</v>
@@ -4305,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ16" t="s">
         <v>58</v>
@@ -4321,7 +4333,7 @@
         <v>0</v>
       </c>
       <c r="AV16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW16" t="s">
         <v>62</v>
@@ -4362,16 +4374,16 @@
         <v>81</v>
       </c>
       <c r="K17" t="n">
-        <v>197.831909566615</v>
+        <v>197.11420188895</v>
       </c>
       <c r="L17" t="n">
-        <v>257.089974293059</v>
+        <v>255.774936061381</v>
       </c>
       <c r="M17" t="n">
-        <v>-23.0495432151297</v>
+        <v>-22.9345123004366</v>
       </c>
       <c r="N17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O17" t="n">
         <v>0.281869939944635</v>
@@ -4380,10 +4392,10 @@
         <v>0.214497999114669</v>
       </c>
       <c r="Q17" t="n">
-        <v>70.5222662420971</v>
+        <v>70.3426227290733</v>
       </c>
       <c r="R17" t="n">
-        <v>34.1638062586657</v>
+        <v>34.0931094404057</v>
       </c>
       <c r="S17" t="n">
         <v>-7.1</v>
@@ -4455,7 +4467,7 @@
         <v>1</v>
       </c>
       <c r="AP17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ17" t="s">
         <v>58</v>
@@ -4471,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="AV17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW17" t="s">
         <v>62</v>
@@ -4512,16 +4524,16 @@
         <v>103</v>
       </c>
       <c r="K18" t="n">
-        <v>1.37649323273997</v>
+        <v>1.37834263890673</v>
       </c>
       <c r="L18" t="n">
-        <v>1.51472971540221</v>
+        <v>1.51665933665964</v>
       </c>
       <c r="M18" t="n">
-        <v>-9.12614846441644</v>
+        <v>-9.11982634528519</v>
       </c>
       <c r="N18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O18" t="n">
         <v>0.19750374713579</v>
@@ -4530,13 +4542,13 @@
         <v>0.197780266451344</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.04870688476231</v>
+        <v>1.04892414811663</v>
       </c>
       <c r="R18" t="n">
-        <v>1.01237551751238</v>
+        <v>1.01242636502018</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="T18" t="n">
         <v>99.2225713661577</v>
@@ -4603,7 +4615,7 @@
         <v>0</v>
       </c>
       <c r="AP18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ18" t="s">
         <v>104</v>
@@ -4619,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="AV18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW18" t="s">
         <v>62</v>
@@ -4660,16 +4672,16 @@
         <v>106</v>
       </c>
       <c r="K19" t="n">
-        <v>4.65981150563212</v>
+        <v>4.64133788876134</v>
       </c>
       <c r="L19" t="n">
-        <v>3.86620017783276</v>
+        <v>3.855171350372</v>
       </c>
       <c r="M19" t="n">
-        <v>20.5269073326727</v>
+        <v>20.3925186960493</v>
       </c>
       <c r="N19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O19" t="n">
         <v>0.169001346505025</v>
@@ -4678,13 +4690,13 @@
         <v>0.169237960429272</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.24326320095429</v>
+        <v>1.24275099079747</v>
       </c>
       <c r="R19" t="n">
-        <v>1.04395109456585</v>
+        <v>1.04383469093291</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9</v>
+        <v>-1.8</v>
       </c>
       <c r="T19" t="n">
         <v>104.885466873245</v>
@@ -4753,7 +4765,7 @@
         <v>1</v>
       </c>
       <c r="AP19" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ19" t="s">
         <v>104</v>
@@ -4769,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="AV19" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW19" t="s">
         <v>62</v>
@@ -4810,16 +4822,16 @@
         <v>97</v>
       </c>
       <c r="K20" t="n">
-        <v>38.3094012247743</v>
+        <v>38.1291314098189</v>
       </c>
       <c r="L20" t="n">
-        <v>29.8974588938714</v>
+        <v>29.8261258574411</v>
       </c>
       <c r="M20" t="n">
-        <v>28.1359775784397</v>
+        <v>27.8380289550959</v>
       </c>
       <c r="N20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O20" t="n">
         <v>0.217211926943254</v>
@@ -4828,10 +4840,10 @@
         <v>0.206644789546605</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.48571094855003</v>
+        <v>9.4734183759449</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25641333528229</v>
+        <v>2.25254869079646</v>
       </c>
       <c r="S20" t="n">
         <v>-4.9</v>
@@ -4903,7 +4915,7 @@
         <v>1</v>
       </c>
       <c r="AP20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ20" t="s">
         <v>104</v>
@@ -4919,7 +4931,7 @@
         <v>1</v>
       </c>
       <c r="AV20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW20" t="s">
         <v>62</v>
@@ -4960,16 +4972,16 @@
         <v>95</v>
       </c>
       <c r="K21" t="n">
-        <v>114.303627305377</v>
+        <v>114.458403008407</v>
       </c>
       <c r="L21" t="n">
         <v>60.6470588235294</v>
       </c>
       <c r="M21" t="n">
-        <v>88.4734882823871</v>
+        <v>88.7286955521737</v>
       </c>
       <c r="N21" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O21" t="n">
         <v>0.177261870502406</v>
@@ -4978,10 +4990,10 @@
         <v>0.177510049748704</v>
       </c>
       <c r="Q21" t="n">
-        <v>25.1863415611991</v>
+        <v>25.2590662991834</v>
       </c>
       <c r="R21" t="n">
-        <v>5.7002986739569</v>
+        <v>5.71887219605248</v>
       </c>
       <c r="S21" t="n">
         <v>-6.8</v>
@@ -5051,7 +5063,7 @@
         <v>1</v>
       </c>
       <c r="AP21" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ21" t="s">
         <v>104</v>
@@ -5067,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="AV21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW21" t="s">
         <v>62</v>
@@ -5108,16 +5120,16 @@
         <v>110</v>
       </c>
       <c r="K22" t="n">
-        <v>116.352828009192</v>
+        <v>116.001264060641</v>
       </c>
       <c r="L22" t="n">
-        <v>109.297267759563</v>
+        <v>109.058887677208</v>
       </c>
       <c r="M22" t="n">
-        <v>6.45538575140772</v>
+        <v>6.36571354365996</v>
       </c>
       <c r="N22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O22" t="n">
         <v>0.224355690086591</v>
@@ -5126,10 +5138,10 @@
         <v>0.21165778771905</v>
       </c>
       <c r="Q22" t="n">
-        <v>30.1485020787689</v>
+        <v>30.1058947323792</v>
       </c>
       <c r="R22" t="n">
-        <v>6.82953723382074</v>
+        <v>6.81340894299632</v>
       </c>
       <c r="S22" t="n">
         <v>-6.3</v>
@@ -5201,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="AP22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ22" t="s">
         <v>104</v>
@@ -5217,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="AV22" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW22" t="s">
         <v>62</v>
@@ -5258,16 +5270,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="n">
-        <v>120.792005660489</v>
+        <v>121.099973592432</v>
       </c>
       <c r="L23" t="n">
-        <v>77.3449342614076</v>
+        <v>77.4647560030984</v>
       </c>
       <c r="M23" t="n">
-        <v>56.1731311998288</v>
+        <v>56.3291228692284</v>
       </c>
       <c r="N23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O23" t="n">
         <v>0.189883473065285</v>
@@ -5276,10 +5288,10 @@
         <v>0.190149323454295</v>
       </c>
       <c r="Q23" t="n">
-        <v>29.1084258816146</v>
+        <v>29.2548691376137</v>
       </c>
       <c r="R23" t="n">
-        <v>6.4621086322528</v>
+        <v>6.48631769407171</v>
       </c>
       <c r="S23" t="n">
         <v>-6.5</v>
@@ -5351,7 +5363,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ23" t="s">
         <v>104</v>
@@ -5367,7 +5379,7 @@
         <v>0</v>
       </c>
       <c r="AV23" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW23" t="s">
         <v>62</v>
@@ -5408,16 +5420,16 @@
         <v>113</v>
       </c>
       <c r="K24" t="n">
-        <v>139.079234047865</v>
+        <v>139.001353462723</v>
       </c>
       <c r="L24" t="n">
-        <v>109.297267759563</v>
+        <v>109.058887677208</v>
       </c>
       <c r="M24" t="n">
-        <v>27.2485917523736</v>
+        <v>27.455319252969</v>
       </c>
       <c r="N24" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O24" t="n">
         <v>0.206618442888247</v>
@@ -5426,10 +5438,10 @@
         <v>0.206907723427158</v>
       </c>
       <c r="Q24" t="n">
-        <v>33.9436944406853</v>
+        <v>33.9799759873545</v>
       </c>
       <c r="R24" t="n">
-        <v>7.43255225364818</v>
+        <v>7.43348299757364</v>
       </c>
       <c r="S24" t="n">
         <v>-6.5</v>
@@ -5501,7 +5513,7 @@
         <v>1</v>
       </c>
       <c r="AP24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ24" t="s">
         <v>104</v>
@@ -5517,7 +5529,7 @@
         <v>0</v>
       </c>
       <c r="AV24" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW24" t="s">
         <v>62</v>
@@ -5558,16 +5570,16 @@
         <v>117</v>
       </c>
       <c r="K25" t="n">
-        <v>1.15178962351306</v>
+        <v>1.15182841985427</v>
       </c>
       <c r="L25" t="n">
-        <v>1.26115742083559</v>
+        <v>1.26144376190416</v>
       </c>
       <c r="M25" t="n">
-        <v>-8.67201790321072</v>
+        <v>-8.68967332197437</v>
       </c>
       <c r="N25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O25" t="n">
         <v>0.185962757131504</v>
@@ -5576,10 +5588,10 @@
         <v>0.170939359159989</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.02912186783382</v>
+        <v>1.02911552076656</v>
       </c>
       <c r="R25" t="n">
-        <v>1.01046298120663</v>
+        <v>1.01047016405382</v>
       </c>
       <c r="S25" t="n">
         <v>4.8</v>
@@ -5651,7 +5663,7 @@
         <v>1</v>
       </c>
       <c r="AP25" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ25" t="s">
         <v>118</v>
@@ -5667,7 +5679,7 @@
         <v>1</v>
       </c>
       <c r="AV25" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW25" t="s">
         <v>62</v>
@@ -5708,16 +5720,16 @@
         <v>120</v>
       </c>
       <c r="K26" t="n">
-        <v>17.2413430238494</v>
+        <v>17.1875536708842</v>
       </c>
       <c r="L26" t="n">
-        <v>9.92024600734054</v>
+        <v>9.88690064260999</v>
       </c>
       <c r="M26" t="n">
-        <v>73.7995510503633</v>
+        <v>73.8416748805012</v>
       </c>
       <c r="N26" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O26" t="n">
         <v>0.19179585776753</v>
@@ -5726,10 +5738,10 @@
         <v>0.167489849107738</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.45915803497176</v>
+        <v>2.45225674232497</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46046379317949</v>
+        <v>1.45808848039101</v>
       </c>
       <c r="S26" t="n">
         <v>-4.8</v>
@@ -5856,16 +5868,16 @@
         <v>113</v>
       </c>
       <c r="K27" t="n">
-        <v>31.7892769271815</v>
+        <v>31.9308193275187</v>
       </c>
       <c r="L27" t="n">
-        <v>23.1334721258385</v>
+        <v>23.2409946548919</v>
       </c>
       <c r="M27" t="n">
-        <v>37.4167991482568</v>
+        <v>37.3900721619833</v>
       </c>
       <c r="N27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O27" t="n">
         <v>0.201632649295259</v>
@@ -5874,10 +5886,10 @@
         <v>0.185343325663262</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.62887520315859</v>
+        <v>3.64385368737094</v>
       </c>
       <c r="R27" t="n">
-        <v>1.84142872129604</v>
+        <v>1.84579166925163</v>
       </c>
       <c r="S27" t="n">
         <v>-5.1</v>
@@ -5949,7 +5961,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ27" t="s">
         <v>118</v>
@@ -5965,7 +5977,7 @@
         <v>0</v>
       </c>
       <c r="AV27" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW27" t="s">
         <v>62</v>
@@ -6006,16 +6018,16 @@
         <v>124</v>
       </c>
       <c r="K28" t="n">
-        <v>49.7310898993127</v>
+        <v>49.6598952681442</v>
       </c>
       <c r="L28" t="n">
-        <v>35.2009855684618</v>
+        <v>35.1021411021411</v>
       </c>
       <c r="M28" t="n">
-        <v>41.2775497509623</v>
+        <v>41.4725532657469</v>
       </c>
       <c r="N28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O28" t="n">
         <v>0.19775334568803</v>
@@ -6024,10 +6036,10 @@
         <v>0.181777419872041</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.82407647658002</v>
+        <v>5.81361481227692</v>
       </c>
       <c r="R28" t="n">
-        <v>2.67289391355432</v>
+        <v>2.66911823227914</v>
       </c>
       <c r="S28" t="n">
         <v>-5.8</v>
@@ -6099,7 +6111,7 @@
         <v>1</v>
       </c>
       <c r="AP28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ28" t="s">
         <v>118</v>
@@ -6115,7 +6127,7 @@
         <v>1</v>
       </c>
       <c r="AV28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW28" t="s">
         <v>62</v>
@@ -6156,16 +6168,16 @@
         <v>95</v>
       </c>
       <c r="K29" t="n">
-        <v>73.0804003167282</v>
+        <v>73.3585006582947</v>
       </c>
       <c r="L29" t="n">
-        <v>43.0503659061558</v>
+        <v>43.1618472162279</v>
       </c>
       <c r="M29" t="n">
-        <v>69.7555846006836</v>
+        <v>69.9614483383685</v>
       </c>
       <c r="N29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O29" t="n">
         <v>0.178245491567671</v>
@@ -6174,10 +6186,10 @@
         <v>0.163845549354749</v>
       </c>
       <c r="Q29" t="n">
-        <v>9.65680360892498</v>
+        <v>9.70494945181077</v>
       </c>
       <c r="R29" t="n">
-        <v>4.11598227552824</v>
+        <v>4.13015524651349</v>
       </c>
       <c r="S29" t="n">
         <v>-6.9</v>
@@ -6247,7 +6259,7 @@
         <v>0</v>
       </c>
       <c r="AP29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ29" t="s">
         <v>118</v>
@@ -6263,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="AV29" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW29" t="s">
         <v>62</v>
@@ -6304,16 +6316,16 @@
         <v>97</v>
       </c>
       <c r="K30" t="n">
-        <v>117.138306382713</v>
+        <v>116.998269741965</v>
       </c>
       <c r="L30" t="n">
-        <v>87.6476774758983</v>
+        <v>87.4943132108486</v>
       </c>
       <c r="M30" t="n">
-        <v>33.6467887753488</v>
+        <v>33.7209990551228</v>
       </c>
       <c r="N30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O30" t="n">
         <v>0.198413755588949</v>
@@ -6322,10 +6334,10 @@
         <v>0.182384477150538</v>
       </c>
       <c r="Q30" t="n">
-        <v>14.1178963040442</v>
+        <v>14.0807012523819</v>
       </c>
       <c r="R30" t="n">
-        <v>6.04221022505611</v>
+        <v>6.024746986282</v>
       </c>
       <c r="S30" t="n">
         <v>-6.9</v>
@@ -6397,7 +6409,7 @@
         <v>1</v>
       </c>
       <c r="AP30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ30" t="s">
         <v>118</v>
@@ -6413,7 +6425,7 @@
         <v>1</v>
       </c>
       <c r="AV30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW30" t="s">
         <v>62</v>
@@ -6454,16 +6466,16 @@
         <v>131</v>
       </c>
       <c r="K31" t="n">
-        <v>2.27501119982835</v>
+        <v>2.26829332593087</v>
       </c>
       <c r="L31" t="n">
-        <v>2.25532778567079</v>
+        <v>2.24974692371718</v>
       </c>
       <c r="M31" t="n">
-        <v>0.872751813843209</v>
+        <v>0.824377267423704</v>
       </c>
       <c r="N31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O31" t="n">
         <v>0.193362066947829</v>
@@ -6472,10 +6484,10 @@
         <v>0.193480460635928</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.36257214336702</v>
+        <v>1.36018865185995</v>
       </c>
       <c r="R31" t="n">
-        <v>1.11885426113514</v>
+        <v>1.11809693933415</v>
       </c>
       <c r="S31" t="n">
         <v>0.7</v>
@@ -6545,7 +6557,7 @@
         <v>1</v>
       </c>
       <c r="AP31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ31" t="s">
         <v>104</v>
@@ -6561,7 +6573,7 @@
         <v>0</v>
       </c>
       <c r="AV31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW31" t="s">
         <v>62</v>
@@ -6602,16 +6614,16 @@
         <v>120</v>
       </c>
       <c r="K32" t="n">
-        <v>3.97335745149052</v>
+        <v>3.98455140519253</v>
       </c>
       <c r="L32" t="n">
-        <v>4.79539678734117</v>
+        <v>4.80368893798934</v>
       </c>
       <c r="M32" t="n">
-        <v>-17.1422589684478</v>
+        <v>-17.0522601144875</v>
       </c>
       <c r="N32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O32" t="n">
         <v>0.279781524378017</v>
@@ -6620,10 +6632,10 @@
         <v>0.259983382364809</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.95713667932225</v>
+        <v>1.96000354050984</v>
       </c>
       <c r="R32" t="n">
-        <v>1.37874118988784</v>
+        <v>1.37979632126934</v>
       </c>
       <c r="S32" t="n">
         <v>-0.7</v>
@@ -6683,7 +6695,7 @@
         <v>1</v>
       </c>
       <c r="AP32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ32" t="s">
         <v>104</v>
@@ -6699,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AV32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW32" t="s">
         <v>62</v>
@@ -6740,16 +6752,16 @@
         <v>134</v>
       </c>
       <c r="K33" t="n">
-        <v>6.21187131843318</v>
+        <v>6.23352691430048</v>
       </c>
       <c r="L33" t="n">
-        <v>5.72750701563484</v>
+        <v>5.74329523918911</v>
       </c>
       <c r="M33" t="n">
-        <v>8.45680854647803</v>
+        <v>8.53572130101023</v>
       </c>
       <c r="N33" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O33" t="n">
         <v>0.186313190127766</v>
@@ -6758,10 +6770,10 @@
         <v>0.186427267858053</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.64406060997949</v>
+        <v>2.6504479591666</v>
       </c>
       <c r="R33" t="n">
-        <v>1.57343479349612</v>
+        <v>1.57588590654956</v>
       </c>
       <c r="S33" t="n">
         <v>-1.4</v>
@@ -6831,7 +6843,7 @@
         <v>1</v>
       </c>
       <c r="AP33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ33" t="s">
         <v>104</v>
@@ -6847,7 +6859,7 @@
         <v>0</v>
       </c>
       <c r="AV33" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW33" t="s">
         <v>62</v>
@@ -6888,16 +6900,16 @@
         <v>81</v>
       </c>
       <c r="K34" t="n">
-        <v>16.6633647860097</v>
+        <v>16.7307608422155</v>
       </c>
       <c r="L34" t="n">
-        <v>15.1320926009986</v>
+        <v>15.2196012783442</v>
       </c>
       <c r="M34" t="n">
-        <v>10.1193683212727</v>
+        <v>9.92903517138441</v>
       </c>
       <c r="N34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O34" t="n">
         <v>0.20708252013797</v>
@@ -6906,10 +6918,10 @@
         <v>0.20720931472435</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.69440364914145</v>
+        <v>6.71180793278364</v>
       </c>
       <c r="R34" t="n">
-        <v>3.50957089730448</v>
+        <v>3.51583043667358</v>
       </c>
       <c r="S34" t="n">
         <v>-2.7</v>
@@ -6981,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="AP34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ34" t="s">
         <v>104</v>
@@ -6997,7 +7009,7 @@
         <v>0</v>
       </c>
       <c r="AV34" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW34" t="s">
         <v>62</v>
@@ -7038,16 +7050,16 @@
         <v>137</v>
       </c>
       <c r="K35" t="n">
-        <v>23.7032550324914</v>
+        <v>23.6429176476973</v>
       </c>
       <c r="L35" t="n">
-        <v>22.2388258839226</v>
+        <v>22.1993340732519</v>
       </c>
       <c r="M35" t="n">
-        <v>6.58501108022762</v>
+        <v>6.50282377697415</v>
       </c>
       <c r="N35" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O35" t="n">
         <v>0.185592860251754</v>
@@ -7056,10 +7068,10 @@
         <v>0.185706496931156</v>
       </c>
       <c r="Q35" t="n">
-        <v>9.11273623684662</v>
+        <v>9.07881398201482</v>
       </c>
       <c r="R35" t="n">
-        <v>4.55235118329355</v>
+        <v>4.53790492857416</v>
       </c>
       <c r="S35" t="n">
         <v>-3.2</v>
@@ -7129,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="AP35" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ35" t="s">
         <v>104</v>
@@ -7145,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="AV35" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW35" t="s">
         <v>62</v>
@@ -7186,16 +7198,16 @@
         <v>106</v>
       </c>
       <c r="K36" t="n">
-        <v>38.7612044697276</v>
+        <v>38.6562003022436</v>
       </c>
       <c r="L36" t="n">
-        <v>29.3020802812775</v>
+        <v>29.2849194729136</v>
       </c>
       <c r="M36" t="n">
-        <v>32.2814083425128</v>
+        <v>32.0003640030418</v>
       </c>
       <c r="N36" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O36" t="n">
         <v>0.186927416411841</v>
@@ -7204,10 +7216,10 @@
         <v>0.187041870226828</v>
       </c>
       <c r="Q36" t="n">
-        <v>14.6454188952139</v>
+        <v>14.6079779681214</v>
       </c>
       <c r="R36" t="n">
-        <v>7.17345586023919</v>
+        <v>7.15254792990655</v>
       </c>
       <c r="S36" t="n">
         <v>-4</v>
@@ -7279,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="AP36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ36" t="s">
         <v>104</v>
@@ -7295,7 +7307,7 @@
         <v>0</v>
       </c>
       <c r="AV36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW36" t="s">
         <v>62</v>
@@ -7336,16 +7348,16 @@
         <v>140</v>
       </c>
       <c r="K37" t="n">
-        <v>77.1410979600278</v>
+        <v>77.1199058088607</v>
       </c>
       <c r="L37" t="n">
         <v>49.6810730253353</v>
       </c>
       <c r="M37" t="n">
-        <v>55.2726083848651</v>
+        <v>55.2299519970768</v>
       </c>
       <c r="N37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O37" t="n">
         <v>0.216367458020136</v>
@@ -7354,10 +7366,10 @@
         <v>0.216499937682482</v>
       </c>
       <c r="Q37" t="n">
-        <v>31.2719614129735</v>
+        <v>31.221955449457</v>
       </c>
       <c r="R37" t="n">
-        <v>15.490007789753</v>
+        <v>15.4628138518016</v>
       </c>
       <c r="S37" t="n">
         <v>-5.2</v>
@@ -7427,7 +7439,7 @@
         <v>1</v>
       </c>
       <c r="AP37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ37" t="s">
         <v>104</v>
@@ -7443,7 +7455,7 @@
         <v>0</v>
       </c>
       <c r="AV37" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW37" t="s">
         <v>62</v>
@@ -7484,16 +7496,16 @@
         <v>134</v>
       </c>
       <c r="K38" t="n">
-        <v>146.608734508159</v>
+        <v>146.074911092113</v>
       </c>
       <c r="L38" t="n">
-        <v>122.408812729498</v>
+        <v>122.10989010989</v>
       </c>
       <c r="M38" t="n">
-        <v>19.7697545128045</v>
+        <v>19.6257821218712</v>
       </c>
       <c r="N38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O38" t="n">
         <v>0.187998981456962</v>
@@ -7502,10 +7514,10 @@
         <v>0.188114091380667</v>
       </c>
       <c r="Q38" t="n">
-        <v>56.9348363069261</v>
+        <v>56.5361237245081</v>
       </c>
       <c r="R38" t="n">
-        <v>27.1631157981936</v>
+        <v>26.9982925906948</v>
       </c>
       <c r="S38" t="n">
         <v>-5.7</v>
@@ -7575,7 +7587,7 @@
         <v>1</v>
       </c>
       <c r="AP38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ38" t="s">
         <v>104</v>
@@ -7591,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="AV38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW38" t="s">
         <v>62</v>
@@ -7632,16 +7644,16 @@
         <v>146</v>
       </c>
       <c r="K39" t="n">
-        <v>1.56520964064995</v>
+        <v>1.56514067342674</v>
       </c>
       <c r="L39" t="n">
-        <v>1.53011826986337</v>
+        <v>1.52997781687447</v>
       </c>
       <c r="M39" t="n">
-        <v>2.29337636689455</v>
+        <v>2.29825924039224</v>
       </c>
       <c r="N39" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O39" t="n">
         <v>0.188784968880326</v>
@@ -7650,10 +7662,10 @@
         <v>0.179276545781164</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.1368261374313</v>
+        <v>1.13675277201387</v>
       </c>
       <c r="R39" t="n">
-        <v>1.04194160480835</v>
+        <v>1.04190612463979</v>
       </c>
       <c r="S39" t="n">
         <v>2</v>
@@ -7723,7 +7735,7 @@
         <v>1</v>
       </c>
       <c r="AP39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ39" t="s">
         <v>147</v>
@@ -7739,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="AV39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW39" t="s">
         <v>62</v>
@@ -7780,16 +7792,16 @@
         <v>149</v>
       </c>
       <c r="K40" t="n">
-        <v>6.65622220877362</v>
+        <v>6.64436462301623</v>
       </c>
       <c r="L40" t="n">
-        <v>6.27987441130298</v>
+        <v>6.26806643685365</v>
       </c>
       <c r="M40" t="n">
-        <v>5.9929191703779</v>
+        <v>6.00341732101144</v>
       </c>
       <c r="N40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O40" t="n">
         <v>0.18523573834733</v>
@@ -7798,10 +7810,10 @@
         <v>0.175906077285127</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.21747885617182</v>
+        <v>2.2135684650876</v>
       </c>
       <c r="R40" t="n">
-        <v>1.43698003560256</v>
+        <v>1.4353622957026</v>
       </c>
       <c r="S40" t="n">
         <v>-2</v>
@@ -7871,7 +7883,7 @@
         <v>0</v>
       </c>
       <c r="AP40" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ40" t="s">
         <v>147</v>
@@ -7887,7 +7899,7 @@
         <v>1</v>
       </c>
       <c r="AV40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW40" t="s">
         <v>62</v>
@@ -7928,16 +7940,16 @@
         <v>151</v>
       </c>
       <c r="K41" t="n">
-        <v>16.2839760796716</v>
+        <v>16.3439244645356</v>
       </c>
       <c r="L41" t="n">
-        <v>19.2654594490464</v>
+        <v>19.317558431524</v>
       </c>
       <c r="M41" t="n">
-        <v>-15.475796864644</v>
+        <v>-15.3934255073135</v>
       </c>
       <c r="N41" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O41" t="n">
         <v>0.184089239887189</v>
@@ -7946,10 +7958,10 @@
         <v>0.174817323848364</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.02022660718191</v>
+        <v>5.03969691760623</v>
       </c>
       <c r="R41" t="n">
-        <v>2.53124704405832</v>
+        <v>2.53807256199118</v>
       </c>
       <c r="S41" t="n">
         <v>-3.1</v>
@@ -8021,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="AP41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ41" t="s">
         <v>147</v>
@@ -8037,7 +8049,7 @@
         <v>0</v>
       </c>
       <c r="AV41" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW41" t="s">
         <v>62</v>
@@ -8078,16 +8090,16 @@
         <v>113</v>
       </c>
       <c r="K42" t="n">
-        <v>20.0674212228944</v>
+        <v>20.0286217482193</v>
       </c>
       <c r="L42" t="n">
-        <v>21.0496737528941</v>
+        <v>21.0142887161168</v>
       </c>
       <c r="M42" t="n">
-        <v>-4.6663551251699</v>
+        <v>-4.69046076797073</v>
       </c>
       <c r="N42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O42" t="n">
         <v>0.206403174480505</v>
@@ -8096,10 +8108,10 @@
         <v>0.1960073854322</v>
       </c>
       <c r="Q42" t="n">
-        <v>6.33571022358588</v>
+        <v>6.32470611922975</v>
       </c>
       <c r="R42" t="n">
-        <v>3.17947792683881</v>
+        <v>3.17215719601853</v>
       </c>
       <c r="S42" t="n">
         <v>-3.5</v>
@@ -8171,7 +8183,7 @@
         <v>1</v>
       </c>
       <c r="AP42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ42" t="s">
         <v>147</v>
@@ -8187,7 +8199,7 @@
         <v>1</v>
       </c>
       <c r="AV42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW42" t="s">
         <v>62</v>
@@ -8228,16 +8240,16 @@
         <v>97</v>
       </c>
       <c r="K43" t="n">
-        <v>20.2951840142169</v>
+        <v>20.3923913651741</v>
       </c>
       <c r="L43" t="n">
-        <v>20.463883773276</v>
+        <v>20.5987641606591</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.824378016061034</v>
+        <v>-1.0018697911942</v>
       </c>
       <c r="N43" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O43" t="n">
         <v>0.211823514079725</v>
@@ -8246,10 +8258,10 @@
         <v>0.201154721928703</v>
       </c>
       <c r="Q43" t="n">
-        <v>6.46820482745113</v>
+        <v>6.49344105701243</v>
       </c>
       <c r="R43" t="n">
-        <v>3.24974933699348</v>
+        <v>3.26119277959329</v>
       </c>
       <c r="S43" t="n">
         <v>-3.5</v>
@@ -8321,7 +8333,7 @@
         <v>0</v>
       </c>
       <c r="AP43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ43" t="s">
         <v>147</v>
@@ -8337,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="AV43" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW43" t="s">
         <v>62</v>
@@ -8378,16 +8390,16 @@
         <v>55</v>
       </c>
       <c r="K44" t="n">
-        <v>25.8511672837112</v>
+        <v>25.790780535727</v>
       </c>
       <c r="L44" t="n">
-        <v>36.5923893157702</v>
+        <v>36.5389112166606</v>
       </c>
       <c r="M44" t="n">
-        <v>-29.3537050542634</v>
+        <v>-29.4155745834944</v>
       </c>
       <c r="N44" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O44" t="n">
         <v>0.188556237244322</v>
@@ -8396,10 +8408,10 @@
         <v>0.179059334538887</v>
       </c>
       <c r="Q44" t="n">
-        <v>8.08898355940409</v>
+        <v>8.06521772550464</v>
       </c>
       <c r="R44" t="n">
-        <v>3.89027335468276</v>
+        <v>3.87803816273564</v>
       </c>
       <c r="S44" t="n">
         <v>-3.6</v>
@@ -8471,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="AP44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ44" t="s">
         <v>147</v>
@@ -8487,7 +8499,7 @@
         <v>0</v>
       </c>
       <c r="AV44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW44" t="s">
         <v>62</v>
@@ -8528,13 +8540,13 @@
         <v>106</v>
       </c>
       <c r="K45" t="n">
-        <v>85.654895401318</v>
+        <v>85.8257971271252</v>
       </c>
       <c r="L45" t="n">
-        <v>86.1386735572782</v>
+        <v>86.2873166522864</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.561627125171071</v>
+        <v>-0.534863689203624</v>
       </c>
       <c r="N45" t="s">
         <v>56</v>
@@ -8546,10 +8558,10 @@
         <v>0.217690312588331</v>
       </c>
       <c r="Q45" t="n">
-        <v>29.2925237414389</v>
+        <v>29.3975000995938</v>
       </c>
       <c r="R45" t="n">
-        <v>14.285142196588</v>
+        <v>14.3284654706877</v>
       </c>
       <c r="S45" t="n">
         <v>-5.7</v>
@@ -8676,16 +8688,16 @@
         <v>149</v>
       </c>
       <c r="K46" t="n">
-        <v>2.43074698697563</v>
+        <v>2.42618248462571</v>
       </c>
       <c r="L46" t="n">
-        <v>2.52472797960163</v>
+        <v>2.52040121978881</v>
       </c>
       <c r="M46" t="n">
-        <v>-3.72242052947137</v>
+        <v>-3.73824351549055</v>
       </c>
       <c r="N46" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O46" t="n">
         <v>0.175229875420781</v>
@@ -8694,10 +8706,10 @@
         <v>0.175229875420781</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.47229810864598</v>
+        <v>1.47023776489886</v>
       </c>
       <c r="R46" t="n">
-        <v>1.19066572531695</v>
+        <v>1.18962323144289</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -8767,7 +8779,7 @@
         <v>0</v>
       </c>
       <c r="AP46" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ46" t="s">
         <v>104</v>
@@ -8783,7 +8795,7 @@
         <v>0</v>
       </c>
       <c r="AV46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW46" t="s">
         <v>62</v>
@@ -8824,16 +8836,16 @@
         <v>131</v>
       </c>
       <c r="K47" t="n">
-        <v>4.87006441757613</v>
+        <v>4.86593399871582</v>
       </c>
       <c r="L47" t="n">
-        <v>4.86155267123621</v>
+        <v>4.85777432360227</v>
       </c>
       <c r="M47" t="n">
-        <v>0.175082878157107</v>
+        <v>0.167971473559403</v>
       </c>
       <c r="N47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O47" t="n">
         <v>0.159844522853372</v>
@@ -8842,10 +8854,10 @@
         <v>0.159844522853372</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.28384150154165</v>
+        <v>2.28069665477132</v>
       </c>
       <c r="R47" t="n">
-        <v>1.54237532728716</v>
+        <v>1.5402086621662</v>
       </c>
       <c r="S47" t="n">
         <v>-1</v>
@@ -8917,7 +8929,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ47" t="s">
         <v>104</v>
@@ -8933,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="AV47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW47" t="s">
         <v>62</v>
@@ -8974,16 +8986,16 @@
         <v>151</v>
       </c>
       <c r="K48" t="n">
-        <v>8.19431479276319</v>
+        <v>8.18419268027611</v>
       </c>
       <c r="L48" t="n">
-        <v>8.23577369678004</v>
+        <v>8.22087957254418</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.503400233460194</v>
+        <v>-0.446264805904761</v>
       </c>
       <c r="N48" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O48" t="n">
         <v>0.17165888308569</v>
@@ -8992,10 +9004,10 @@
         <v>0.17165888308569</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.62499138080447</v>
+        <v>3.61757251948902</v>
       </c>
       <c r="R48" t="n">
-        <v>2.18037717931071</v>
+        <v>2.1761964473513</v>
       </c>
       <c r="S48" t="n">
         <v>-1.7</v>
@@ -9067,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="AP48" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ48" t="s">
         <v>104</v>
@@ -9083,7 +9095,7 @@
         <v>1</v>
       </c>
       <c r="AV48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW48" t="s">
         <v>62</v>
@@ -9124,16 +9136,16 @@
         <v>164</v>
       </c>
       <c r="K49" t="n">
-        <v>8.98795184425733</v>
+        <v>9.02838767542818</v>
       </c>
       <c r="L49" t="n">
-        <v>8.32767091348155</v>
+        <v>8.35829502716256</v>
       </c>
       <c r="M49" t="n">
-        <v>7.92875868457841</v>
+        <v>8.01709733968445</v>
       </c>
       <c r="N49" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O49" t="n">
         <v>0.167975709020704</v>
@@ -9142,10 +9154,10 @@
         <v>0.167975709020704</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.94155209265562</v>
+        <v>3.95652042333249</v>
       </c>
       <c r="R49" t="n">
-        <v>2.34533798994269</v>
+        <v>2.35168006284218</v>
       </c>
       <c r="S49" t="n">
         <v>-1.8</v>
@@ -9215,7 +9227,7 @@
         <v>0</v>
       </c>
       <c r="AP49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ49" t="s">
         <v>104</v>
@@ -9231,7 +9243,7 @@
         <v>0</v>
       </c>
       <c r="AV49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW49" t="s">
         <v>62</v>
@@ -9272,16 +9284,16 @@
         <v>166</v>
       </c>
       <c r="K50" t="n">
-        <v>12.4487896694329</v>
+        <v>12.5188702988757</v>
       </c>
       <c r="L50" t="n">
-        <v>10.8033920276547</v>
+        <v>10.8644215100489</v>
       </c>
       <c r="M50" t="n">
-        <v>15.2303798433511</v>
+        <v>15.2281351316921</v>
       </c>
       <c r="N50" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O50" t="n">
         <v>0.168547749366312</v>
@@ -9290,10 +9302,10 @@
         <v>0.168547749366312</v>
       </c>
       <c r="Q50" t="n">
-        <v>5.35579518511374</v>
+        <v>5.38074741766252</v>
       </c>
       <c r="R50" t="n">
-        <v>3.08233236474106</v>
+        <v>3.0934112722604</v>
       </c>
       <c r="S50" t="n">
         <v>-2.3</v>
@@ -9363,7 +9375,7 @@
         <v>1</v>
       </c>
       <c r="AP50" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ50" t="s">
         <v>104</v>
@@ -9379,7 +9391,7 @@
         <v>0</v>
       </c>
       <c r="AV50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW50" t="s">
         <v>62</v>
@@ -9420,16 +9432,16 @@
         <v>95</v>
       </c>
       <c r="K51" t="n">
-        <v>21.9722615463504</v>
+        <v>21.9958523239913</v>
       </c>
       <c r="L51" t="n">
-        <v>22.9954012416647</v>
+        <v>23.0271701588764</v>
       </c>
       <c r="M51" t="n">
-        <v>-4.44932308230627</v>
+        <v>-4.47869984791643</v>
       </c>
       <c r="N51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O51" t="n">
         <v>0.167139589354102</v>
@@ -9438,13 +9450,13 @@
         <v>0.167139589354102</v>
       </c>
       <c r="Q51" t="n">
-        <v>9.08777518174381</v>
+        <v>9.09263320942814</v>
       </c>
       <c r="R51" t="n">
-        <v>4.99636123899842</v>
+        <v>4.99207232235771</v>
       </c>
       <c r="S51" t="n">
-        <v>-2.9</v>
+        <v>-3</v>
       </c>
       <c r="T51" t="n">
         <v>106.128355248913</v>
@@ -9513,7 +9525,7 @@
         <v>1</v>
       </c>
       <c r="AP51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ51" t="s">
         <v>104</v>
@@ -9529,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="AV51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW51" t="s">
         <v>62</v>
@@ -9570,16 +9582,16 @@
         <v>151</v>
       </c>
       <c r="K52" t="n">
-        <v>41.4407592903226</v>
+        <v>41.617385049565</v>
       </c>
       <c r="L52" t="n">
-        <v>48.3826802128689</v>
+        <v>48.476490547746</v>
       </c>
       <c r="M52" t="n">
-        <v>-14.3479461906698</v>
+        <v>-14.1493441886542</v>
       </c>
       <c r="N52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O52" t="n">
         <v>0.189349458396071</v>
@@ -9588,10 +9600,10 @@
         <v>0.189349458396071</v>
       </c>
       <c r="Q52" t="n">
-        <v>17.6648758723378</v>
+        <v>17.7390957598237</v>
       </c>
       <c r="R52" t="n">
-        <v>9.78533235728257</v>
+        <v>9.82275180994341</v>
       </c>
       <c r="S52" t="n">
         <v>-3.7</v>
@@ -9663,7 +9675,7 @@
         <v>1</v>
       </c>
       <c r="AP52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ52" t="s">
         <v>104</v>
@@ -9679,7 +9691,7 @@
         <v>0</v>
       </c>
       <c r="AV52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW52" t="s">
         <v>62</v>
@@ -9720,16 +9732,16 @@
         <v>172</v>
       </c>
       <c r="K53" t="n">
-        <v>1.19720476089486</v>
+        <v>1.19626040669845</v>
       </c>
       <c r="L53" t="n">
-        <v>1.24577400749903</v>
+        <v>1.24484359635037</v>
       </c>
       <c r="M53" t="n">
-        <v>-3.89872049920843</v>
+        <v>-3.90275451425103</v>
       </c>
       <c r="N53" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O53" t="n">
         <v>0.206401419391934</v>
@@ -9738,13 +9750,13 @@
         <v>0.189837474955115</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.0398394496658</v>
+        <v>1.03961927602541</v>
       </c>
       <c r="R53" t="n">
-        <v>1.01555191514149</v>
+        <v>1.01551528400223</v>
       </c>
       <c r="S53" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T53" t="n">
         <v>107.778577023459</v>
@@ -9811,7 +9823,7 @@
         <v>1</v>
       </c>
       <c r="AP53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ53" t="s">
         <v>118</v>
@@ -9827,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="AV53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW53" t="s">
         <v>62</v>
@@ -9868,16 +9880,16 @@
         <v>117</v>
       </c>
       <c r="K54" t="n">
-        <v>18.9960938482343</v>
+        <v>19.1111538678353</v>
       </c>
       <c r="L54" t="n">
-        <v>15.036385505939</v>
+        <v>15.0862875245135</v>
       </c>
       <c r="M54" t="n">
-        <v>26.3341767922312</v>
+        <v>26.6789714618775</v>
       </c>
       <c r="N54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O54" t="n">
         <v>0.198522934879396</v>
@@ -9886,13 +9898,13 @@
         <v>0.18259124762422</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.03986070446185</v>
+        <v>3.0444173455533</v>
       </c>
       <c r="R54" t="n">
-        <v>1.7297953290709</v>
+        <v>1.73215721499751</v>
       </c>
       <c r="S54" t="n">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="T54" t="n">
         <v>99.8275084733771</v>
@@ -9959,7 +9971,7 @@
         <v>1</v>
       </c>
       <c r="AP54" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ54" t="s">
         <v>118</v>
@@ -9975,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="AV54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW54" t="s">
         <v>62</v>
@@ -10016,13 +10028,13 @@
         <v>175</v>
       </c>
       <c r="K55" t="n">
-        <v>26.0964452779433</v>
+        <v>26.2468100668819</v>
       </c>
       <c r="L55" t="n">
-        <v>24.6504806507271</v>
+        <v>24.7603367170092</v>
       </c>
       <c r="M55" t="n">
-        <v>5.86586788186405</v>
+        <v>6.00344561894277</v>
       </c>
       <c r="N55" t="s">
         <v>56</v>
@@ -10034,10 +10046,10 @@
         <v>0.174282263786151</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.07722494186137</v>
+        <v>4.08515411030988</v>
       </c>
       <c r="R55" t="n">
-        <v>2.12605858362084</v>
+        <v>2.12981018929457</v>
       </c>
       <c r="S55" t="n">
         <v>-4.5</v>
@@ -10164,16 +10176,16 @@
         <v>55</v>
       </c>
       <c r="K56" t="n">
-        <v>34.1634835295104</v>
+        <v>34.3618008711833</v>
       </c>
       <c r="L56" t="n">
-        <v>25.6889288466478</v>
+        <v>25.8215853343661</v>
       </c>
       <c r="M56" t="n">
-        <v>32.9891321411341</v>
+        <v>33.0739395983211</v>
       </c>
       <c r="N56" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O56" t="n">
         <v>0.194534517090508</v>
@@ -10182,10 +10194,10 @@
         <v>0.178922904817572</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.46514159755109</v>
+        <v>5.47729949734269</v>
       </c>
       <c r="R56" t="n">
-        <v>2.71385614607453</v>
+        <v>2.71907956972744</v>
       </c>
       <c r="S56" t="n">
         <v>-5</v>
@@ -10255,7 +10267,7 @@
         <v>0</v>
       </c>
       <c r="AP56" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ56" t="s">
         <v>118</v>
@@ -10271,7 +10283,7 @@
         <v>0</v>
       </c>
       <c r="AV56" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW56" t="s">
         <v>62</v>
@@ -10312,16 +10324,16 @@
         <v>178</v>
       </c>
       <c r="K57" t="n">
-        <v>47.0135592947248</v>
+        <v>46.9111148321385</v>
       </c>
       <c r="L57" t="n">
-        <v>44.6260597947345</v>
+        <v>44.5465478841871</v>
       </c>
       <c r="M57" t="n">
-        <v>5.35001187864672</v>
+        <v>5.30808123246471</v>
       </c>
       <c r="N57" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O57" t="n">
         <v>0.184376786961971</v>
@@ -10330,10 +10342,10 @@
         <v>0.169580343877061</v>
       </c>
       <c r="Q57" t="n">
-        <v>6.95133987040596</v>
+        <v>6.91563242423712</v>
       </c>
       <c r="R57" t="n">
-        <v>3.29228807586676</v>
+        <v>3.27590224456929</v>
       </c>
       <c r="S57" t="n">
         <v>-5.2</v>
@@ -10403,7 +10415,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ57" t="s">
         <v>118</v>
@@ -10419,7 +10431,7 @@
         <v>1</v>
       </c>
       <c r="AV57" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW57" t="s">
         <v>62</v>
@@ -10460,16 +10472,16 @@
         <v>180</v>
       </c>
       <c r="K58" t="n">
-        <v>59.3622111625462</v>
+        <v>59.3227403728656</v>
       </c>
       <c r="L58" t="n">
-        <v>51.4174807197943</v>
+        <v>51.4704065877509</v>
       </c>
       <c r="M58" t="n">
-        <v>15.4514191118146</v>
+        <v>15.2560166233143</v>
       </c>
       <c r="N58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O58" t="n">
         <v>0.210727464160382</v>
@@ -10478,10 +10490,10 @@
         <v>0.184129588686787</v>
       </c>
       <c r="Q58" t="n">
-        <v>9.95728045595108</v>
+        <v>9.92143946926129</v>
       </c>
       <c r="R58" t="n">
-        <v>4.71066670652139</v>
+        <v>4.69593637898484</v>
       </c>
       <c r="S58" t="n">
         <v>-5.8</v>
@@ -10608,16 +10620,16 @@
         <v>95</v>
       </c>
       <c r="K59" t="n">
-        <v>156.936923422479</v>
+        <v>157.224276919776</v>
       </c>
       <c r="L59" t="n">
-        <v>106.051961823966</v>
+        <v>106.277364505845</v>
       </c>
       <c r="M59" t="n">
-        <v>47.9811601061906</v>
+        <v>47.9376889432833</v>
       </c>
       <c r="N59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O59" t="n">
         <v>0.189286216437061</v>
@@ -10626,10 +10638,10 @@
         <v>0.174095786153413</v>
       </c>
       <c r="Q59" t="n">
-        <v>27.157887786811</v>
+        <v>27.1097908696799</v>
       </c>
       <c r="R59" t="n">
-        <v>12.1428361342888</v>
+        <v>12.127529006199</v>
       </c>
       <c r="S59" t="n">
         <v>-7.6</v>
@@ -10699,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="AP59" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ59" t="s">
         <v>118</v>
@@ -10715,7 +10727,7 @@
         <v>0</v>
       </c>
       <c r="AV59" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW59" t="s">
         <v>62</v>
@@ -10756,16 +10768,16 @@
         <v>117</v>
       </c>
       <c r="K60" t="n">
-        <v>1.07172397301965</v>
+        <v>1.07183534946294</v>
       </c>
       <c r="L60" t="n">
-        <v>1.07927994042673</v>
+        <v>1.07937313142869</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.700093379303113</v>
+        <v>-0.698348119503089</v>
       </c>
       <c r="N60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O60" t="n">
         <v>0.20630614559854</v>
@@ -10774,10 +10786,10 @@
         <v>0.189670220451166</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.00700288055791</v>
+        <v>1.00702925805344</v>
       </c>
       <c r="R60" t="n">
-        <v>1.00163968580717</v>
+        <v>1.00163973630715</v>
       </c>
       <c r="S60" t="n">
         <v>4.3</v>
@@ -10847,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="AP60" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ60" t="s">
         <v>118</v>
@@ -10863,7 +10875,7 @@
         <v>0</v>
       </c>
       <c r="AV60" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW60" t="s">
         <v>62</v>
@@ -10904,13 +10916,13 @@
         <v>131</v>
       </c>
       <c r="K61" t="n">
-        <v>20.2503563595032</v>
+        <v>20.2659389347716</v>
       </c>
       <c r="L61" t="n">
-        <v>18.3058758923668</v>
+        <v>18.3327222731439</v>
       </c>
       <c r="M61" t="n">
-        <v>10.6221656836816</v>
+        <v>10.5451696306974</v>
       </c>
       <c r="N61" t="s">
         <v>56</v>
@@ -10922,10 +10934,10 @@
         <v>0.161542916689964</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.37330988653431</v>
+        <v>1.37615446443268</v>
       </c>
       <c r="R61" t="n">
-        <v>1.03908856555065</v>
+        <v>1.03943436943015</v>
       </c>
       <c r="S61" t="n">
         <v>-4.3</v>
@@ -11052,16 +11064,16 @@
         <v>188</v>
       </c>
       <c r="K62" t="n">
-        <v>73.2762174585862</v>
+        <v>72.6399251473632</v>
       </c>
       <c r="L62" t="n">
-        <v>73.4790595150624</v>
+        <v>72.7309090909091</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.276054236152401</v>
+        <v>-0.125096667542157</v>
       </c>
       <c r="N62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O62" t="n">
         <v>0.180798884066448</v>
@@ -11070,10 +11082,10 @@
         <v>0.166219790005376</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.39511104784305</v>
+        <v>4.37003522900108</v>
       </c>
       <c r="R62" t="n">
-        <v>1.21217285022524</v>
+        <v>1.21162696793261</v>
       </c>
       <c r="S62" t="n">
         <v>-6</v>
@@ -11145,7 +11157,7 @@
         <v>1</v>
       </c>
       <c r="AP62" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ62" t="s">
         <v>118</v>
@@ -11161,7 +11173,7 @@
         <v>1</v>
       </c>
       <c r="AV62" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW62" t="s">
         <v>62</v>
@@ -11202,16 +11214,16 @@
         <v>140</v>
       </c>
       <c r="K63" t="n">
-        <v>417.689151278263</v>
+        <v>415.812596874204</v>
       </c>
       <c r="L63" t="n">
-        <v>283.300283286119</v>
+        <v>281.704225352113</v>
       </c>
       <c r="M63" t="n">
-        <v>47.436898556299</v>
+        <v>47.6060915857632</v>
       </c>
       <c r="N63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O63" t="n">
         <v>0.195217174420103</v>
@@ -11220,10 +11232,10 @@
         <v>0.1794754315277</v>
       </c>
       <c r="Q63" t="n">
-        <v>32.3631663305415</v>
+        <v>32.23870060884</v>
       </c>
       <c r="R63" t="n">
-        <v>7.68096208804551</v>
+        <v>7.6866633744465</v>
       </c>
       <c r="S63" t="n">
         <v>-9.2</v>
@@ -11293,7 +11305,7 @@
         <v>1</v>
       </c>
       <c r="AP63" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ63" t="s">
         <v>118</v>
@@ -11309,7 +11321,7 @@
         <v>1</v>
       </c>
       <c r="AV63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW63" t="s">
         <v>62</v>
@@ -11350,16 +11362,16 @@
         <v>113</v>
       </c>
       <c r="K64" t="n">
-        <v>666.240815175775</v>
+        <v>664.213327954876</v>
       </c>
       <c r="L64" t="n">
         <v>591.745562130178</v>
       </c>
       <c r="M64" t="n">
-        <v>12.5890683112904</v>
+        <v>12.2464401023689</v>
       </c>
       <c r="N64" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O64" t="n">
         <v>0.209166404566918</v>
@@ -11368,10 +11380,10 @@
         <v>0.192299836488564</v>
       </c>
       <c r="Q64" t="n">
-        <v>49.1121803542976</v>
+        <v>48.857106085623</v>
       </c>
       <c r="R64" t="n">
-        <v>11.8908539482399</v>
+        <v>11.8844794262101</v>
       </c>
       <c r="S64" t="n">
         <v>-9.2</v>
@@ -11443,7 +11455,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ64" t="s">
         <v>118</v>
@@ -11459,7 +11471,7 @@
         <v>1</v>
       </c>
       <c r="AV64" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW64" t="s">
         <v>62</v>
@@ -11500,13 +11512,13 @@
         <v>131</v>
       </c>
       <c r="K65" t="n">
-        <v>1.84001529536852</v>
+        <v>1.83937345284614</v>
       </c>
       <c r="L65" t="n">
-        <v>1.65608491893951</v>
+        <v>1.65509822418615</v>
       </c>
       <c r="M65" t="n">
-        <v>11.106337261183</v>
+        <v>11.1337941136758</v>
       </c>
       <c r="N65" t="s">
         <v>56</v>
@@ -11518,10 +11530,10 @@
         <v>0.173590431393282</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.21595110307706</v>
+        <v>1.21562725742662</v>
       </c>
       <c r="R65" t="n">
-        <v>1.06683357950359</v>
+        <v>1.06670548093165</v>
       </c>
       <c r="S65" t="n">
         <v>1.4</v>
@@ -11648,12 +11660,12 @@
         <v>86</v>
       </c>
       <c r="K66" t="n">
-        <v>5.05231413430149</v>
+        <v>5.04651722418458</v>
       </c>
       <c r="L66"/>
       <c r="M66"/>
       <c r="N66" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O66" t="n">
         <v>0.30256386655721</v>
@@ -11662,10 +11674,10 @@
         <v>0.214433592660986</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.06300619480696</v>
+        <v>2.06033978657003</v>
       </c>
       <c r="R66" t="n">
-        <v>1.37360976651235</v>
+        <v>1.37240851399241</v>
       </c>
       <c r="S66" t="n">
         <v>-1.4</v>
@@ -11733,7 +11745,7 @@
         <v>1</v>
       </c>
       <c r="AV66" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW66" t="s">
         <v>62</v>
@@ -11774,16 +11786,16 @@
         <v>97</v>
       </c>
       <c r="K67" t="n">
-        <v>9.74506447683597</v>
+        <v>9.72794811498859</v>
       </c>
       <c r="L67" t="n">
-        <v>12.4493962405079</v>
+        <v>12.4370103220992</v>
       </c>
       <c r="M67" t="n">
-        <v>-21.7225937019545</v>
+        <v>-21.7822622716405</v>
       </c>
       <c r="N67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O67" t="n">
         <v>0.282366488432476</v>
@@ -11792,10 +11804,10 @@
         <v>0.204720513169133</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.69579915907187</v>
+        <v>3.68684155181817</v>
       </c>
       <c r="R67" t="n">
-        <v>1.95192936897625</v>
+        <v>1.94733785453135</v>
       </c>
       <c r="S67" t="n">
         <v>-2.4</v>
@@ -11867,7 +11879,7 @@
         <v>1</v>
       </c>
       <c r="AP67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ67" t="s">
         <v>58</v>
@@ -11883,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="AV67" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW67" t="s">
         <v>62</v>
@@ -11924,16 +11936,16 @@
         <v>106</v>
       </c>
       <c r="K68" t="n">
-        <v>10.4311908538181</v>
+        <v>10.4819828707235</v>
       </c>
       <c r="L68" t="n">
-        <v>8.98930337078652</v>
+        <v>9.03968182229052</v>
       </c>
       <c r="M68" t="n">
-        <v>16.0400358465757</v>
+        <v>15.9552191856632</v>
       </c>
       <c r="N68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O68" t="n">
         <v>0.232862983947003</v>
@@ -11942,10 +11954,10 @@
         <v>0.177711484201139</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.79570625001345</v>
+        <v>3.81325643226895</v>
       </c>
       <c r="R68" t="n">
-        <v>2.01194383611338</v>
+        <v>2.01817848817603</v>
       </c>
       <c r="S68" t="n">
         <v>-2.7</v>
@@ -12015,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="AP68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ68" t="s">
         <v>58</v>
@@ -12031,7 +12043,7 @@
         <v>0</v>
       </c>
       <c r="AV68" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW68" t="s">
         <v>62</v>
@@ -12072,16 +12084,16 @@
         <v>188</v>
       </c>
       <c r="K69" t="n">
-        <v>26.2074950891221</v>
+        <v>26.2422240702277</v>
       </c>
       <c r="L69" t="n">
-        <v>29.4568483063328</v>
+        <v>29.4915953995871</v>
       </c>
       <c r="M69" t="n">
-        <v>-11.0308923188915</v>
+        <v>-11.0179571004318</v>
       </c>
       <c r="N69" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O69" t="n">
         <v>0.27341132448237</v>
@@ -12090,10 +12102,10 @@
         <v>0.198227866787628</v>
       </c>
       <c r="Q69" t="n">
-        <v>9.62903321356002</v>
+        <v>9.63562238805346</v>
       </c>
       <c r="R69" t="n">
-        <v>4.66069212623719</v>
+        <v>4.66225739936272</v>
       </c>
       <c r="S69" t="n">
         <v>-4.1</v>
@@ -12217,19 +12229,19 @@
         <v>198</v>
       </c>
       <c r="J70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K70" t="n">
-        <v>45.5420016784768</v>
+        <v>45.7138103113957</v>
       </c>
       <c r="L70" t="n">
-        <v>57.5077630822312</v>
+        <v>57.7735413056037</v>
       </c>
       <c r="M70" t="n">
-        <v>-20.8072106484899</v>
+        <v>-20.8741419024599</v>
       </c>
       <c r="N70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O70" t="n">
         <v>0.319659379505316</v>
@@ -12238,10 +12250,10 @@
         <v>0.226549554495945</v>
       </c>
       <c r="Q70" t="n">
-        <v>18.1873245148265</v>
+        <v>18.2604737122813</v>
       </c>
       <c r="R70" t="n">
-        <v>9.03080640076085</v>
+        <v>9.05946165072416</v>
       </c>
       <c r="S70" t="n">
         <v>-5.1</v>
@@ -12301,7 +12313,7 @@
         <v>1</v>
       </c>
       <c r="AP70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ70" t="s">
         <v>58</v>
@@ -12317,7 +12329,7 @@
         <v>0</v>
       </c>
       <c r="AV70" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW70" t="s">
         <v>62</v>
@@ -12367,7 +12379,7 @@
         <v>28.198849455323</v>
       </c>
       <c r="N71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O71" t="n">
         <v>0.293890392530775</v>
@@ -12451,7 +12463,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ71" t="s">
         <v>58</v>
@@ -12467,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="AV71" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW71" t="s">
         <v>62</v>
@@ -12513,7 +12525,7 @@
       <c r="L72"/>
       <c r="M72"/>
       <c r="N72" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O72" t="n">
         <v>0.358701438423957</v>
@@ -12593,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="AV72" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW72" t="s">
         <v>62</v>
@@ -12639,7 +12651,7 @@
       <c r="L73"/>
       <c r="M73"/>
       <c r="N73" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O73" t="n">
         <v>0.358701438423957</v>
@@ -12719,7 +12731,7 @@
         <v>0</v>
       </c>
       <c r="AV73" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW73" t="s">
         <v>62</v>
@@ -12765,7 +12777,7 @@
       <c r="L74"/>
       <c r="M74"/>
       <c r="N74" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O74" t="n">
         <v>0.358701438423957</v>
@@ -12845,7 +12857,7 @@
         <v>0</v>
       </c>
       <c r="AV74" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW74" t="s">
         <v>62</v>
@@ -12891,7 +12903,7 @@
       <c r="L75"/>
       <c r="M75"/>
       <c r="N75" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O75" t="n">
         <v>0.358701438423957</v>
@@ -12971,7 +12983,7 @@
         <v>0</v>
       </c>
       <c r="AV75" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW75" t="s">
         <v>62</v>
@@ -13017,7 +13029,7 @@
       <c r="L76"/>
       <c r="M76"/>
       <c r="N76" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O76" t="n">
         <v>0.358701438423957</v>
@@ -13097,7 +13109,7 @@
         <v>0</v>
       </c>
       <c r="AV76" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW76" t="s">
         <v>62</v>
@@ -13297,7 +13309,7 @@
         <v>31.3051099129022</v>
       </c>
       <c r="N78" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O78" t="n">
         <v>0.281039275702189</v>
@@ -13595,7 +13607,7 @@
         <v>-2.10270710769686</v>
       </c>
       <c r="N80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O80" t="n">
         <v>0.168118937747013</v>
@@ -13679,7 +13691,7 @@
         <v>1</v>
       </c>
       <c r="AP80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ80" t="s">
         <v>118</v>
@@ -13695,7 +13707,7 @@
         <v>1</v>
       </c>
       <c r="AV80" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW80" t="s">
         <v>62</v>
@@ -13745,7 +13757,7 @@
         <v>-3.75332417754183</v>
       </c>
       <c r="N81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O81" t="n">
         <v>0.189409917295146</v>
@@ -13829,7 +13841,7 @@
         <v>1</v>
       </c>
       <c r="AP81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ81" t="s">
         <v>118</v>
@@ -13845,7 +13857,7 @@
         <v>0</v>
       </c>
       <c r="AV81" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW81" t="s">
         <v>62</v>
@@ -13895,7 +13907,7 @@
         <v>1.31449680009221</v>
       </c>
       <c r="N82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O82" t="n">
         <v>0.176949212237029</v>
@@ -13979,7 +13991,7 @@
         <v>0</v>
       </c>
       <c r="AP82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ82" t="s">
         <v>118</v>
@@ -13995,7 +14007,7 @@
         <v>0</v>
       </c>
       <c r="AV82" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW82" t="s">
         <v>62</v>
@@ -14045,7 +14057,7 @@
         <v>11.2140877634154</v>
       </c>
       <c r="N83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O83" t="n">
         <v>0.177618021394308</v>
@@ -14129,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="AP83" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ83" t="s">
         <v>118</v>
@@ -14145,7 +14157,7 @@
         <v>0</v>
       </c>
       <c r="AV83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW83" t="s">
         <v>62</v>
@@ -14195,7 +14207,7 @@
         <v>0.755178039145599</v>
       </c>
       <c r="N84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O84" t="n">
         <v>0.175899027799507</v>
@@ -14279,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="AP84" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ84" t="s">
         <v>118</v>
@@ -14295,7 +14307,7 @@
         <v>0</v>
       </c>
       <c r="AV84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW84" t="s">
         <v>62</v>
@@ -14495,7 +14507,7 @@
         <v>-13.1179569938516</v>
       </c>
       <c r="N86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O86" t="n">
         <v>0.2405593471922</v>
@@ -14579,7 +14591,7 @@
         <v>1</v>
       </c>
       <c r="AP86" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ86" t="s">
         <v>58</v>
@@ -14595,7 +14607,7 @@
         <v>0</v>
       </c>
       <c r="AV86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW86" t="s">
         <v>62</v>
@@ -14645,7 +14657,7 @@
         <v>26.5149658987762</v>
       </c>
       <c r="N87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O87" t="n">
         <v>0.260063115258339</v>
@@ -14729,7 +14741,7 @@
         <v>1</v>
       </c>
       <c r="AP87" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ87" t="s">
         <v>58</v>
@@ -14745,7 +14757,7 @@
         <v>0</v>
       </c>
       <c r="AV87" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW87" t="s">
         <v>62</v>
@@ -14795,7 +14807,7 @@
         <v>6.00506878265836</v>
       </c>
       <c r="N88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O88" t="n">
         <v>0.233640289057751</v>
@@ -14879,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="AP88" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ88" t="s">
         <v>58</v>
@@ -14895,7 +14907,7 @@
         <v>0</v>
       </c>
       <c r="AV88" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW88" t="s">
         <v>62</v>
@@ -14945,7 +14957,7 @@
         <v>0.233965667374769</v>
       </c>
       <c r="N89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O89" t="n">
         <v>0.275184677778951</v>
@@ -15029,7 +15041,7 @@
         <v>1</v>
       </c>
       <c r="AP89" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ89" t="s">
         <v>58</v>
@@ -15045,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="AV89" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW89" t="s">
         <v>62</v>
@@ -15095,7 +15107,7 @@
         <v>12.2649426587847</v>
       </c>
       <c r="N90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O90" t="n">
         <v>0.227325833283534</v>
@@ -15179,7 +15191,7 @@
         <v>0</v>
       </c>
       <c r="AP90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ90" t="s">
         <v>58</v>
@@ -15195,7 +15207,7 @@
         <v>0</v>
       </c>
       <c r="AV90" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW90" t="s">
         <v>62</v>
@@ -15241,7 +15253,7 @@
       <c r="L91"/>
       <c r="M91"/>
       <c r="N91" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O91" t="n">
         <v>0.309820778490077</v>
@@ -15321,7 +15333,7 @@
         <v>0</v>
       </c>
       <c r="AV91" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW91" t="s">
         <v>62</v>
@@ -15367,7 +15379,7 @@
       <c r="L92"/>
       <c r="M92"/>
       <c r="N92" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O92" t="n">
         <v>0.309820778490077</v>
@@ -15447,7 +15459,7 @@
         <v>0</v>
       </c>
       <c r="AV92" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW92" t="s">
         <v>62</v>
@@ -15493,7 +15505,7 @@
       <c r="L93"/>
       <c r="M93"/>
       <c r="N93" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O93" t="n">
         <v>0.309820778490077</v>
@@ -15573,7 +15585,7 @@
         <v>0</v>
       </c>
       <c r="AV93" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW93" t="s">
         <v>62</v>
@@ -15623,7 +15635,7 @@
         <v>-11.7765172412735</v>
       </c>
       <c r="N94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O94" t="n">
         <v>0.283808682525441</v>
@@ -15707,7 +15719,7 @@
         <v>1</v>
       </c>
       <c r="AP94" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ94" t="s">
         <v>58</v>
@@ -15723,7 +15735,7 @@
         <v>0</v>
       </c>
       <c r="AV94" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW94" t="s">
         <v>62</v>
@@ -15773,7 +15785,7 @@
         <v>19.2356539699841</v>
       </c>
       <c r="N95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O95" t="n">
         <v>0.339883979110624</v>
@@ -15913,7 +15925,7 @@
         <v>14.8171566590343</v>
       </c>
       <c r="N96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O96" t="n">
         <v>0.339883979110624</v>
@@ -15985,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="AP96" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ96" t="s">
         <v>58</v>
@@ -16001,7 +16013,7 @@
         <v>0</v>
       </c>
       <c r="AV96" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW96" t="s">
         <v>62</v>
@@ -16051,7 +16063,7 @@
         <v>10.7482722873243</v>
       </c>
       <c r="N97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O97" t="n">
         <v>0.339883979110624</v>
@@ -16125,7 +16137,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ97" t="s">
         <v>58</v>
@@ -16141,7 +16153,7 @@
         <v>0</v>
       </c>
       <c r="AV97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW97" t="s">
         <v>62</v>
@@ -16191,7 +16203,7 @@
         <v>16.9934582480623</v>
       </c>
       <c r="N98" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O98" t="n">
         <v>0.26067188127574</v>
@@ -16275,7 +16287,7 @@
         <v>1</v>
       </c>
       <c r="AP98" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ98" t="s">
         <v>58</v>
@@ -16291,7 +16303,7 @@
         <v>0</v>
       </c>
       <c r="AV98" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW98" t="s">
         <v>62</v>
@@ -16337,7 +16349,7 @@
       <c r="L99"/>
       <c r="M99"/>
       <c r="N99" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O99" t="n">
         <v>0.339883979110624</v>
@@ -16417,7 +16429,7 @@
         <v>0</v>
       </c>
       <c r="AV99" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW99" t="s">
         <v>62</v>
@@ -16463,7 +16475,7 @@
       <c r="L100"/>
       <c r="M100"/>
       <c r="N100" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O100" t="n">
         <v>0.339883979110624</v>
@@ -16543,7 +16555,7 @@
         <v>0</v>
       </c>
       <c r="AV100" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW100" t="s">
         <v>62</v>
@@ -16593,7 +16605,7 @@
         <v>23.5585853011938</v>
       </c>
       <c r="N101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O101" t="n">
         <v>0.258020477716358</v>
@@ -16677,7 +16689,7 @@
         <v>1</v>
       </c>
       <c r="AP101" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ101" t="s">
         <v>58</v>
@@ -16693,7 +16705,7 @@
         <v>0</v>
       </c>
       <c r="AV101" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW101" t="s">
         <v>62</v>
@@ -16743,7 +16755,7 @@
         <v>4.51469264767344</v>
       </c>
       <c r="N102" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O102" t="n">
         <v>0.213924818112413</v>
@@ -16827,7 +16839,7 @@
         <v>1</v>
       </c>
       <c r="AP102" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ102" t="s">
         <v>118</v>
@@ -16843,7 +16855,7 @@
         <v>0</v>
       </c>
       <c r="AV102" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW102" t="s">
         <v>62</v>
@@ -16893,7 +16905,7 @@
         <v>-31.3232281690065</v>
       </c>
       <c r="N103" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O103" t="n">
         <v>0.208463294069909</v>
@@ -16977,7 +16989,7 @@
         <v>1</v>
       </c>
       <c r="AP103" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ103" t="s">
         <v>118</v>
@@ -16993,7 +17005,7 @@
         <v>0</v>
       </c>
       <c r="AV103" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW103" t="s">
         <v>62</v>
@@ -17043,7 +17055,7 @@
         <v>5.44799155717299</v>
       </c>
       <c r="N104" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O104" t="n">
         <v>0.17467339390136</v>
@@ -17127,7 +17139,7 @@
         <v>0</v>
       </c>
       <c r="AP104" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ104" t="s">
         <v>118</v>
@@ -17143,7 +17155,7 @@
         <v>0</v>
       </c>
       <c r="AV104" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW104" t="s">
         <v>62</v>
@@ -17193,7 +17205,7 @@
         <v>26.898399562472</v>
       </c>
       <c r="N105" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O105" t="n">
         <v>0.182798090652848</v>
@@ -17277,7 +17289,7 @@
         <v>1</v>
       </c>
       <c r="AP105" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ105" t="s">
         <v>118</v>
@@ -17293,7 +17305,7 @@
         <v>0</v>
       </c>
       <c r="AV105" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW105" t="s">
         <v>62</v>
@@ -17483,7 +17495,7 @@
         <v>27.8240452415797</v>
       </c>
       <c r="N107" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O107" t="n">
         <v>0.175996303907521</v>
@@ -17567,7 +17579,7 @@
         <v>1</v>
       </c>
       <c r="AP107" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ107" t="s">
         <v>118</v>
@@ -17583,7 +17595,7 @@
         <v>0</v>
       </c>
       <c r="AV107" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW107" t="s">
         <v>62</v>
@@ -17783,7 +17795,7 @@
         <v>19.6109300799005</v>
       </c>
       <c r="N109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O109" t="n">
         <v>0.178112281656771</v>
@@ -17867,7 +17879,7 @@
         <v>1</v>
       </c>
       <c r="AP109" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ109" t="s">
         <v>118</v>
@@ -17883,7 +17895,7 @@
         <v>0</v>
       </c>
       <c r="AV109" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW109" t="s">
         <v>62</v>
@@ -18083,7 +18095,7 @@
         <v>3.28962084122495</v>
       </c>
       <c r="N111" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O111" t="n">
         <v>0.266269036501533</v>
@@ -18167,7 +18179,7 @@
         <v>0</v>
       </c>
       <c r="AP111" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ111" t="s">
         <v>58</v>
@@ -18183,7 +18195,7 @@
         <v>0</v>
       </c>
       <c r="AV111" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW111" t="s">
         <v>62</v>
@@ -18233,7 +18245,7 @@
         <v>-7.34346298676889</v>
       </c>
       <c r="N112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O112" t="n">
         <v>0.268061980914793</v>
@@ -18317,7 +18329,7 @@
         <v>1</v>
       </c>
       <c r="AP112" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ112" t="s">
         <v>58</v>
@@ -18333,7 +18345,7 @@
         <v>0</v>
       </c>
       <c r="AV112" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW112" t="s">
         <v>62</v>
@@ -18383,7 +18395,7 @@
         <v>2.41080202755841</v>
       </c>
       <c r="N113" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O113" t="n">
         <v>0.270696957111369</v>
@@ -18467,7 +18479,7 @@
         <v>1</v>
       </c>
       <c r="AP113" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ113" t="s">
         <v>58</v>
@@ -18483,7 +18495,7 @@
         <v>0</v>
       </c>
       <c r="AV113" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW113" t="s">
         <v>62</v>
@@ -18533,7 +18545,7 @@
         <v>-2.23923103781071</v>
       </c>
       <c r="N114" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O114" t="n">
         <v>0.335447459208469</v>
@@ -18669,7 +18681,7 @@
       <c r="L115"/>
       <c r="M115"/>
       <c r="N115" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O115" t="n">
         <v>0.335447459208469</v>
@@ -18749,7 +18761,7 @@
         <v>0</v>
       </c>
       <c r="AV115" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW115" t="s">
         <v>62</v>
@@ -18795,7 +18807,7 @@
       <c r="L116"/>
       <c r="M116"/>
       <c r="N116" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O116" t="n">
         <v>0.335447459208469</v>
@@ -18875,7 +18887,7 @@
         <v>0</v>
       </c>
       <c r="AV116" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW116" t="s">
         <v>62</v>
@@ -18925,7 +18937,7 @@
         <v>34.7514839775029</v>
       </c>
       <c r="N117" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O117" t="n">
         <v>0.269672295625439</v>
@@ -19009,7 +19021,7 @@
         <v>1</v>
       </c>
       <c r="AP117" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ117" t="s">
         <v>58</v>
@@ -19025,7 +19037,7 @@
         <v>0</v>
       </c>
       <c r="AV117" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW117" t="s">
         <v>62</v>
@@ -19075,7 +19087,7 @@
         <v>-11.1992013947073</v>
       </c>
       <c r="N118" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O118" t="n">
         <v>0.280696797212448</v>
@@ -19225,7 +19237,7 @@
         <v>27.087132545736</v>
       </c>
       <c r="N119" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O119" t="n">
         <v>0.246182607113973</v>
@@ -19309,7 +19321,7 @@
         <v>1</v>
       </c>
       <c r="AP119" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ119" t="s">
         <v>58</v>
@@ -19325,7 +19337,7 @@
         <v>0</v>
       </c>
       <c r="AV119" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW119" t="s">
         <v>62</v>
@@ -19375,7 +19387,7 @@
         <v>9.56153431254092</v>
       </c>
       <c r="N120" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O120" t="n">
         <v>0.246751232370215</v>
@@ -19459,7 +19471,7 @@
         <v>1</v>
       </c>
       <c r="AP120" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ120" t="s">
         <v>58</v>
@@ -19475,7 +19487,7 @@
         <v>0</v>
       </c>
       <c r="AV120" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW120" t="s">
         <v>62</v>
@@ -19525,7 +19537,7 @@
         <v>-9.06541174637384</v>
       </c>
       <c r="N121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O121" t="n">
         <v>0.277020638923289</v>
@@ -19609,7 +19621,7 @@
         <v>1</v>
       </c>
       <c r="AP121" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ121" t="s">
         <v>58</v>
@@ -19625,7 +19637,7 @@
         <v>0</v>
       </c>
       <c r="AV121" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW121" t="s">
         <v>62</v>
@@ -19675,7 +19687,7 @@
         <v>-6.29848797318829</v>
       </c>
       <c r="N122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O122" t="n">
         <v>0.25967026493458</v>
@@ -19759,7 +19771,7 @@
         <v>0</v>
       </c>
       <c r="AP122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ122" t="s">
         <v>58</v>
@@ -19775,7 +19787,7 @@
         <v>0</v>
       </c>
       <c r="AV122" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW122" t="s">
         <v>62</v>
@@ -19821,7 +19833,7 @@
       <c r="L123"/>
       <c r="M123"/>
       <c r="N123" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O123" t="n">
         <v>0.341579841999037</v>
@@ -19901,7 +19913,7 @@
         <v>0</v>
       </c>
       <c r="AV123" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW123" t="s">
         <v>62</v>
@@ -19951,7 +19963,7 @@
         <v>-1.86183838129252</v>
       </c>
       <c r="N124" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O124" t="n">
         <v>0.275446192859705</v>
@@ -20101,7 +20113,7 @@
         <v>-20.5831276796656</v>
       </c>
       <c r="N125" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O125" t="n">
         <v>0.282477498853569</v>
@@ -20251,7 +20263,7 @@
         <v>-16.2148667329646</v>
       </c>
       <c r="N126" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O126" t="n">
         <v>0.169088334166879</v>
@@ -20335,7 +20347,7 @@
         <v>1</v>
       </c>
       <c r="AP126" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ126" t="s">
         <v>104</v>
@@ -20351,7 +20363,7 @@
         <v>1</v>
       </c>
       <c r="AV126" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW126" t="s">
         <v>62</v>
@@ -20401,7 +20413,7 @@
         <v>20.7573824446357</v>
       </c>
       <c r="N127" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O127" t="n">
         <v>0.159839385854159</v>
@@ -20485,7 +20497,7 @@
         <v>1</v>
       </c>
       <c r="AP127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ127" t="s">
         <v>104</v>
@@ -20501,7 +20513,7 @@
         <v>1</v>
       </c>
       <c r="AV127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW127" t="s">
         <v>62</v>
@@ -20551,7 +20563,7 @@
         <v>6.97945132710356</v>
       </c>
       <c r="N128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O128" t="n">
         <v>0.161305771677828</v>
@@ -20635,7 +20647,7 @@
         <v>1</v>
       </c>
       <c r="AP128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ128" t="s">
         <v>104</v>
@@ -20651,7 +20663,7 @@
         <v>0</v>
       </c>
       <c r="AV128" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW128" t="s">
         <v>62</v>
@@ -20701,7 +20713,7 @@
         <v>17.2450262559394</v>
       </c>
       <c r="N129" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O129" t="n">
         <v>0.167864928006107</v>
@@ -20785,7 +20797,7 @@
         <v>1</v>
       </c>
       <c r="AP129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ129" t="s">
         <v>104</v>
@@ -20801,7 +20813,7 @@
         <v>0</v>
       </c>
       <c r="AV129" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW129" t="s">
         <v>62</v>
@@ -20851,7 +20863,7 @@
         <v>23.1833338329214</v>
       </c>
       <c r="N130" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O130" t="n">
         <v>0.166651080290938</v>
@@ -20935,7 +20947,7 @@
         <v>1</v>
       </c>
       <c r="AP130" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ130" t="s">
         <v>104</v>
@@ -20951,7 +20963,7 @@
         <v>0</v>
       </c>
       <c r="AV130" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW130" t="s">
         <v>62</v>
@@ -21001,7 +21013,7 @@
         <v>18.9454374712623</v>
       </c>
       <c r="N131" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O131" t="n">
         <v>0.161192658482776</v>
@@ -21085,7 +21097,7 @@
         <v>1</v>
       </c>
       <c r="AP131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ131" t="s">
         <v>104</v>
@@ -21101,7 +21113,7 @@
         <v>0</v>
       </c>
       <c r="AV131" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW131" t="s">
         <v>62</v>
@@ -21151,7 +21163,7 @@
         <v>10.1517664578619</v>
       </c>
       <c r="N132" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O132" t="n">
         <v>0.169622510876998</v>
@@ -21235,7 +21247,7 @@
         <v>1</v>
       </c>
       <c r="AP132" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ132" t="s">
         <v>104</v>
@@ -21251,7 +21263,7 @@
         <v>0</v>
       </c>
       <c r="AV132" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW132" t="s">
         <v>62</v>
@@ -21301,7 +21313,7 @@
         <v>-11.8589341563519</v>
       </c>
       <c r="N133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O133" t="n">
         <v>0.271779973430504</v>
@@ -21385,7 +21397,7 @@
         <v>1</v>
       </c>
       <c r="AP133" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ133" t="s">
         <v>58</v>
@@ -21401,7 +21413,7 @@
         <v>0</v>
       </c>
       <c r="AV133" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW133" t="s">
         <v>62</v>
@@ -21451,7 +21463,7 @@
         <v>-15.8008243551825</v>
       </c>
       <c r="N134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O134" t="n">
         <v>0.283525702327891</v>
@@ -21535,7 +21547,7 @@
         <v>1</v>
       </c>
       <c r="AP134" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ134" t="s">
         <v>58</v>
@@ -21551,7 +21563,7 @@
         <v>0</v>
       </c>
       <c r="AV134" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW134" t="s">
         <v>62</v>
@@ -21751,7 +21763,7 @@
         <v>40.9559809614787</v>
       </c>
       <c r="N136" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O136" t="n">
         <v>0.25799324887992</v>
@@ -21835,7 +21847,7 @@
         <v>1</v>
       </c>
       <c r="AP136" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ136" t="s">
         <v>58</v>
@@ -21851,7 +21863,7 @@
         <v>0</v>
       </c>
       <c r="AV136" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW136" t="s">
         <v>62</v>
@@ -21901,7 +21913,7 @@
         <v>35.2930853905869</v>
       </c>
       <c r="N137" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O137" t="n">
         <v>0.293370839561845</v>
@@ -21985,7 +21997,7 @@
         <v>1</v>
       </c>
       <c r="AP137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ137" t="s">
         <v>58</v>
@@ -22001,7 +22013,7 @@
         <v>0</v>
       </c>
       <c r="AV137" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW137" t="s">
         <v>62</v>
@@ -22047,7 +22059,7 @@
       <c r="L138"/>
       <c r="M138"/>
       <c r="N138" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O138" t="n">
         <v>0.33794123391405</v>
@@ -22127,7 +22139,7 @@
         <v>0</v>
       </c>
       <c r="AV138" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW138" t="s">
         <v>62</v>
@@ -22177,7 +22189,7 @@
         <v>-9.29916061095832</v>
       </c>
       <c r="N139" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O139" t="n">
         <v>0.33794123391405</v>
@@ -22251,7 +22263,7 @@
         <v>1</v>
       </c>
       <c r="AP139" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ139" t="s">
         <v>58</v>
@@ -22267,7 +22279,7 @@
         <v>0</v>
       </c>
       <c r="AV139" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW139" t="s">
         <v>62</v>
@@ -22317,7 +22329,7 @@
         <v>-4.97336270646259</v>
       </c>
       <c r="N140" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O140" t="n">
         <v>0.248644803997442</v>
@@ -22401,7 +22413,7 @@
         <v>1</v>
       </c>
       <c r="AP140" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ140" t="s">
         <v>58</v>
@@ -22417,7 +22429,7 @@
         <v>0</v>
       </c>
       <c r="AV140" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW140" t="s">
         <v>62</v>
@@ -22467,7 +22479,7 @@
         <v>9.30379002748905</v>
       </c>
       <c r="N141" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O141" t="n">
         <v>0.174815655546376</v>
@@ -22551,7 +22563,7 @@
         <v>1</v>
       </c>
       <c r="AP141" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ141" t="s">
         <v>104</v>
@@ -22567,7 +22579,7 @@
         <v>0</v>
       </c>
       <c r="AV141" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW141" t="s">
         <v>62</v>
@@ -22617,7 +22629,7 @@
         <v>9.03124887479585</v>
       </c>
       <c r="N142" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O142" t="n">
         <v>0.163405245049457</v>
@@ -22701,7 +22713,7 @@
         <v>0</v>
       </c>
       <c r="AP142" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ142" t="s">
         <v>104</v>
@@ -22717,7 +22729,7 @@
         <v>0</v>
       </c>
       <c r="AV142" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW142" t="s">
         <v>62</v>
@@ -22767,7 +22779,7 @@
         <v>-25.7476573585895</v>
       </c>
       <c r="N143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O143" t="n">
         <v>0.174002275297058</v>
@@ -22851,7 +22863,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ143" t="s">
         <v>104</v>
@@ -22867,7 +22879,7 @@
         <v>0</v>
       </c>
       <c r="AV143" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW143" t="s">
         <v>62</v>
@@ -22917,7 +22929,7 @@
         <v>-12.2375955423258</v>
       </c>
       <c r="N144" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O144" t="n">
         <v>0.175358121924559</v>
@@ -23001,7 +23013,7 @@
         <v>1</v>
       </c>
       <c r="AP144" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ144" t="s">
         <v>104</v>
@@ -23017,7 +23029,7 @@
         <v>0</v>
       </c>
       <c r="AV144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW144" t="s">
         <v>62</v>
@@ -23067,7 +23079,7 @@
         <v>19.4083938732682</v>
       </c>
       <c r="N145" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O145" t="n">
         <v>0.177071829454133</v>
@@ -23151,7 +23163,7 @@
         <v>1</v>
       </c>
       <c r="AP145" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ145" t="s">
         <v>104</v>
@@ -23167,7 +23179,7 @@
         <v>0</v>
       </c>
       <c r="AV145" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW145" t="s">
         <v>62</v>
@@ -23217,7 +23229,7 @@
         <v>-11.5605651334122</v>
       </c>
       <c r="N146" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O146" t="n">
         <v>0.17449596664002</v>
@@ -23301,7 +23313,7 @@
         <v>0</v>
       </c>
       <c r="AP146" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ146" t="s">
         <v>104</v>
@@ -23317,7 +23329,7 @@
         <v>0</v>
       </c>
       <c r="AV146" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW146" t="s">
         <v>62</v>
@@ -23367,7 +23379,7 @@
         <v>-2.50461483222459</v>
       </c>
       <c r="N147" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O147" t="n">
         <v>0.198370403947282</v>
@@ -23451,7 +23463,7 @@
         <v>1</v>
       </c>
       <c r="AP147" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ147" t="s">
         <v>104</v>
@@ -23467,7 +23479,7 @@
         <v>0</v>
       </c>
       <c r="AV147" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW147" t="s">
         <v>62</v>
@@ -23517,7 +23529,7 @@
         <v>13.8641201415336</v>
       </c>
       <c r="N148" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O148" t="n">
         <v>0.17061038201066</v>
@@ -23601,7 +23613,7 @@
         <v>1</v>
       </c>
       <c r="AP148" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ148" t="s">
         <v>104</v>
@@ -23617,7 +23629,7 @@
         <v>0</v>
       </c>
       <c r="AV148" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW148" t="s">
         <v>62</v>
@@ -23667,7 +23679,7 @@
         <v>16.2597416216604</v>
       </c>
       <c r="N149" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O149" t="n">
         <v>0.30457793088011</v>
@@ -23751,7 +23763,7 @@
         <v>1</v>
       </c>
       <c r="AP149" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ149" t="s">
         <v>58</v>
@@ -23767,7 +23779,7 @@
         <v>0</v>
       </c>
       <c r="AV149" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW149" t="s">
         <v>62</v>
@@ -23817,7 +23829,7 @@
         <v>-5.85622797571164</v>
       </c>
       <c r="N150" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O150" t="n">
         <v>0.257129698085039</v>
@@ -23967,7 +23979,7 @@
         <v>-1.63667892374401</v>
       </c>
       <c r="N151" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O151" t="n">
         <v>0.284518227584785</v>
@@ -24051,7 +24063,7 @@
         <v>1</v>
       </c>
       <c r="AP151" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ151" t="s">
         <v>58</v>
@@ -24067,7 +24079,7 @@
         <v>0</v>
       </c>
       <c r="AV151" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW151" t="s">
         <v>62</v>
@@ -24117,7 +24129,7 @@
         <v>-8.75483055511078</v>
       </c>
       <c r="N152" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O152" t="n">
         <v>0.291751215776892</v>
@@ -24267,7 +24279,7 @@
         <v>-34.6990541523762</v>
       </c>
       <c r="N153" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O153" t="n">
         <v>0.28776631705588</v>
@@ -24417,7 +24429,7 @@
         <v>3.21020181577025</v>
       </c>
       <c r="N154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O154" t="n">
         <v>0.26693270766267</v>
@@ -24501,7 +24513,7 @@
         <v>1</v>
       </c>
       <c r="AP154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ154" t="s">
         <v>58</v>
@@ -24517,7 +24529,7 @@
         <v>0</v>
       </c>
       <c r="AV154" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW154" t="s">
         <v>62</v>
@@ -24567,7 +24579,7 @@
         <v>14.3100761711571</v>
       </c>
       <c r="N155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O155" t="n">
         <v>0.313128084065022</v>
@@ -24641,7 +24653,7 @@
         <v>1</v>
       </c>
       <c r="AP155" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ155" t="s">
         <v>58</v>
@@ -24657,7 +24669,7 @@
         <v>0</v>
       </c>
       <c r="AV155" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW155" t="s">
         <v>62</v>
@@ -24703,7 +24715,7 @@
       <c r="L156"/>
       <c r="M156"/>
       <c r="N156" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O156" t="n">
         <v>0.313128084065022</v>
@@ -24783,7 +24795,7 @@
         <v>0</v>
       </c>
       <c r="AV156" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW156" t="s">
         <v>62</v>
@@ -24833,7 +24845,7 @@
         <v>-21.3010685226165</v>
       </c>
       <c r="N157" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O157" t="n">
         <v>0.239715804496989</v>
@@ -24917,7 +24929,7 @@
         <v>1</v>
       </c>
       <c r="AP157" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ157" t="s">
         <v>58</v>
@@ -24933,7 +24945,7 @@
         <v>0</v>
       </c>
       <c r="AV157" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW157" t="s">
         <v>62</v>
@@ -24983,7 +24995,7 @@
         <v>7.38572751315631</v>
       </c>
       <c r="N158" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O158" t="n">
         <v>0.252588422577364</v>
@@ -25067,7 +25079,7 @@
         <v>1</v>
       </c>
       <c r="AP158" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ158" t="s">
         <v>58</v>
@@ -25083,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AV158" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW158" t="s">
         <v>62</v>
@@ -25133,7 +25145,7 @@
         <v>-12.9417309414642</v>
       </c>
       <c r="N159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O159" t="n">
         <v>0.254452734297448</v>
@@ -25217,7 +25229,7 @@
         <v>1</v>
       </c>
       <c r="AP159" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ159" t="s">
         <v>58</v>
@@ -25233,7 +25245,7 @@
         <v>0</v>
       </c>
       <c r="AV159" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW159" t="s">
         <v>62</v>
@@ -25283,7 +25295,7 @@
         <v>16.6065060006806</v>
       </c>
       <c r="N160" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O160" t="n">
         <v>0.259797108326417</v>
@@ -25367,7 +25379,7 @@
         <v>1</v>
       </c>
       <c r="AP160" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ160" t="s">
         <v>58</v>
@@ -25383,7 +25395,7 @@
         <v>0</v>
       </c>
       <c r="AV160" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW160" t="s">
         <v>62</v>
@@ -25433,7 +25445,7 @@
         <v>25.5348613485264</v>
       </c>
       <c r="N161" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O161" t="n">
         <v>0.223337608990553</v>
@@ -25517,7 +25529,7 @@
         <v>0</v>
       </c>
       <c r="AP161" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ161" t="s">
         <v>58</v>
@@ -25533,7 +25545,7 @@
         <v>0</v>
       </c>
       <c r="AV161" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW161" t="s">
         <v>62</v>
@@ -25583,7 +25595,7 @@
         <v>13.4692207072387</v>
       </c>
       <c r="N162" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O162" t="n">
         <v>0.228505881487332</v>
@@ -25667,7 +25679,7 @@
         <v>1</v>
       </c>
       <c r="AP162" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ162" t="s">
         <v>58</v>
@@ -25683,7 +25695,7 @@
         <v>0</v>
       </c>
       <c r="AV162" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW162" t="s">
         <v>62</v>
@@ -25729,7 +25741,7 @@
       <c r="L163"/>
       <c r="M163"/>
       <c r="N163" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O163" t="n">
         <v>0.310056061223634</v>
@@ -25809,7 +25821,7 @@
         <v>0</v>
       </c>
       <c r="AV163" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW163" t="s">
         <v>62</v>
@@ -25859,7 +25871,7 @@
         <v>24.0507826499617</v>
       </c>
       <c r="N164" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O164" t="n">
         <v>0.242131381271137</v>
@@ -25943,7 +25955,7 @@
         <v>1</v>
       </c>
       <c r="AP164" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ164" t="s">
         <v>58</v>
@@ -25959,7 +25971,7 @@
         <v>0</v>
       </c>
       <c r="AV164" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW164" t="s">
         <v>62</v>
@@ -26009,7 +26021,7 @@
         <v>-0.79659990717369</v>
       </c>
       <c r="N165" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O165" t="n">
         <v>0.201307291652032</v>
@@ -26093,7 +26105,7 @@
         <v>0</v>
       </c>
       <c r="AP165" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ165" t="s">
         <v>118</v>
@@ -26109,7 +26121,7 @@
         <v>0</v>
       </c>
       <c r="AV165" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW165" t="s">
         <v>62</v>
@@ -26159,7 +26171,7 @@
         <v>53.5356357203026</v>
       </c>
       <c r="N166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O166" t="n">
         <v>0.205895415185436</v>
@@ -26243,7 +26255,7 @@
         <v>0</v>
       </c>
       <c r="AP166" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ166" t="s">
         <v>118</v>
@@ -26259,7 +26271,7 @@
         <v>0</v>
       </c>
       <c r="AV166" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW166" t="s">
         <v>62</v>
@@ -26309,7 +26321,7 @@
         <v>-29.7110215719997</v>
       </c>
       <c r="N167" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O167" t="n">
         <v>0.192181843726898</v>
@@ -26609,7 +26621,7 @@
         <v>-26.4048178897106</v>
       </c>
       <c r="N169" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O169" t="n">
         <v>0.182576773709641</v>
@@ -26693,7 +26705,7 @@
         <v>1</v>
       </c>
       <c r="AP169" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ169" t="s">
         <v>118</v>
@@ -26709,7 +26721,7 @@
         <v>0</v>
       </c>
       <c r="AV169" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW169" t="s">
         <v>62</v>
@@ -26759,7 +26771,7 @@
         <v>-11.9713050939816</v>
       </c>
       <c r="N170" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O170" t="n">
         <v>0.193676332163056</v>
@@ -26843,7 +26855,7 @@
         <v>0</v>
       </c>
       <c r="AP170" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ170" t="s">
         <v>118</v>
@@ -26859,7 +26871,7 @@
         <v>0</v>
       </c>
       <c r="AV170" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW170" t="s">
         <v>62</v>
@@ -26909,7 +26921,7 @@
         <v>-4.08316695070835</v>
       </c>
       <c r="N171" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O171" t="n">
         <v>0.187912716102483</v>
@@ -26993,7 +27005,7 @@
         <v>1</v>
       </c>
       <c r="AP171" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ171" t="s">
         <v>118</v>
@@ -27009,7 +27021,7 @@
         <v>0</v>
       </c>
       <c r="AV171" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW171" t="s">
         <v>62</v>
@@ -27205,7 +27217,7 @@
       <c r="L173"/>
       <c r="M173"/>
       <c r="N173" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O173" t="n">
         <v>0.228119022973593</v>
@@ -27285,7 +27297,7 @@
         <v>0</v>
       </c>
       <c r="AV173" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW173" t="s">
         <v>62</v>
@@ -27331,7 +27343,7 @@
       <c r="L174"/>
       <c r="M174"/>
       <c r="N174" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O174" t="n">
         <v>0.228119022973593</v>
@@ -27411,7 +27423,7 @@
         <v>0</v>
       </c>
       <c r="AV174" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW174" t="s">
         <v>62</v>
@@ -27457,7 +27469,7 @@
       <c r="L175"/>
       <c r="M175"/>
       <c r="N175" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O175" t="n">
         <v>0.228119022973593</v>
@@ -27537,7 +27549,7 @@
         <v>0</v>
       </c>
       <c r="AV175" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW175" t="s">
         <v>62</v>
@@ -27587,7 +27599,7 @@
         <v>11.9570641463916</v>
       </c>
       <c r="N176" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O176" t="n">
         <v>0.1776454149824</v>
@@ -27671,7 +27683,7 @@
         <v>0</v>
       </c>
       <c r="AP176" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ176" t="s">
         <v>58</v>
@@ -27687,7 +27699,7 @@
         <v>0</v>
       </c>
       <c r="AV176" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW176" t="s">
         <v>62</v>
@@ -27737,7 +27749,7 @@
         <v>99.2970044910463</v>
       </c>
       <c r="N177" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O177" t="n">
         <v>0.228119022973593</v>
@@ -27877,7 +27889,7 @@
         <v>104.904011123419</v>
       </c>
       <c r="N178" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O178" t="n">
         <v>0.228119022973593</v>
@@ -28167,7 +28179,7 @@
         <v>51.151923142816</v>
       </c>
       <c r="N180" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O180" t="n">
         <v>0.189594801625709</v>
@@ -28317,7 +28329,7 @@
         <v>57.1862276343325</v>
       </c>
       <c r="N181" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O181" t="n">
         <v>0.179051864828733</v>
@@ -28401,7 +28413,7 @@
         <v>0</v>
       </c>
       <c r="AP181" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ181" t="s">
         <v>58</v>
@@ -28417,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="AV181" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW181" t="s">
         <v>62</v>
@@ -28463,7 +28475,7 @@
       <c r="L182"/>
       <c r="M182"/>
       <c r="N182" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O182" t="n">
         <v>0.228530910158683</v>
@@ -28543,7 +28555,7 @@
         <v>0</v>
       </c>
       <c r="AV182" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW182" t="s">
         <v>62</v>
@@ -28589,7 +28601,7 @@
       <c r="L183"/>
       <c r="M183"/>
       <c r="N183" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O183" t="n">
         <v>0.228530910158683</v>
@@ -28669,7 +28681,7 @@
         <v>0</v>
       </c>
       <c r="AV183" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW183" t="s">
         <v>62</v>
@@ -28715,7 +28727,7 @@
       <c r="L184"/>
       <c r="M184"/>
       <c r="N184" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O184" t="n">
         <v>0.228530910158683</v>
@@ -28795,7 +28807,7 @@
         <v>0</v>
       </c>
       <c r="AV184" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW184" t="s">
         <v>62</v>
@@ -28841,7 +28853,7 @@
       <c r="L185"/>
       <c r="M185"/>
       <c r="N185" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O185" t="n">
         <v>0.228530910158683</v>
@@ -28921,7 +28933,7 @@
         <v>0</v>
       </c>
       <c r="AV185" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW185" t="s">
         <v>62</v>
@@ -28971,7 +28983,7 @@
         <v>-0.108179276465892</v>
       </c>
       <c r="N186" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O186" t="n">
         <v>0.171163842186505</v>
@@ -29055,7 +29067,7 @@
         <v>0</v>
       </c>
       <c r="AP186" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ186" t="s">
         <v>58</v>
@@ -29071,7 +29083,7 @@
         <v>0</v>
       </c>
       <c r="AV186" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW186" t="s">
         <v>62</v>
@@ -29121,7 +29133,7 @@
         <v>106.538767500139</v>
       </c>
       <c r="N187" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O187" t="n">
         <v>0.195026230641509</v>
@@ -29271,7 +29283,7 @@
         <v>140.144837319229</v>
       </c>
       <c r="N188" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O188" t="n">
         <v>0.175074406565663</v>
@@ -29355,7 +29367,7 @@
         <v>0</v>
       </c>
       <c r="AP188" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ188" t="s">
         <v>58</v>
@@ -29371,7 +29383,7 @@
         <v>0</v>
       </c>
       <c r="AV188" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW188" t="s">
         <v>62</v>
@@ -29417,7 +29429,7 @@
       <c r="L189"/>
       <c r="M189"/>
       <c r="N189" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O189" t="n">
         <v>0.218146052610956</v>
@@ -29497,7 +29509,7 @@
         <v>0</v>
       </c>
       <c r="AV189" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW189" t="s">
         <v>62</v>
@@ -29547,7 +29559,7 @@
         <v>16.5551672127385</v>
       </c>
       <c r="N190" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O190" t="n">
         <v>0.182833556948451</v>
@@ -29631,7 +29643,7 @@
         <v>1</v>
       </c>
       <c r="AP190" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ190" t="s">
         <v>58</v>
@@ -29647,7 +29659,7 @@
         <v>0</v>
       </c>
       <c r="AV190" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW190" t="s">
         <v>62</v>
@@ -29697,7 +29709,7 @@
         <v>111.89276245294</v>
       </c>
       <c r="N191" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O191" t="n">
         <v>0.218146052610956</v>
@@ -29833,7 +29845,7 @@
         <v>100.633908052104</v>
       </c>
       <c r="N192" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O192" t="n">
         <v>0.18311148238604</v>
@@ -29917,7 +29929,7 @@
         <v>1</v>
       </c>
       <c r="AP192" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ192" t="s">
         <v>58</v>
@@ -29933,7 +29945,7 @@
         <v>0</v>
       </c>
       <c r="AV192" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW192" t="s">
         <v>62</v>
@@ -29983,7 +29995,7 @@
         <v>120.543483320806</v>
       </c>
       <c r="N193" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O193" t="n">
         <v>0.184813014417126</v>
@@ -30067,7 +30079,7 @@
         <v>1</v>
       </c>
       <c r="AP193" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ193" t="s">
         <v>58</v>
@@ -30083,7 +30095,7 @@
         <v>0</v>
       </c>
       <c r="AV193" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW193" t="s">
         <v>62</v>
@@ -30133,7 +30145,7 @@
         <v>89.2318163387069</v>
       </c>
       <c r="N194" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O194" t="n">
         <v>0.181306043797117</v>
@@ -30217,7 +30229,7 @@
         <v>0</v>
       </c>
       <c r="AP194" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ194" t="s">
         <v>58</v>
@@ -30233,7 +30245,7 @@
         <v>0</v>
       </c>
       <c r="AV194" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW194" t="s">
         <v>62</v>
@@ -30283,7 +30295,7 @@
         <v>134.673899089619</v>
       </c>
       <c r="N195" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O195" t="n">
         <v>0.18311148238604</v>
@@ -30367,7 +30379,7 @@
         <v>1</v>
       </c>
       <c r="AP195" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ195" t="s">
         <v>58</v>
@@ -30383,7 +30395,7 @@
         <v>0</v>
       </c>
       <c r="AV195" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW195" t="s">
         <v>62</v>
@@ -30723,7 +30735,7 @@
         <v>41.796493664536</v>
       </c>
       <c r="N198" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O198" t="n">
         <v>0.231660713119291</v>
@@ -30797,7 +30809,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ198" t="s">
         <v>118</v>
@@ -30813,7 +30825,7 @@
         <v>0</v>
       </c>
       <c r="AV198" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW198" t="s">
         <v>62</v>
@@ -30863,7 +30875,7 @@
         <v>42.368907156743</v>
       </c>
       <c r="N199" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O199" t="n">
         <v>0.231660713119291</v>
@@ -30937,7 +30949,7 @@
         <v>1</v>
       </c>
       <c r="AP199" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ199" t="s">
         <v>118</v>
@@ -30953,7 +30965,7 @@
         <v>0</v>
       </c>
       <c r="AV199" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW199" t="s">
         <v>62</v>
@@ -31003,7 +31015,7 @@
         <v>66.7191002605687</v>
       </c>
       <c r="N200" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O200" t="n">
         <v>0.231660713119291</v>
@@ -31077,7 +31089,7 @@
         <v>0</v>
       </c>
       <c r="AP200" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ200" t="s">
         <v>118</v>
@@ -31093,7 +31105,7 @@
         <v>0</v>
       </c>
       <c r="AV200" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW200" t="s">
         <v>62</v>
@@ -31431,7 +31443,7 @@
         <v>-29.9261670067844</v>
       </c>
       <c r="N203" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O203" t="n">
         <v>0.179782421466735</v>
@@ -31515,7 +31527,7 @@
         <v>1</v>
       </c>
       <c r="AP203" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ203" t="s">
         <v>118</v>
@@ -31531,7 +31543,7 @@
         <v>0</v>
       </c>
       <c r="AV203" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW203" t="s">
         <v>62</v>
@@ -31581,7 +31593,7 @@
         <v>-50.6538967662661</v>
       </c>
       <c r="N204" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O204" t="n">
         <v>0.177472105833633</v>
@@ -31665,7 +31677,7 @@
         <v>0</v>
       </c>
       <c r="AP204" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ204" t="s">
         <v>118</v>
@@ -31681,7 +31693,7 @@
         <v>0</v>
       </c>
       <c r="AV204" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW204" t="s">
         <v>62</v>
@@ -31731,7 +31743,7 @@
         <v>-12.087655983596</v>
       </c>
       <c r="N205" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O205" t="n">
         <v>0.188106643863481</v>
@@ -31815,7 +31827,7 @@
         <v>0</v>
       </c>
       <c r="AP205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ205" t="s">
         <v>104</v>
@@ -31831,7 +31843,7 @@
         <v>0</v>
       </c>
       <c r="AV205" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW205" t="s">
         <v>62</v>
@@ -31881,7 +31893,7 @@
         <v>45.4427118723385</v>
       </c>
       <c r="N206" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O206" t="n">
         <v>0.229487664812408</v>
@@ -31955,7 +31967,7 @@
         <v>1</v>
       </c>
       <c r="AP206" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ206" t="s">
         <v>104</v>
@@ -31971,7 +31983,7 @@
         <v>0</v>
       </c>
       <c r="AV206" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW206" t="s">
         <v>62</v>
@@ -32021,7 +32033,7 @@
         <v>-23.1690934640345</v>
       </c>
       <c r="N207" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O207" t="n">
         <v>0.168848633166867</v>
@@ -32105,7 +32117,7 @@
         <v>1</v>
       </c>
       <c r="AP207" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ207" t="s">
         <v>104</v>
@@ -32121,7 +32133,7 @@
         <v>0</v>
       </c>
       <c r="AV207" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW207" t="s">
         <v>62</v>
@@ -32171,7 +32183,7 @@
         <v>-34.6518858238782</v>
       </c>
       <c r="N208" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O208" t="n">
         <v>0.175772330291871</v>
@@ -32255,7 +32267,7 @@
         <v>1</v>
       </c>
       <c r="AP208" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ208" t="s">
         <v>104</v>
@@ -32271,7 +32283,7 @@
         <v>0</v>
       </c>
       <c r="AV208" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW208" t="s">
         <v>62</v>
@@ -32321,7 +32333,7 @@
         <v>48.6981700444202</v>
       </c>
       <c r="N209" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O209" t="n">
         <v>0.189919636343159</v>
@@ -32405,7 +32417,7 @@
         <v>1</v>
       </c>
       <c r="AP209" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ209" t="s">
         <v>104</v>
@@ -32421,7 +32433,7 @@
         <v>0</v>
       </c>
       <c r="AV209" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW209" t="s">
         <v>62</v>
@@ -32471,7 +32483,7 @@
         <v>30.6393943888547</v>
       </c>
       <c r="N210" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O210" t="n">
         <v>0.229487664812408</v>
@@ -32545,7 +32557,7 @@
         <v>1</v>
       </c>
       <c r="AP210" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ210" t="s">
         <v>104</v>
@@ -32561,7 +32573,7 @@
         <v>0</v>
       </c>
       <c r="AV210" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW210" t="s">
         <v>62</v>
@@ -32611,7 +32623,7 @@
         <v>-14.1240751156362</v>
       </c>
       <c r="N211" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O211" t="n">
         <v>0.188332921371067</v>
@@ -32695,7 +32707,7 @@
         <v>1</v>
       </c>
       <c r="AP211" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ211" t="s">
         <v>104</v>
@@ -32711,7 +32723,7 @@
         <v>0</v>
       </c>
       <c r="AV211" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW211" t="s">
         <v>62</v>
@@ -32761,7 +32773,7 @@
         <v>-42.5397450072464</v>
       </c>
       <c r="N212" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O212" t="n">
         <v>0.175807363228346</v>
@@ -32845,7 +32857,7 @@
         <v>1</v>
       </c>
       <c r="AP212" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ212" t="s">
         <v>104</v>
@@ -32861,7 +32873,7 @@
         <v>0</v>
       </c>
       <c r="AV212" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW212" t="s">
         <v>62</v>
@@ -32911,7 +32923,7 @@
         <v>-10.0099906717982</v>
       </c>
       <c r="N213" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O213" t="n">
         <v>0.173797637404939</v>
@@ -33057,7 +33069,7 @@
       <c r="L214"/>
       <c r="M214"/>
       <c r="N214" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O214" t="n">
         <v>0.221824733842179</v>
@@ -33137,7 +33149,7 @@
         <v>0</v>
       </c>
       <c r="AV214" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW214" t="s">
         <v>62</v>
@@ -33183,7 +33195,7 @@
       <c r="L215"/>
       <c r="M215"/>
       <c r="N215" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O215" t="n">
         <v>0.221824733842179</v>
@@ -33263,7 +33275,7 @@
         <v>0</v>
       </c>
       <c r="AV215" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW215" t="s">
         <v>62</v>
@@ -33313,7 +33325,7 @@
         <v>79.9019094966243</v>
       </c>
       <c r="N216" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O216" t="n">
         <v>0.222650458997365</v>
@@ -33387,7 +33399,7 @@
         <v>0</v>
       </c>
       <c r="AP216" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ216" t="s">
         <v>58</v>
@@ -33403,7 +33415,7 @@
         <v>0</v>
       </c>
       <c r="AV216" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW216" t="s">
         <v>62</v>
@@ -33453,7 +33465,7 @@
         <v>34.3664345815073</v>
       </c>
       <c r="N217" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O217" t="n">
         <v>0.173797637404939</v>
@@ -33537,7 +33549,7 @@
         <v>1</v>
       </c>
       <c r="AP217" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ217" t="s">
         <v>58</v>
@@ -33553,7 +33565,7 @@
         <v>0</v>
       </c>
       <c r="AV217" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW217" t="s">
         <v>62</v>
@@ -33603,7 +33615,7 @@
         <v>11.6207539296941</v>
       </c>
       <c r="N218" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O218" t="n">
         <v>0.185916749911762</v>
@@ -33687,7 +33699,7 @@
         <v>0</v>
       </c>
       <c r="AP218" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ218" t="s">
         <v>58</v>
@@ -33703,7 +33715,7 @@
         <v>0</v>
       </c>
       <c r="AV218" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW218" t="s">
         <v>62</v>
@@ -33753,7 +33765,7 @@
         <v>-22.4615346297508</v>
       </c>
       <c r="N219" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O219" t="n">
         <v>0.185916749911762</v>
@@ -33837,7 +33849,7 @@
         <v>1</v>
       </c>
       <c r="AP219" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ219" t="s">
         <v>58</v>
@@ -33853,7 +33865,7 @@
         <v>0</v>
       </c>
       <c r="AV219" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW219" t="s">
         <v>62</v>
@@ -33903,7 +33915,7 @@
         <v>41.0297015117179</v>
       </c>
       <c r="N220" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O220" t="n">
         <v>0.175149162368464</v>
@@ -33987,7 +33999,7 @@
         <v>1</v>
       </c>
       <c r="AP220" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ220" t="s">
         <v>58</v>
@@ -34003,7 +34015,7 @@
         <v>0</v>
       </c>
       <c r="AV220" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW220" t="s">
         <v>62</v>
@@ -34053,7 +34065,7 @@
         <v>-3.87777324181754</v>
       </c>
       <c r="N221" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O221" t="n">
         <v>0.176974526184448</v>
@@ -34203,7 +34215,7 @@
         <v>-5.2889391259733</v>
       </c>
       <c r="N222" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O222" t="n">
         <v>0.179641077724989</v>
@@ -34349,7 +34361,7 @@
       <c r="L223"/>
       <c r="M223"/>
       <c r="N223" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O223" t="n">
         <v>0.224922411888871</v>
@@ -34429,7 +34441,7 @@
         <v>0</v>
       </c>
       <c r="AV223" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW223" t="s">
         <v>62</v>
@@ -34479,7 +34491,7 @@
         <v>13.4327813779897</v>
       </c>
       <c r="N224" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O224" t="n">
         <v>0.17770934169368</v>
@@ -34563,7 +34575,7 @@
         <v>1</v>
       </c>
       <c r="AP224" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ224" t="s">
         <v>58</v>
@@ -34579,7 +34591,7 @@
         <v>0</v>
       </c>
       <c r="AV224" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW224" t="s">
         <v>62</v>
@@ -34629,7 +34641,7 @@
         <v>5.84737057241671</v>
       </c>
       <c r="N225" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O225" t="n">
         <v>0.166645876338837</v>
@@ -34713,7 +34725,7 @@
         <v>0</v>
       </c>
       <c r="AP225" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ225" t="s">
         <v>58</v>
@@ -34729,7 +34741,7 @@
         <v>0</v>
       </c>
       <c r="AV225" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW225" t="s">
         <v>62</v>
@@ -34779,7 +34791,7 @@
         <v>98.8766846639965</v>
       </c>
       <c r="N226" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O226" t="n">
         <v>0.224922411888871</v>
@@ -34915,7 +34927,7 @@
         <v>97.439052460466</v>
       </c>
       <c r="N227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O227" t="n">
         <v>0.188799548604557</v>
@@ -34999,7 +35011,7 @@
         <v>1</v>
       </c>
       <c r="AP227" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ227" t="s">
         <v>58</v>
@@ -35015,7 +35027,7 @@
         <v>0</v>
       </c>
       <c r="AV227" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW227" t="s">
         <v>62</v>
@@ -35065,7 +35077,7 @@
         <v>50.9002577035774</v>
       </c>
       <c r="N228" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O228" t="n">
         <v>0.172309985364427</v>
@@ -35149,7 +35161,7 @@
         <v>1</v>
       </c>
       <c r="AP228" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ228" t="s">
         <v>58</v>
@@ -35165,7 +35177,7 @@
         <v>0</v>
       </c>
       <c r="AV228" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW228" t="s">
         <v>62</v>
@@ -35211,7 +35223,7 @@
       <c r="L229"/>
       <c r="M229"/>
       <c r="N229" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O229" t="n">
         <v>0.217329926073665</v>
@@ -35291,7 +35303,7 @@
         <v>0</v>
       </c>
       <c r="AV229" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW229" t="s">
         <v>62</v>
@@ -35341,7 +35353,7 @@
         <v>32.909961327076</v>
       </c>
       <c r="N230" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O230" t="n">
         <v>0.178506051945352</v>
@@ -35425,7 +35437,7 @@
         <v>0</v>
       </c>
       <c r="AP230" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ230" t="s">
         <v>58</v>
@@ -35441,7 +35453,7 @@
         <v>0</v>
       </c>
       <c r="AV230" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW230" t="s">
         <v>62</v>
@@ -35491,7 +35503,7 @@
         <v>-41.1617590913512</v>
       </c>
       <c r="N231" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O231" t="n">
         <v>0.1702759968862</v>
@@ -35641,7 +35653,7 @@
         <v>-40.8144876032567</v>
       </c>
       <c r="N232" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O232" t="n">
         <v>0.161765760744047</v>
@@ -35725,7 +35737,7 @@
         <v>1</v>
       </c>
       <c r="AP232" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ232" t="s">
         <v>58</v>
@@ -35741,7 +35753,7 @@
         <v>0</v>
       </c>
       <c r="AV232" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW232" t="s">
         <v>62</v>
@@ -35791,7 +35803,7 @@
         <v>93.0694200919457</v>
       </c>
       <c r="N233" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O233" t="n">
         <v>0.171600136062756</v>
@@ -35875,7 +35887,7 @@
         <v>0</v>
       </c>
       <c r="AP233" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ233" t="s">
         <v>58</v>
@@ -35891,7 +35903,7 @@
         <v>0</v>
       </c>
       <c r="AV233" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW233" t="s">
         <v>62</v>
@@ -35941,7 +35953,7 @@
         <v>59.3804054293601</v>
       </c>
       <c r="N234" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O234" t="n">
         <v>0.217329926073665</v>
@@ -36015,7 +36027,7 @@
         <v>0</v>
       </c>
       <c r="AP234" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ234" t="s">
         <v>58</v>
@@ -36031,7 +36043,7 @@
         <v>0</v>
       </c>
       <c r="AV234" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW234" t="s">
         <v>62</v>
@@ -36081,7 +36093,7 @@
         <v>82.6150305019057</v>
       </c>
       <c r="N235" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O235" t="n">
         <v>0.167469601872422</v>
@@ -36165,7 +36177,7 @@
         <v>1</v>
       </c>
       <c r="AP235" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ235" t="s">
         <v>58</v>
@@ -36181,7 +36193,7 @@
         <v>0</v>
       </c>
       <c r="AV235" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW235" t="s">
         <v>62</v>
@@ -36231,7 +36243,7 @@
         <v>85.591549235919</v>
       </c>
       <c r="N236" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O236" t="n">
         <v>0.165102488432761</v>
@@ -36315,7 +36327,7 @@
         <v>1</v>
       </c>
       <c r="AP236" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ236" t="s">
         <v>58</v>
@@ -36331,7 +36343,7 @@
         <v>0</v>
       </c>
       <c r="AV236" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW236" t="s">
         <v>62</v>
@@ -36531,7 +36543,7 @@
         <v>22.0735393226745</v>
       </c>
       <c r="N238" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O238" t="n">
         <v>0.188929697311367</v>
@@ -36615,7 +36627,7 @@
         <v>1</v>
       </c>
       <c r="AP238" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ238" t="s">
         <v>118</v>
@@ -36631,7 +36643,7 @@
         <v>0</v>
       </c>
       <c r="AV238" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW238" t="s">
         <v>62</v>
@@ -36681,7 +36693,7 @@
         <v>51.5032823402619</v>
       </c>
       <c r="N239" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O239" t="n">
         <v>0.192538560729259</v>
@@ -36765,7 +36777,7 @@
         <v>1</v>
       </c>
       <c r="AP239" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ239" t="s">
         <v>118</v>
@@ -36781,7 +36793,7 @@
         <v>0</v>
       </c>
       <c r="AV239" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW239" t="s">
         <v>62</v>
@@ -36831,7 +36843,7 @@
         <v>-19.8262126426897</v>
       </c>
       <c r="N240" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O240" t="n">
         <v>0.180614605821977</v>
@@ -36915,7 +36927,7 @@
         <v>1</v>
       </c>
       <c r="AP240" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ240" t="s">
         <v>118</v>
@@ -36931,7 +36943,7 @@
         <v>0</v>
       </c>
       <c r="AV240" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW240" t="s">
         <v>62</v>
@@ -36981,7 +36993,7 @@
         <v>-18.9159183364079</v>
       </c>
       <c r="N241" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O241" t="n">
         <v>0.196094153282159</v>
@@ -37131,7 +37143,7 @@
         <v>106.032706946494</v>
       </c>
       <c r="N242" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O242" t="n">
         <v>0.182915662327605</v>
@@ -37215,7 +37227,7 @@
         <v>1</v>
       </c>
       <c r="AP242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ242" t="s">
         <v>118</v>
@@ -37231,7 +37243,7 @@
         <v>0</v>
       </c>
       <c r="AV242" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW242" t="s">
         <v>62</v>
@@ -37281,7 +37293,7 @@
         <v>16.1476303522209</v>
       </c>
       <c r="N243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O243" t="n">
         <v>0.182915662327605</v>
@@ -37365,7 +37377,7 @@
         <v>1</v>
       </c>
       <c r="AP243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ243" t="s">
         <v>118</v>
@@ -37381,7 +37393,7 @@
         <v>0</v>
       </c>
       <c r="AV243" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW243" t="s">
         <v>62</v>
@@ -37431,7 +37443,7 @@
         <v>-28.0095912074529</v>
       </c>
       <c r="N244" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O244" t="n">
         <v>0.192538560729259</v>
@@ -37581,7 +37593,7 @@
         <v>-4.75473023930704</v>
       </c>
       <c r="N245" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O245" t="n">
         <v>0.180384377277171</v>
@@ -37665,7 +37677,7 @@
         <v>1</v>
       </c>
       <c r="AP245" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ245" t="s">
         <v>58</v>
@@ -37681,7 +37693,7 @@
         <v>0</v>
       </c>
       <c r="AV245" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW245" t="s">
         <v>62</v>
@@ -37727,7 +37739,7 @@
       <c r="L246"/>
       <c r="M246"/>
       <c r="N246" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O246" t="n">
         <v>0.223694023321694</v>
@@ -37807,7 +37819,7 @@
         <v>0</v>
       </c>
       <c r="AV246" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW246" t="s">
         <v>62</v>
@@ -37857,7 +37869,7 @@
         <v>-7.28274205827204</v>
       </c>
       <c r="N247" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O247" t="n">
         <v>0.181904125338601</v>
@@ -38003,7 +38015,7 @@
       <c r="L248"/>
       <c r="M248"/>
       <c r="N248" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O248" t="n">
         <v>0.223694023321694</v>
@@ -38083,7 +38095,7 @@
         <v>0</v>
       </c>
       <c r="AV248" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AW248" t="s">
         <v>62</v>
@@ -38133,7 +38145,7 @@
         <v>81.2624080076174</v>
       </c>
       <c r="N249" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O249" t="n">
         <v>0.223694023321694</v>
@@ -38207,7 +38219,7 @@
         <v>1</v>
       </c>
       <c r="AP249" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ249" t="s">
         <v>58</v>
@@ -38223,7 +38235,7 @@
         <v>0</v>
       </c>
       <c r="AV249" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW249" t="s">
         <v>62</v>
@@ -38423,7 +38435,7 @@
         <v>95.1321540352232</v>
       </c>
       <c r="N251" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O251" t="n">
         <v>0.189350400205156</v>
@@ -38507,7 +38519,7 @@
         <v>0</v>
       </c>
       <c r="AP251" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ251" t="s">
         <v>58</v>
@@ -38523,7 +38535,7 @@
         <v>0</v>
       </c>
       <c r="AV251" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW251" t="s">
         <v>62</v>
@@ -38573,7 +38585,7 @@
         <v>-13.9417908767858</v>
       </c>
       <c r="N252" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O252" t="n">
         <v>0.176625122604684</v>
@@ -38657,7 +38669,7 @@
         <v>1</v>
       </c>
       <c r="AP252" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ252" t="s">
         <v>58</v>
@@ -38673,7 +38685,7 @@
         <v>0</v>
       </c>
       <c r="AV252" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW252" t="s">
         <v>62</v>
@@ -38723,7 +38735,7 @@
         <v>-6.00692643050981</v>
       </c>
       <c r="N253" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O253" t="n">
         <v>0.183118618005032</v>
@@ -38807,7 +38819,7 @@
         <v>1</v>
       </c>
       <c r="AP253" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ253" t="s">
         <v>118</v>
@@ -38823,7 +38835,7 @@
         <v>0</v>
       </c>
       <c r="AV253" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW253" t="s">
         <v>62</v>
@@ -39023,7 +39035,7 @@
         <v>-11.1149279652651</v>
       </c>
       <c r="N255" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O255" t="n">
         <v>0.173165129648517</v>
@@ -39107,7 +39119,7 @@
         <v>1</v>
       </c>
       <c r="AP255" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ255" t="s">
         <v>118</v>
@@ -39123,7 +39135,7 @@
         <v>0</v>
       </c>
       <c r="AV255" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW255" t="s">
         <v>62</v>
@@ -39173,7 +39185,7 @@
         <v>83.3100999022354</v>
       </c>
       <c r="N256" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O256" t="n">
         <v>0.233721466569025</v>
@@ -39247,7 +39259,7 @@
         <v>1</v>
       </c>
       <c r="AP256" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ256" t="s">
         <v>118</v>
@@ -39263,7 +39275,7 @@
         <v>0</v>
       </c>
       <c r="AV256" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW256" t="s">
         <v>62</v>
@@ -39313,7 +39325,7 @@
         <v>67.8575085934477</v>
       </c>
       <c r="N257" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O257" t="n">
         <v>0.194251117299208</v>
@@ -39397,7 +39409,7 @@
         <v>1</v>
       </c>
       <c r="AP257" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ257" t="s">
         <v>118</v>
@@ -39413,7 +39425,7 @@
         <v>0</v>
       </c>
       <c r="AV257" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW257" t="s">
         <v>62</v>
@@ -39463,7 +39475,7 @@
         <v>-46.0311181823635</v>
       </c>
       <c r="N258" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O258" t="n">
         <v>0.173165129648517</v>
@@ -39547,7 +39559,7 @@
         <v>1</v>
       </c>
       <c r="AP258" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ258" t="s">
         <v>118</v>
@@ -39563,7 +39575,7 @@
         <v>0</v>
       </c>
       <c r="AV258" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW258" t="s">
         <v>62</v>
@@ -39613,7 +39625,7 @@
         <v>8.39776493200386</v>
       </c>
       <c r="N259" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O259" t="n">
         <v>0.184542626911111</v>
@@ -39697,7 +39709,7 @@
         <v>1</v>
       </c>
       <c r="AP259" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AQ259" t="s">
         <v>118</v>
@@ -39713,7 +39725,7 @@
         <v>0</v>
       </c>
       <c r="AV259" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW259" t="s">
         <v>62</v>
@@ -39763,7 +39775,7 @@
         <v>2.53179113079265</v>
       </c>
       <c r="N260" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="O260" t="n">
         <v>0.196185462430614</v>
@@ -39847,7 +39859,7 @@
         <v>1</v>
       </c>
       <c r="AP260" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AQ260" t="s">
         <v>118</v>
@@ -39863,7 +39875,7 @@
         <v>0</v>
       </c>
       <c r="AV260" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AW260" t="s">
         <v>62</v>
